--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2109,10 +2109,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118532207</v>
+        <v>118529884</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2121,30 +2121,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2165,13 +2165,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577207</v>
+        <v>577363</v>
       </c>
       <c r="R13" t="n">
-        <v>6558976</v>
+        <v>6558869</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2210,7 +2210,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blommande exemplar. 15 plantor under en granlåga med ullticka.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2237,7 +2242,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118529884</v>
+        <v>118530252</v>
       </c>
       <c r="B14" t="n">
         <v>104940</v>
@@ -2272,7 +2277,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2280,11 +2285,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2293,13 +2294,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577363</v>
+        <v>577257</v>
       </c>
       <c r="R14" t="n">
-        <v>6558869</v>
+        <v>6558906</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2328,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2338,12 +2339,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blommande exemplar. 15 plantor under en granlåga med ullticka.</t>
+          <t>Grönpyrola intill en låga. Knärot brevid. Ullticka, vedticka på granlåga ovanför. Fuktig sänka i barrnaturskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,10 +2371,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118530252</v>
+        <v>118532207</v>
       </c>
       <c r="B15" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,30 +2383,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2413,7 +2414,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2422,13 +2427,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577257</v>
+        <v>577207</v>
       </c>
       <c r="R15" t="n">
-        <v>6558906</v>
+        <v>6558976</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2467,12 +2472,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Grönpyrola intill en låga. Knärot brevid. Ullticka, vedticka på granlåga ovanför. Fuktig sänka i barrnaturskog</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2499,10 +2499,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118531233</v>
+        <v>118529201</v>
       </c>
       <c r="B16" t="n">
-        <v>97846</v>
+        <v>5166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2511,43 +2511,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2555,13 +2552,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577167</v>
+        <v>577341</v>
       </c>
       <c r="R16" t="n">
-        <v>6558870</v>
+        <v>6558833</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2590,7 +2587,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2600,12 +2597,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>28 plantor och tre blommande knärot.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2632,10 +2624,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118529201</v>
+        <v>118531233</v>
       </c>
       <c r="B17" t="n">
-        <v>5166</v>
+        <v>97846</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2644,40 +2636,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2685,13 +2680,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577341</v>
+        <v>577167</v>
       </c>
       <c r="R17" t="n">
-        <v>6558833</v>
+        <v>6558870</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2720,7 +2715,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2730,7 +2725,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>28 plantor och tre blommande knärot.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3394,10 +3394,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118531272</v>
+        <v>118531029</v>
       </c>
       <c r="B23" t="n">
-        <v>97846</v>
+        <v>58105</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3406,43 +3406,36 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3450,13 +3443,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>577176</v>
+        <v>577100</v>
       </c>
       <c r="R23" t="n">
-        <v>6558878</v>
+        <v>6558783</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3485,7 +3478,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3495,12 +3488,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 plantor en blommande</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3527,10 +3515,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118531470</v>
+        <v>118530351</v>
       </c>
       <c r="B24" t="n">
-        <v>97846</v>
+        <v>58105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3539,43 +3527,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3583,13 +3568,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>577201</v>
+        <v>577257</v>
       </c>
       <c r="R24" t="n">
-        <v>6558924</v>
+        <v>6558906</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3618,7 +3603,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3628,12 +3613,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Femtio plantor och en blommande</t>
+          <t>Flertalet paddor i skogen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3660,10 +3645,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118531029</v>
+        <v>118531272</v>
       </c>
       <c r="B25" t="n">
-        <v>58105</v>
+        <v>97846</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3672,36 +3657,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3709,13 +3701,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>577100</v>
+        <v>577176</v>
       </c>
       <c r="R25" t="n">
-        <v>6558783</v>
+        <v>6558878</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3744,7 +3736,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3754,7 +3746,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>5 plantor en blommande</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3781,10 +3778,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118530351</v>
+        <v>118531470</v>
       </c>
       <c r="B26" t="n">
-        <v>58105</v>
+        <v>97846</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3793,40 +3790,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3834,13 +3834,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>577257</v>
+        <v>577201</v>
       </c>
       <c r="R26" t="n">
-        <v>6558906</v>
+        <v>6558924</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flertalet paddor i skogen.</t>
+          <t>Femtio plantor och en blommande</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5177,10 +5177,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118607100</v>
+        <v>118604444</v>
       </c>
       <c r="B37" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5189,39 +5189,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5229,13 +5233,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577496</v>
+        <v>577389</v>
       </c>
       <c r="R37" t="n">
-        <v>6558946</v>
+        <v>6558832</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5264,7 +5268,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5274,7 +5278,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>16 plantor 2 blomnande knärot</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5301,10 +5310,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118604444</v>
+        <v>118607100</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5313,43 +5322,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5357,13 +5362,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577389</v>
+        <v>577496</v>
       </c>
       <c r="R38" t="n">
-        <v>6558832</v>
+        <v>6558946</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5392,7 +5397,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5402,12 +5407,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>16 plantor 2 blomnande knärot</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -8411,10 +8411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118657784</v>
+        <v>118656843</v>
       </c>
       <c r="B62" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8423,25 +8423,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8451,22 +8451,21 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hökhult (Hökhult), Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>577361</v>
+        <v>577542</v>
       </c>
       <c r="R62" t="n">
-        <v>6559178</v>
+        <v>6558904</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8498,7 +8497,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8508,12 +8507,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>1 floralt skott</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8528,7 +8522,7 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>Barrskog på blockmark</t>
+          <t>Hällmarksbarrskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -8546,10 +8540,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118656843</v>
+        <v>118657784</v>
       </c>
       <c r="B63" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8558,25 +8552,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8586,21 +8580,22 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Hökhult (Hökhult), Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>577542</v>
+        <v>577361</v>
       </c>
       <c r="R63" t="n">
-        <v>6558904</v>
+        <v>6559178</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8632,7 +8627,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8642,7 +8637,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1 floralt skott</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AH63" t="inlineStr">
         <is>
-          <t>Hällmarksbarrskog</t>
+          <t>Barrskog på blockmark</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118746645</v>
+        <v>118744246</v>
       </c>
       <c r="B72" t="n">
-        <v>57659</v>
+        <v>97846</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9703,53 +9703,57 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577424</v>
+        <v>577640</v>
       </c>
       <c r="R72" t="n">
-        <v>6558952</v>
+        <v>6558957</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9778,7 +9782,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9788,7 +9792,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>150 plantor i mossan. Flertalet blommande.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9939,10 +9948,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>118744246</v>
+        <v>118746645</v>
       </c>
       <c r="B74" t="n">
-        <v>97846</v>
+        <v>57659</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9951,57 +9960,53 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>577640</v>
+        <v>577424</v>
       </c>
       <c r="R74" t="n">
-        <v>6558957</v>
+        <v>6558952</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10030,7 +10035,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -10040,12 +10045,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>150 plantor i mossan. Flertalet blommande.</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10072,10 +10072,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118747517</v>
+        <v>118745374</v>
       </c>
       <c r="B75" t="n">
-        <v>91781</v>
+        <v>97846</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10084,52 +10084,53 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577315</v>
+        <v>577535</v>
       </c>
       <c r="R75" t="n">
-        <v>6559045</v>
+        <v>6558856</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10158,7 +10159,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10168,12 +10169,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10200,10 +10196,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118742934</v>
+        <v>118747517</v>
       </c>
       <c r="B76" t="n">
-        <v>79102</v>
+        <v>91781</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10216,30 +10212,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>788</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577625</v>
+        <v>577315</v>
       </c>
       <c r="R76" t="n">
-        <v>6559039</v>
+        <v>6559045</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10292,7 +10292,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10319,10 +10324,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118745374</v>
+        <v>118742934</v>
       </c>
       <c r="B77" t="n">
-        <v>97846</v>
+        <v>79102</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10331,53 +10336,48 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577535</v>
+        <v>577625</v>
       </c>
       <c r="R77" t="n">
-        <v>6558856</v>
+        <v>6559039</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -13248,10 +13248,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118746507</v>
+        <v>118743767</v>
       </c>
       <c r="B100" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13260,30 +13260,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -13296,14 +13296,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577446</v>
+        <v>577628</v>
       </c>
       <c r="R100" t="n">
-        <v>6558957</v>
+        <v>6558968</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13345,7 +13345,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Plantor i norrsluttning ner mot kärr.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13360,22 +13365,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118743767</v>
+        <v>118746507</v>
       </c>
       <c r="B101" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -13384,30 +13389,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -13420,14 +13425,14 @@
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>577628</v>
+        <v>577446</v>
       </c>
       <c r="R101" t="n">
-        <v>6558968</v>
+        <v>6558957</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -13459,7 +13464,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -13469,12 +13474,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Plantor i norrsluttning ner mot kärr.</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -13489,12 +13489,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -14014,10 +14014,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118762524</v>
+        <v>118763040</v>
       </c>
       <c r="B106" t="n">
-        <v>97846</v>
+        <v>8416</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -14026,53 +14026,50 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Söder om Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>577403</v>
+        <v>577568</v>
       </c>
       <c r="R106" t="n">
-        <v>6559045</v>
+        <v>6559189</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -14101,7 +14098,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -14111,12 +14108,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Blommande knärot och 14 plantor90</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -14136,7 +14128,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>Barrnaturskog</t>
+          <t>Äldre hällmarkskog</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -14154,10 +14146,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>118763040</v>
+        <v>118762524</v>
       </c>
       <c r="B107" t="n">
-        <v>8416</v>
+        <v>97846</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -14166,50 +14158,53 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Söder om Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>577568</v>
+        <v>577403</v>
       </c>
       <c r="R107" t="n">
-        <v>6559189</v>
+        <v>6559045</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -14238,7 +14233,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -14248,7 +14243,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Blommande knärot och 14 plantor90</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -14268,7 +14268,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>Äldre hällmarkskog</t>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2757,10 +2757,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118530482</v>
+        <v>118531964</v>
       </c>
       <c r="B18" t="n">
-        <v>5186</v>
+        <v>97846</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2769,40 +2769,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2810,13 +2809,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577273</v>
+        <v>577215</v>
       </c>
       <c r="R18" t="n">
-        <v>6558897</v>
+        <v>6558945</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2845,7 +2844,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2855,7 +2854,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>29 plantor. 3 blommande</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2882,10 +2886,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118531964</v>
+        <v>118530482</v>
       </c>
       <c r="B19" t="n">
-        <v>97846</v>
+        <v>5186</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2894,39 +2898,40 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2934,13 +2939,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>577215</v>
+        <v>577273</v>
       </c>
       <c r="R19" t="n">
-        <v>6558945</v>
+        <v>6558897</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2969,7 +2974,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2979,12 +2984,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>29 plantor. 3 blommande</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -10072,10 +10072,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>118745374</v>
+        <v>118747517</v>
       </c>
       <c r="B75" t="n">
-        <v>97846</v>
+        <v>91781</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10084,53 +10084,52 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>577535</v>
+        <v>577315</v>
       </c>
       <c r="R75" t="n">
-        <v>6558856</v>
+        <v>6559045</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -10159,7 +10158,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10169,7 +10168,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10196,10 +10200,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>118747517</v>
+        <v>118742934</v>
       </c>
       <c r="B76" t="n">
-        <v>91781</v>
+        <v>79102</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10212,34 +10216,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>788</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>577315</v>
+        <v>577625</v>
       </c>
       <c r="R76" t="n">
-        <v>6559045</v>
+        <v>6559039</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -10282,7 +10282,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10292,12 +10292,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10324,10 +10319,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>118742934</v>
+        <v>118745374</v>
       </c>
       <c r="B77" t="n">
-        <v>79102</v>
+        <v>97846</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10336,48 +10331,53 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>577625</v>
+        <v>577535</v>
       </c>
       <c r="R77" t="n">
-        <v>6559039</v>
+        <v>6558856</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10825,10 +10825,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>118746174</v>
+        <v>118745057</v>
       </c>
       <c r="B81" t="n">
-        <v>58105</v>
+        <v>97846</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10837,62 +10837,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>577447</v>
+        <v>577589</v>
       </c>
       <c r="R81" t="n">
-        <v>6558938</v>
+        <v>6558945</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10921,7 +10912,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10931,7 +10922,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10958,7 +10949,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118745057</v>
+        <v>118745233</v>
       </c>
       <c r="B82" t="n">
         <v>97846</v>
@@ -10993,7 +10984,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -11001,19 +10992,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>577589</v>
+        <v>577546</v>
       </c>
       <c r="R82" t="n">
-        <v>6558945</v>
+        <v>6558828</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -11045,7 +11040,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -11055,7 +11050,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11070,22 +11065,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118745233</v>
+        <v>118746174</v>
       </c>
       <c r="B83" t="n">
-        <v>97846</v>
+        <v>58105</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -11094,57 +11089,62 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>208245</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>577546</v>
+        <v>577447</v>
       </c>
       <c r="R83" t="n">
-        <v>6558828</v>
+        <v>6558938</v>
       </c>
       <c r="S83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11198,12 +11198,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4418,10 +4418,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118606898</v>
+        <v>118606437</v>
       </c>
       <c r="B31" t="n">
-        <v>91779</v>
+        <v>56502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4434,30 +4434,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4465,13 +4474,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>577545</v>
+        <v>577532</v>
       </c>
       <c r="R31" t="n">
-        <v>6558905</v>
+        <v>6558938</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4500,7 +4509,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4510,7 +4519,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Uppflygande tjädertupp i barrnaturskog på hällmark.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4537,10 +4551,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118606437</v>
+        <v>118606898</v>
       </c>
       <c r="B32" t="n">
-        <v>56502</v>
+        <v>91779</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4553,39 +4567,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4593,13 +4598,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>577532</v>
+        <v>577545</v>
       </c>
       <c r="R32" t="n">
-        <v>6558938</v>
+        <v>6558905</v>
       </c>
       <c r="S32" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4628,7 +4633,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4638,12 +4643,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Uppflygande tjädertupp i barrnaturskog på hällmark.</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4799,42 +4799,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118608044</v>
+        <v>118604444</v>
       </c>
       <c r="B34" t="n">
-        <v>94620</v>
+        <v>97846</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4843,13 +4855,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>577450</v>
+        <v>577389</v>
       </c>
       <c r="R34" t="n">
-        <v>6558784</v>
+        <v>6558832</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4878,7 +4890,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4888,12 +4900,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Stort bestånd med blåmossa. På äldre hällmarkstallskog. Skogsområdet avverkningsanmält.</t>
+          <t>16 plantor 2 blomnande knärot</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4920,54 +4932,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118604444</v>
+        <v>118608044</v>
       </c>
       <c r="B35" t="n">
-        <v>97846</v>
+        <v>94620</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4976,13 +4976,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>577389</v>
+        <v>577450</v>
       </c>
       <c r="R35" t="n">
-        <v>6558832</v>
+        <v>6558784</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>16 plantor 2 blomnande knärot</t>
+          <t>Stort bestånd med blåmossa. På äldre hällmarkstallskog. Skogsområdet avverkningsanmält.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5186,10 +5186,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118609397</v>
+        <v>118605786</v>
       </c>
       <c r="B37" t="n">
-        <v>90908</v>
+        <v>97846</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5198,34 +5198,35 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5233,10 +5234,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>577425</v>
+        <v>577513</v>
       </c>
       <c r="R37" t="n">
-        <v>6558745</v>
+        <v>6558801</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -5268,7 +5269,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5278,12 +5279,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer unddr gammal tall på hällmarkstallskog på 100 möh. Skogen är avverkningsanmäld av certifierat skogsbruk.</t>
+          <t>Nio plantor. Tre blommande exemplar</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5310,10 +5311,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118605786</v>
+        <v>118609397</v>
       </c>
       <c r="B38" t="n">
-        <v>97846</v>
+        <v>90908</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5322,35 +5323,34 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5358,10 +5358,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>577513</v>
+        <v>577425</v>
       </c>
       <c r="R38" t="n">
-        <v>6558801</v>
+        <v>6558745</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5393,7 +5393,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5403,12 +5403,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Nio plantor. Tre blommande exemplar</t>
+          <t>Växer unddr gammal tall på hällmarkstallskog på 100 möh. Skogen är avverkningsanmäld av certifierat skogsbruk.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -6211,10 +6211,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118607040</v>
+        <v>118608463</v>
       </c>
       <c r="B45" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6223,43 +6223,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6267,13 +6267,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>577471</v>
+        <v>577454</v>
       </c>
       <c r="R45" t="n">
-        <v>6558868</v>
+        <v>6558802</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6339,10 +6339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118608463</v>
+        <v>118607040</v>
       </c>
       <c r="B46" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6351,43 +6351,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6395,13 +6395,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>577454</v>
+        <v>577471</v>
       </c>
       <c r="R46" t="n">
-        <v>6558802</v>
+        <v>6558868</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6854,10 +6854,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118604257</v>
+        <v>118605873</v>
       </c>
       <c r="B50" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6866,38 +6866,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
@@ -6906,13 +6906,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>577388</v>
+        <v>577513</v>
       </c>
       <c r="R50" t="n">
-        <v>6558909</v>
+        <v>6558801</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Tjugo plantor tre blommande.</t>
+          <t>Hundratals plantor. Flertalet blomställningar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6983,7 +6983,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118608594</v>
+        <v>118604257</v>
       </c>
       <c r="B51" t="n">
         <v>97846</v>
@@ -7016,13 +7016,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -7031,13 +7035,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>577525</v>
+        <v>577388</v>
       </c>
       <c r="R51" t="n">
-        <v>6558770</v>
+        <v>6558909</v>
       </c>
       <c r="S51" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -7066,7 +7070,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7076,12 +7080,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Tolv plantor. 2 blommande.</t>
+          <t>Tjugo plantor tre blommande.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7090,7 +7094,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7109,10 +7112,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118605873</v>
+        <v>118608594</v>
       </c>
       <c r="B52" t="n">
-        <v>104940</v>
+        <v>97846</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7121,37 +7124,33 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -7161,13 +7160,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>577513</v>
+        <v>577525</v>
       </c>
       <c r="R52" t="n">
-        <v>6558801</v>
+        <v>6558770</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7196,7 +7195,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7206,12 +7205,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Hundratals plantor. Flertalet blomställningar</t>
+          <t>Tolv plantor. 2 blommande.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7220,6 +7219,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118659071</v>
+        <v>118657203</v>
       </c>
       <c r="B58" t="n">
-        <v>57443</v>
+        <v>97846</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7901,39 +7901,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7941,13 +7941,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>577635</v>
+        <v>577269</v>
       </c>
       <c r="R58" t="n">
-        <v>6558998</v>
+        <v>6559022</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7986,7 +7986,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1 floralt skott</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7995,6 +8000,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8018,10 +8024,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118657203</v>
+        <v>118659071</v>
       </c>
       <c r="B59" t="n">
-        <v>97846</v>
+        <v>57443</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8030,39 +8036,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -8070,13 +8076,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>577269</v>
+        <v>577635</v>
       </c>
       <c r="R59" t="n">
-        <v>6559022</v>
+        <v>6558998</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -8105,7 +8111,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8115,12 +8121,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>1 floralt skott</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8129,7 +8130,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8153,10 +8153,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118656843</v>
+        <v>118656671</v>
       </c>
       <c r="B60" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8165,49 +8165,46 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Svalboviken, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>577542</v>
+        <v>577407</v>
       </c>
       <c r="R60" t="n">
-        <v>6558904</v>
+        <v>6559090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8234,22 +8231,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Flertalet blommande exemplar och många plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8264,28 +8266,33 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Hällmarksbarrskog</t>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Barrnaturskog</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118656671</v>
+        <v>118656843</v>
       </c>
       <c r="B61" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8294,46 +8301,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Svalboviken, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>577407</v>
+        <v>577542</v>
       </c>
       <c r="R61" t="n">
-        <v>6559090</v>
+        <v>6558904</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8360,27 +8370,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Flertalet blommande exemplar och många plantor</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8395,23 +8400,18 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Barrnaturskog</t>
+          <t>Hällmarksbarrskog</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -11475,7 +11475,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118743247</v>
+        <v>118742646</v>
       </c>
       <c r="B86" t="n">
         <v>97846</v>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11527,17 +11527,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>577655</v>
+        <v>577605</v>
       </c>
       <c r="R86" t="n">
-        <v>6559000</v>
+        <v>6559123</v>
       </c>
       <c r="S86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11576,7 +11576,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11603,7 +11603,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118742646</v>
+        <v>118743247</v>
       </c>
       <c r="B87" t="n">
         <v>97846</v>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11655,17 +11655,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>577605</v>
+        <v>577655</v>
       </c>
       <c r="R87" t="n">
-        <v>6559123</v>
+        <v>6559000</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -12612,10 +12612,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118745272</v>
+        <v>118747303</v>
       </c>
       <c r="B95" t="n">
-        <v>104940</v>
+        <v>58105</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -12628,46 +12628,55 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>208245</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>577546</v>
+        <v>577315</v>
       </c>
       <c r="R95" t="n">
-        <v>6558828</v>
+        <v>6559045</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -12699,7 +12708,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -12709,7 +12718,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12724,22 +12733,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118745173</v>
+        <v>118745272</v>
       </c>
       <c r="B96" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -12748,30 +12757,30 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12779,11 +12788,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12792,13 +12797,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>577561</v>
+        <v>577546</v>
       </c>
       <c r="R96" t="n">
-        <v>6558827</v>
+        <v>6558828</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -12827,7 +12832,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12837,12 +12842,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Arton plantor. Två blommande</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -13002,10 +13002,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118747303</v>
+        <v>118745173</v>
       </c>
       <c r="B98" t="n">
-        <v>58105</v>
+        <v>97846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -13014,62 +13014,57 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>577315</v>
+        <v>577561</v>
       </c>
       <c r="R98" t="n">
-        <v>6559045</v>
+        <v>6558827</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -13098,7 +13093,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -13108,7 +13103,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Arton plantor. Två blommande</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13123,12 +13123,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -13642,7 +13642,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118745233</v>
+        <v>118745126</v>
       </c>
       <c r="B103" t="n">
         <v>97846</v>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13685,11 +13685,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -13698,13 +13694,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>577546</v>
+        <v>577539</v>
       </c>
       <c r="R103" t="n">
-        <v>6558828</v>
+        <v>6558820</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13733,7 +13729,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13743,7 +13739,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13770,7 +13766,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118745126</v>
+        <v>118745233</v>
       </c>
       <c r="B104" t="n">
         <v>97846</v>
@@ -13805,7 +13801,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13813,7 +13809,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
@@ -13822,13 +13822,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>577539</v>
+        <v>577546</v>
       </c>
       <c r="R104" t="n">
-        <v>6558820</v>
+        <v>6558828</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -16343,10 +16343,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>118762639</v>
+        <v>118762567</v>
       </c>
       <c r="B123" t="n">
-        <v>5186</v>
+        <v>97846</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -16355,36 +16355,39 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -16392,10 +16395,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>577415</v>
+        <v>577399</v>
       </c>
       <c r="R123" t="n">
-        <v>6559052</v>
+        <v>6559046</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -16438,6 +16441,11 @@
       <c r="AB123" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Hundratals plantor och blommande knärot i området.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -16475,10 +16483,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118762567</v>
+        <v>118762639</v>
       </c>
       <c r="B124" t="n">
-        <v>97846</v>
+        <v>5186</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -16487,39 +16495,36 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -16527,10 +16532,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>577399</v>
+        <v>577415</v>
       </c>
       <c r="R124" t="n">
-        <v>6559046</v>
+        <v>6559052</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -16573,11 +16578,6 @@
       <c r="AB124" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Hundratals plantor och blommande knärot i området.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -17842,6 +17842,1030 @@
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>118905061</v>
+      </c>
+      <c r="B134" t="n">
+        <v>91771</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>577317</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6559085</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>118903309</v>
+      </c>
+      <c r="B135" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>118904803</v>
+      </c>
+      <c r="B136" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>118903917</v>
+      </c>
+      <c r="B137" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>577317</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6559085</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>118901779</v>
+      </c>
+      <c r="B138" t="n">
+        <v>91771</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>118899119</v>
+      </c>
+      <c r="B139" t="n">
+        <v>91781</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>788</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>118905087</v>
+      </c>
+      <c r="B140" t="n">
+        <v>91779</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>118904861</v>
+      </c>
+      <c r="B141" t="n">
+        <v>90524</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>577302</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6559095</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>118898334</v>
+      </c>
+      <c r="B142" t="n">
+        <v>97846</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>577361</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6559062</v>
+      </c>
+      <c r="S142" t="n">
+        <v>4</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -1332,7 +1332,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118531539</v>
+        <v>118531470</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577210</v>
+        <v>577201</v>
       </c>
       <c r="R7" t="n">
-        <v>6558919</v>
+        <v>6558924</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>16 plantor. Tre blommande</t>
+          <t>Femtio plantor och en blommande</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1465,7 +1465,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118531470</v>
+        <v>118531539</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577201</v>
+        <v>577210</v>
       </c>
       <c r="R8" t="n">
-        <v>6558924</v>
+        <v>6558919</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Femtio plantor och en blommande</t>
+          <t>16 plantor. Tre blommande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -9451,10 +9451,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118745374</v>
+        <v>118741902</v>
       </c>
       <c r="B70" t="n">
-        <v>97853</v>
+        <v>5166</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9463,53 +9463,54 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>577535</v>
+        <v>577559</v>
       </c>
       <c r="R70" t="n">
-        <v>6558856</v>
+        <v>6559169</v>
       </c>
       <c r="S70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9538,7 +9539,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9548,7 +9549,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9575,7 +9576,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118746563</v>
+        <v>118745374</v>
       </c>
       <c r="B71" t="n">
         <v>97853</v>
@@ -9610,7 +9611,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9618,11 +9619,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
@@ -9631,13 +9628,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>577424</v>
+        <v>577535</v>
       </c>
       <c r="R71" t="n">
-        <v>6558952</v>
+        <v>6558856</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9666,7 +9663,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9676,7 +9673,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9691,19 +9688,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118743731</v>
+        <v>118746563</v>
       </c>
       <c r="B72" t="n">
         <v>97853</v>
@@ -9738,7 +9735,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9746,22 +9743,26 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>577636</v>
+        <v>577424</v>
       </c>
       <c r="R72" t="n">
-        <v>6558986</v>
+        <v>6558952</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9790,7 +9791,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9800,7 +9801,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9815,22 +9816,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>118741902</v>
+        <v>118743731</v>
       </c>
       <c r="B73" t="n">
-        <v>5166</v>
+        <v>97853</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9839,54 +9840,53 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>577559</v>
+        <v>577636</v>
       </c>
       <c r="R73" t="n">
-        <v>6559169</v>
+        <v>6558986</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10462,10 +10462,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>118746174</v>
+        <v>118745546</v>
       </c>
       <c r="B78" t="n">
-        <v>58105</v>
+        <v>97853</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10474,62 +10474,57 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>årsunge</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>577447</v>
+        <v>577533</v>
       </c>
       <c r="R78" t="n">
-        <v>6558938</v>
+        <v>6558857</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10558,7 +10553,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10568,7 +10563,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10595,10 +10590,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>118745546</v>
+        <v>118743698</v>
       </c>
       <c r="B79" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10607,30 +10602,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10638,26 +10633,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>577533</v>
+        <v>577636</v>
       </c>
       <c r="R79" t="n">
-        <v>6558857</v>
+        <v>6558986</v>
       </c>
       <c r="S79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -10686,7 +10677,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10696,7 +10687,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10723,10 +10714,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118743698</v>
+        <v>118746174</v>
       </c>
       <c r="B80" t="n">
-        <v>104947</v>
+        <v>58105</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10739,49 +10730,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>208245</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>577636</v>
+        <v>577447</v>
       </c>
       <c r="R80" t="n">
-        <v>6558986</v>
+        <v>6558938</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -13128,10 +13128,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118746645</v>
+        <v>118742959</v>
       </c>
       <c r="B99" t="n">
-        <v>57659</v>
+        <v>79109</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -13140,50 +13140,45 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>577424</v>
+        <v>577603</v>
       </c>
       <c r="R99" t="n">
-        <v>6558952</v>
+        <v>6559106</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -13215,7 +13210,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -13225,7 +13220,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Växer på gammal tallstubbe på hällmark</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13252,10 +13252,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118745157</v>
+        <v>118746645</v>
       </c>
       <c r="B100" t="n">
-        <v>97853</v>
+        <v>57659</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -13264,39 +13264,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -13304,10 +13304,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>577561</v>
+        <v>577424</v>
       </c>
       <c r="R100" t="n">
-        <v>6558808</v>
+        <v>6558952</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13364,12 +13364,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -13501,10 +13501,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118742959</v>
+        <v>118745157</v>
       </c>
       <c r="B102" t="n">
-        <v>79109</v>
+        <v>97853</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -13513,45 +13513,50 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>577603</v>
+        <v>577561</v>
       </c>
       <c r="R102" t="n">
-        <v>6559106</v>
+        <v>6558808</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -13583,7 +13588,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -13593,12 +13598,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Växer på gammal tallstubbe på hällmark</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -13613,22 +13613,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118747517</v>
+        <v>118747088</v>
       </c>
       <c r="B103" t="n">
-        <v>91788</v>
+        <v>97853</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -13637,38 +13637,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -13676,13 +13681,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>577315</v>
+        <v>577380</v>
       </c>
       <c r="R103" t="n">
-        <v>6559045</v>
+        <v>6559017</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -13711,7 +13716,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13721,12 +13726,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
+          <t>En blommande. Åtta plantor</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13741,22 +13746,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118747088</v>
+        <v>118747517</v>
       </c>
       <c r="B104" t="n">
-        <v>97853</v>
+        <v>91788</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -13765,43 +13770,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -13809,13 +13809,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>577380</v>
+        <v>577315</v>
       </c>
       <c r="R104" t="n">
-        <v>6559017</v>
+        <v>6559045</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>En blommande. Åtta plantor</t>
+          <t>Fuktig grannaturskog. Växer som i en häxring. Både gamla och nya exemplar</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13874,12 +13874,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -25493,10 +25493,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119603136</v>
+        <v>119612860</v>
       </c>
       <c r="B198" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -25505,48 +25505,61 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 3, knärot 325 m s, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>577241</v>
+        <v>577550</v>
       </c>
       <c r="R198" t="n">
-        <v>6558978</v>
+        <v>6559170</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25568,54 +25581,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>D-Kat-0635</t>
+        </is>
+      </c>
       <c r="Y198" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
+      </c>
+      <c r="AH198" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI198" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
-        </is>
-      </c>
-      <c r="AY198" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119612860</v>
+        <v>119603136</v>
       </c>
       <c r="B199" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -25624,61 +25647,48 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Strandmossen 3, knärot 325 m s, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>577550</v>
+        <v>577241</v>
       </c>
       <c r="R199" t="n">
-        <v>6559170</v>
+        <v>6558978</v>
       </c>
       <c r="S199" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25700,57 +25710,47 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>D-Kat-0635</t>
-        </is>
-      </c>
       <c r="Y199" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
-      </c>
-      <c r="AH199" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI199" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY199" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jessica Loddby de Neergaard</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -26615,10 +26615,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119701851</v>
+        <v>119699345</v>
       </c>
       <c r="B207" t="n">
-        <v>91861</v>
+        <v>91858</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26627,41 +26627,41 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>5964</v>
+        <v>4368</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>577273</v>
+        <v>577474</v>
       </c>
       <c r="R207" t="n">
-        <v>6559028</v>
+        <v>6559036</v>
       </c>
       <c r="S207" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26717,10 +26717,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119699345</v>
+        <v>119699553</v>
       </c>
       <c r="B208" t="n">
-        <v>91858</v>
+        <v>91842</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26733,21 +26733,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -26757,13 +26757,13 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>577474</v>
+        <v>577460</v>
       </c>
       <c r="R208" t="n">
-        <v>6559036</v>
+        <v>6559048</v>
       </c>
       <c r="S208" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26819,10 +26819,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699553</v>
+        <v>119701851</v>
       </c>
       <c r="B209" t="n">
-        <v>91842</v>
+        <v>91861</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26831,38 +26831,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>788</v>
+        <v>5964</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577460</v>
+        <v>577273</v>
       </c>
       <c r="R209" t="n">
-        <v>6559048</v>
+        <v>6559028</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -27659,10 +27659,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119699969</v>
+        <v>119701745</v>
       </c>
       <c r="B217" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27675,34 +27675,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577561</v>
+        <v>577203</v>
       </c>
       <c r="R217" t="n">
-        <v>6558994</v>
+        <v>6558998</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27761,10 +27761,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119699197</v>
+        <v>119699969</v>
       </c>
       <c r="B218" t="n">
-        <v>91858</v>
+        <v>91840</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27773,25 +27773,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27801,10 +27801,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577394</v>
+        <v>577561</v>
       </c>
       <c r="R218" t="n">
-        <v>6559096</v>
+        <v>6558994</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27863,10 +27863,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119701745</v>
+        <v>119699197</v>
       </c>
       <c r="B219" t="n">
-        <v>91185</v>
+        <v>91858</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27875,38 +27875,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6031</v>
+        <v>4368</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577203</v>
+        <v>577394</v>
       </c>
       <c r="R219" t="n">
-        <v>6558998</v>
+        <v>6559096</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -23515,10 +23515,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119603453</v>
+        <v>119602380</v>
       </c>
       <c r="B182" t="n">
-        <v>4772</v>
+        <v>97907</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -23527,43 +23527,50 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M182" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>577583</v>
+        <v>577448</v>
       </c>
       <c r="R182" t="n">
-        <v>6559135</v>
+        <v>6558899</v>
       </c>
       <c r="S182" t="n">
         <v>4</v>
@@ -23595,7 +23602,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -23605,7 +23612,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -23620,22 +23627,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119602380</v>
+        <v>119603453</v>
       </c>
       <c r="B183" t="n">
-        <v>97907</v>
+        <v>4772</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -23644,50 +23651,43 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>577448</v>
+        <v>577583</v>
       </c>
       <c r="R183" t="n">
-        <v>6558899</v>
+        <v>6559135</v>
       </c>
       <c r="S183" t="n">
         <v>4</v>
@@ -23719,7 +23719,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23744,12 +23744,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
@@ -23993,10 +23993,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119601286</v>
+        <v>119601087</v>
       </c>
       <c r="B186" t="n">
-        <v>97907</v>
+        <v>91228</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -24009,46 +24009,48 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>577556</v>
+        <v>577575</v>
       </c>
       <c r="R186" t="n">
-        <v>6558966</v>
+        <v>6558990</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24077,7 +24079,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -24087,7 +24089,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24098,31 +24100,26 @@
       </c>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119612701</v>
+        <v>119599959</v>
       </c>
       <c r="B187" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -24131,61 +24128,54 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Strandmossen, knärot 300 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>577461</v>
+        <v>577484</v>
       </c>
       <c r="R187" t="n">
-        <v>6559175</v>
+        <v>6559147</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -24207,64 +24197,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>D-Kat-0634</t>
-        </is>
-      </c>
       <c r="Y187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY187" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119599959</v>
+        <v>119601987</v>
       </c>
       <c r="B188" t="n">
-        <v>5189</v>
+        <v>94681</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -24277,50 +24257,45 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>105930</v>
+        <v>2180</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>577484</v>
+        <v>577535</v>
       </c>
       <c r="R188" t="n">
-        <v>6559147</v>
+        <v>6558941</v>
       </c>
       <c r="S188" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24349,7 +24324,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24359,7 +24334,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24374,12 +24349,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
@@ -24510,10 +24485,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119601087</v>
+        <v>119601286</v>
       </c>
       <c r="B190" t="n">
-        <v>91228</v>
+        <v>97907</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -24526,48 +24501,46 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577575</v>
+        <v>577556</v>
       </c>
       <c r="R190" t="n">
-        <v>6558990</v>
+        <v>6558966</v>
       </c>
       <c r="S190" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24596,7 +24569,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24606,7 +24579,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24617,26 +24590,31 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
+      </c>
+      <c r="AH190" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119601987</v>
+        <v>119612701</v>
       </c>
       <c r="B191" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -24645,49 +24623,61 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, knärot 300 m s, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577535</v>
+        <v>577461</v>
       </c>
       <c r="R191" t="n">
-        <v>6558941</v>
+        <v>6559175</v>
       </c>
       <c r="S191" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24709,47 +24699,57 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>D-Kat-0634</t>
+        </is>
+      </c>
       <c r="Y191" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
+      </c>
+      <c r="AH191" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI191" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
-        </is>
-      </c>
-      <c r="AY191" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -27659,10 +27659,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119701745</v>
+        <v>119699969</v>
       </c>
       <c r="B217" t="n">
-        <v>91185</v>
+        <v>91840</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27675,34 +27675,34 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577203</v>
+        <v>577561</v>
       </c>
       <c r="R217" t="n">
-        <v>6558998</v>
+        <v>6558994</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27761,10 +27761,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119699969</v>
+        <v>119699197</v>
       </c>
       <c r="B218" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27773,25 +27773,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4364</v>
+        <v>4368</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27801,10 +27801,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577561</v>
+        <v>577394</v>
       </c>
       <c r="R218" t="n">
-        <v>6558994</v>
+        <v>6559096</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27863,10 +27863,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119699197</v>
+        <v>119701745</v>
       </c>
       <c r="B219" t="n">
-        <v>91858</v>
+        <v>91185</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27875,38 +27875,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4368</v>
+        <v>6031</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577394</v>
+        <v>577203</v>
       </c>
       <c r="R219" t="n">
-        <v>6559096</v>
+        <v>6558998</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -27965,7 +27965,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119701628</v>
+        <v>119699201</v>
       </c>
       <c r="B220" t="n">
         <v>97907</v>
@@ -28001,14 +28001,14 @@
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577186</v>
+        <v>577394</v>
       </c>
       <c r="R220" t="n">
-        <v>6558951</v>
+        <v>6559096</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -28067,7 +28067,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119699201</v>
+        <v>119701628</v>
       </c>
       <c r="B221" t="n">
         <v>97907</v>
@@ -28103,14 +28103,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577394</v>
+        <v>577186</v>
       </c>
       <c r="R221" t="n">
-        <v>6559096</v>
+        <v>6558951</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -21178,10 +21178,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119602238</v>
+        <v>119601987</v>
       </c>
       <c r="B163" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -21194,34 +21194,31 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
@@ -21229,13 +21226,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>577459</v>
+        <v>577535</v>
       </c>
       <c r="R163" t="n">
-        <v>6558921</v>
+        <v>6558941</v>
       </c>
       <c r="S163" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -21264,7 +21261,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -21274,7 +21271,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -21289,22 +21286,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119602564</v>
+        <v>119601316</v>
       </c>
       <c r="B164" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -21313,50 +21310,54 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>577409</v>
+        <v>577573</v>
       </c>
       <c r="R164" t="n">
-        <v>6558923</v>
+        <v>6558989</v>
       </c>
       <c r="S164" t="n">
         <v>4</v>
@@ -21388,7 +21389,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -21398,7 +21399,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21425,10 +21426,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119599599</v>
+        <v>119602671</v>
       </c>
       <c r="B165" t="n">
-        <v>90582</v>
+        <v>91832</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21441,46 +21442,44 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5442</v>
+        <v>4361</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>577474</v>
+        <v>577392</v>
       </c>
       <c r="R165" t="n">
-        <v>6559269</v>
+        <v>6558896</v>
       </c>
       <c r="S165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -21509,7 +21508,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -21519,7 +21518,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -21534,22 +21533,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119603449</v>
+        <v>119603201</v>
       </c>
       <c r="B166" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -21558,48 +21557,50 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>577598</v>
+        <v>577223</v>
       </c>
       <c r="R166" t="n">
-        <v>6559069</v>
+        <v>6558959</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21628,7 +21629,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -21638,7 +21639,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -21649,26 +21650,31 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119600732</v>
+        <v>119599963</v>
       </c>
       <c r="B167" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -21677,53 +21683,49 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>577625</v>
+        <v>577548</v>
       </c>
       <c r="R167" t="n">
-        <v>6559039</v>
+        <v>6559163</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -21752,7 +21754,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -21762,7 +21764,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -21777,22 +21779,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119600824</v>
+        <v>119601728</v>
       </c>
       <c r="B168" t="n">
-        <v>58166</v>
+        <v>90334</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -21805,21 +21807,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>208249</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -21827,14 +21829,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr"/>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -21842,13 +21842,13 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>577588</v>
+        <v>577557</v>
       </c>
       <c r="R168" t="n">
-        <v>6559049</v>
+        <v>6558969</v>
       </c>
       <c r="S168" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -21887,7 +21887,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -21902,22 +21902,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119599963</v>
+        <v>119602562</v>
       </c>
       <c r="B169" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21926,49 +21926,53 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>577548</v>
+        <v>577392</v>
       </c>
       <c r="R169" t="n">
-        <v>6559163</v>
+        <v>6558906</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -21997,7 +22001,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -22007,7 +22011,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -22022,22 +22026,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119602448</v>
+        <v>119601087</v>
       </c>
       <c r="B170" t="n">
-        <v>94681</v>
+        <v>91228</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -22046,46 +22050,49 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2180</v>
+        <v>898</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>577444</v>
+        <v>577575</v>
       </c>
       <c r="R170" t="n">
-        <v>6558882</v>
+        <v>6558990</v>
       </c>
       <c r="S170" t="n">
         <v>4</v>
@@ -22117,7 +22124,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -22127,7 +22134,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22154,10 +22161,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119601316</v>
+        <v>119603449</v>
       </c>
       <c r="B171" t="n">
-        <v>57326</v>
+        <v>79144</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -22170,50 +22177,41 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>577573</v>
+        <v>577598</v>
       </c>
       <c r="R171" t="n">
-        <v>6558989</v>
+        <v>6559069</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -22245,7 +22243,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -22255,7 +22253,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22270,22 +22268,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119599958</v>
+        <v>119599396</v>
       </c>
       <c r="B172" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -22294,51 +22292,46 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>577484</v>
+        <v>577460</v>
       </c>
       <c r="R172" t="n">
-        <v>6559147</v>
+        <v>6559174</v>
       </c>
       <c r="S172" t="n">
         <v>4</v>
@@ -22370,7 +22363,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -22380,7 +22373,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -22407,10 +22400,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119599967</v>
+        <v>119599958</v>
       </c>
       <c r="B173" t="n">
-        <v>94681</v>
+        <v>5169</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -22423,28 +22416,37 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
@@ -22486,7 +22488,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -22496,7 +22498,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -22523,10 +22525,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119599395</v>
+        <v>119602000</v>
       </c>
       <c r="B174" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -22535,52 +22537,49 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>577449</v>
+        <v>577523</v>
       </c>
       <c r="R174" t="n">
-        <v>6559178</v>
+        <v>6558933</v>
       </c>
       <c r="S174" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -22609,7 +22608,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -22619,7 +22618,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -22634,22 +22633,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119602280</v>
+        <v>119602238</v>
       </c>
       <c r="B175" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -22658,50 +22657,52 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>577412</v>
+        <v>577459</v>
       </c>
       <c r="R175" t="n">
-        <v>6558928</v>
+        <v>6558921</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -22730,7 +22731,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -22740,7 +22741,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -22755,22 +22756,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119602497</v>
+        <v>119612860</v>
       </c>
       <c r="B176" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -22779,49 +22780,61 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
-      <c r="K176" t="inlineStr"/>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 3, knärot 325 m s, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>577411</v>
+        <v>577550</v>
       </c>
       <c r="R176" t="n">
-        <v>6558925</v>
+        <v>6559170</v>
       </c>
       <c r="S176" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -22843,54 +22856,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>D-Kat-0635</t>
+        </is>
+      </c>
       <c r="Y176" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>14:39</t>
-        </is>
-      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
+      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
+      </c>
+      <c r="AH176" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI176" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119599816</v>
+        <v>119601607</v>
       </c>
       <c r="B177" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -22899,38 +22922,39 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -22938,13 +22962,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>577555</v>
+        <v>577578</v>
       </c>
       <c r="R177" t="n">
-        <v>6559157</v>
+        <v>6558968</v>
       </c>
       <c r="S177" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -22973,7 +22997,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -22983,7 +23007,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -22998,22 +23022,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119599396</v>
+        <v>119599599</v>
       </c>
       <c r="B178" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -23022,49 +23046,50 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>577460</v>
+        <v>577474</v>
       </c>
       <c r="R178" t="n">
-        <v>6559174</v>
+        <v>6559269</v>
       </c>
       <c r="S178" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -23093,7 +23118,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -23103,7 +23128,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23118,22 +23143,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119602671</v>
+        <v>119601750</v>
       </c>
       <c r="B179" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -23142,48 +23167,53 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr"/>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>577392</v>
+        <v>577554</v>
       </c>
       <c r="R179" t="n">
-        <v>6558896</v>
+        <v>6558959</v>
       </c>
       <c r="S179" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -23212,7 +23242,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23222,7 +23252,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23249,10 +23279,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119600170</v>
+        <v>119601840</v>
       </c>
       <c r="B180" t="n">
-        <v>97907</v>
+        <v>90057</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -23265,46 +23295,45 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>577585</v>
+        <v>577557</v>
       </c>
       <c r="R180" t="n">
-        <v>6559134</v>
+        <v>6558949</v>
       </c>
       <c r="S180" t="n">
         <v>4</v>
@@ -23336,7 +23365,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -23346,7 +23375,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23373,10 +23402,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119612900</v>
+        <v>119601454</v>
       </c>
       <c r="B181" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -23385,61 +23414,52 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Strandmossen 4, knärot 360 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>577583</v>
+        <v>577558</v>
       </c>
       <c r="R181" t="n">
-        <v>6559135</v>
+        <v>6558970</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -23461,61 +23481,51 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>D-Kat-0636</t>
-        </is>
-      </c>
       <c r="Y181" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
         <v>0</v>
       </c>
-      <c r="AF181" t="inlineStr"/>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI181" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY181" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119602380</v>
+        <v>119612900</v>
       </c>
       <c r="B182" t="n">
         <v>97907</v>
@@ -23550,30 +23560,38 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 4, knärot 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>577448</v>
+        <v>577583</v>
       </c>
       <c r="R182" t="n">
-        <v>6558899</v>
+        <v>6559135</v>
       </c>
       <c r="S182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -23595,54 +23613,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>D-Kat-0636</t>
+        </is>
+      </c>
       <c r="Y182" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
+      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
+      </c>
+      <c r="AH182" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI182" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119603453</v>
+        <v>119602593</v>
       </c>
       <c r="B183" t="n">
-        <v>4772</v>
+        <v>94681</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -23655,42 +23683,41 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>102306</v>
+        <v>2180</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M183" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>577583</v>
+        <v>577389</v>
       </c>
       <c r="R183" t="n">
-        <v>6559135</v>
+        <v>6558904</v>
       </c>
       <c r="S183" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -23719,7 +23746,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -23729,7 +23756,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23744,22 +23771,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119600012</v>
+        <v>119603453</v>
       </c>
       <c r="B184" t="n">
-        <v>5169</v>
+        <v>4772</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -23772,43 +23799,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="L184" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>577548</v>
+        <v>577583</v>
       </c>
       <c r="R184" t="n">
-        <v>6559163</v>
+        <v>6559135</v>
       </c>
       <c r="S184" t="n">
         <v>4</v>
@@ -23840,7 +23863,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -23850,7 +23873,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -23870,17 +23893,17 @@
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119603451</v>
+        <v>119603442</v>
       </c>
       <c r="B185" t="n">
-        <v>94681</v>
+        <v>58138</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -23893,27 +23916,36 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2180</v>
+        <v>208245</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -23921,10 +23953,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>577601</v>
+        <v>577549</v>
       </c>
       <c r="R185" t="n">
-        <v>6559060</v>
+        <v>6558967</v>
       </c>
       <c r="S185" t="n">
         <v>4</v>
@@ -23956,7 +23988,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -23966,7 +23998,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -23993,10 +24025,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119601087</v>
+        <v>119612701</v>
       </c>
       <c r="B186" t="n">
-        <v>91228</v>
+        <v>97907</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -24009,48 +24041,57 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, knärot 300 m s, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>577575</v>
+        <v>577461</v>
       </c>
       <c r="R186" t="n">
-        <v>6558990</v>
+        <v>6559175</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24072,54 +24113,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>D-Kat-0634</t>
+        </is>
+      </c>
       <c r="Y186" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY186" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119599959</v>
+        <v>119612765</v>
       </c>
       <c r="B187" t="n">
-        <v>5189</v>
+        <v>97907</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -24128,54 +24179,61 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr"/>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N187" t="inlineStr"/>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen 2, knärot 350 m s, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>577484</v>
+        <v>577495</v>
       </c>
       <c r="R187" t="n">
-        <v>6559147</v>
+        <v>6559150</v>
       </c>
       <c r="S187" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -24197,51 +24255,61 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>D-kat-0633</t>
+        </is>
+      </c>
       <c r="Y187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB187" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
+      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
+      </c>
+      <c r="AH187" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI187" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY187" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119601987</v>
+        <v>119603451</v>
       </c>
       <c r="B188" t="n">
         <v>94681</v>
@@ -24275,27 +24343,23 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>577535</v>
+        <v>577601</v>
       </c>
       <c r="R188" t="n">
-        <v>6558941</v>
+        <v>6559060</v>
       </c>
       <c r="S188" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24324,7 +24388,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24334,7 +24398,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24349,22 +24413,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119602562</v>
+        <v>119600012</v>
       </c>
       <c r="B189" t="n">
-        <v>105009</v>
+        <v>5169</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -24377,49 +24441,46 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>577392</v>
+        <v>577548</v>
       </c>
       <c r="R189" t="n">
-        <v>6558906</v>
+        <v>6559163</v>
       </c>
       <c r="S189" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -24448,7 +24509,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -24458,7 +24519,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24473,19 +24534,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119601286</v>
+        <v>119602564</v>
       </c>
       <c r="B190" t="n">
         <v>97907</v>
@@ -24520,27 +24581,30 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577556</v>
+        <v>577409</v>
       </c>
       <c r="R190" t="n">
-        <v>6558966</v>
+        <v>6558923</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24569,7 +24633,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24579,7 +24643,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24590,28 +24654,23 @@
       </c>
       <c r="AG190" t="b">
         <v>0</v>
-      </c>
-      <c r="AH190" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119612701</v>
+        <v>119602380</v>
       </c>
       <c r="B191" t="n">
         <v>97907</v>
@@ -24646,38 +24705,30 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Strandmossen, knärot 300 m s, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577461</v>
+        <v>577448</v>
       </c>
       <c r="R191" t="n">
-        <v>6559175</v>
+        <v>6558899</v>
       </c>
       <c r="S191" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24699,64 +24750,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>D-Kat-0634</t>
-        </is>
-      </c>
       <c r="Y191" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB191" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AD191" t="b">
         <v>0</v>
       </c>
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
-      </c>
-      <c r="AH191" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI191" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY191" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119602000</v>
+        <v>119599395</v>
       </c>
       <c r="B192" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -24765,49 +24806,52 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>577523</v>
+        <v>577449</v>
       </c>
       <c r="R192" t="n">
-        <v>6558933</v>
+        <v>6559178</v>
       </c>
       <c r="S192" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24836,7 +24880,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -24846,7 +24890,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24861,22 +24905,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119601840</v>
+        <v>119602497</v>
       </c>
       <c r="B193" t="n">
-        <v>90057</v>
+        <v>105009</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24885,38 +24929,35 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2051</v>
+        <v>221144</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
@@ -24924,10 +24965,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577557</v>
+        <v>577411</v>
       </c>
       <c r="R193" t="n">
-        <v>6558949</v>
+        <v>6558925</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -24959,7 +25000,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -24969,7 +25010,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -24996,10 +25037,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119603442</v>
+        <v>119599959</v>
       </c>
       <c r="B194" t="n">
-        <v>58138</v>
+        <v>5189</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -25012,16 +25053,16 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -25039,20 +25080,20 @@
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>577549</v>
+        <v>577484</v>
       </c>
       <c r="R194" t="n">
-        <v>6558967</v>
+        <v>6559147</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -25084,7 +25125,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -25094,7 +25135,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25121,10 +25162,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119601607</v>
+        <v>119602836</v>
       </c>
       <c r="B195" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -25133,53 +25174,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>577578</v>
+        <v>577328</v>
       </c>
       <c r="R195" t="n">
-        <v>6558968</v>
+        <v>6558894</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -25208,7 +25241,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25218,7 +25251,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25245,7 +25278,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119601750</v>
+        <v>119602280</v>
       </c>
       <c r="B196" t="n">
         <v>97907</v>
@@ -25280,7 +25313,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -25288,22 +25321,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>577554</v>
+        <v>577412</v>
       </c>
       <c r="R196" t="n">
-        <v>6558959</v>
+        <v>6558928</v>
       </c>
       <c r="S196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25332,7 +25362,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25342,7 +25372,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25357,19 +25387,19 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119601023</v>
+        <v>119600170</v>
       </c>
       <c r="B197" t="n">
         <v>97907</v>
@@ -25404,7 +25434,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -25421,10 +25451,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>577571</v>
+        <v>577585</v>
       </c>
       <c r="R197" t="n">
-        <v>6558987</v>
+        <v>6559134</v>
       </c>
       <c r="S197" t="n">
         <v>4</v>
@@ -25456,7 +25486,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25466,7 +25496,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25481,19 +25511,19 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119612860</v>
+        <v>119601023</v>
       </c>
       <c r="B198" t="n">
         <v>97907</v>
@@ -25528,38 +25558,30 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Strandmossen 3, knärot 325 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>577550</v>
+        <v>577571</v>
       </c>
       <c r="R198" t="n">
-        <v>6559170</v>
+        <v>6558987</v>
       </c>
       <c r="S198" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25581,64 +25603,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>D-Kat-0635</t>
-        </is>
-      </c>
       <c r="Y198" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB198" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
-      </c>
-      <c r="AH198" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI198" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY198" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Jessica Loddby de Neergaard</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119603136</v>
+        <v>119600732</v>
       </c>
       <c r="B199" t="n">
-        <v>91832</v>
+        <v>94681</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -25647,48 +25659,53 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>577241</v>
+        <v>577625</v>
       </c>
       <c r="R199" t="n">
-        <v>6558978</v>
+        <v>6559039</v>
       </c>
       <c r="S199" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25717,7 +25734,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -25727,7 +25744,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25742,22 +25759,22 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119603450</v>
+        <v>119603136</v>
       </c>
       <c r="B200" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -25770,40 +25787,44 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>577315</v>
+        <v>577241</v>
       </c>
       <c r="R200" t="n">
-        <v>6558912</v>
+        <v>6558978</v>
       </c>
       <c r="S200" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25832,7 +25853,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -25842,7 +25863,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25857,19 +25878,19 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119602836</v>
+        <v>119599967</v>
       </c>
       <c r="B201" t="n">
         <v>94681</v>
@@ -25902,24 +25923,24 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>577328</v>
+        <v>577484</v>
       </c>
       <c r="R201" t="n">
-        <v>6558894</v>
+        <v>6559147</v>
       </c>
       <c r="S201" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25948,7 +25969,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -25958,7 +25979,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25973,22 +25994,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119612765</v>
+        <v>119599816</v>
       </c>
       <c r="B202" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -25997,61 +26018,52 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Strandmossen 2, knärot 350 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>577495</v>
+        <v>577555</v>
       </c>
       <c r="R202" t="n">
-        <v>6559150</v>
+        <v>6559157</v>
       </c>
       <c r="S202" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -26073,64 +26085,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>D-kat-0633</t>
-        </is>
-      </c>
       <c r="Y202" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
-      </c>
-      <c r="AH202" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI202" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY202" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119602593</v>
+        <v>119601286</v>
       </c>
       <c r="B203" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -26139,45 +26141,50 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>577389</v>
+        <v>577556</v>
       </c>
       <c r="R203" t="n">
-        <v>6558904</v>
+        <v>6558966</v>
       </c>
       <c r="S203" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -26206,7 +26213,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -26216,7 +26223,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -26227,26 +26234,31 @@
       </c>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119601728</v>
+        <v>119603450</v>
       </c>
       <c r="B204" t="n">
-        <v>90334</v>
+        <v>91884</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -26255,52 +26267,44 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3215</v>
+        <v>5449</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>577557</v>
+        <v>577315</v>
       </c>
       <c r="R204" t="n">
-        <v>6558969</v>
+        <v>6558912</v>
       </c>
       <c r="S204" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -26329,7 +26333,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26339,7 +26343,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26354,22 +26358,22 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119601454</v>
+        <v>119602448</v>
       </c>
       <c r="B205" t="n">
-        <v>91883</v>
+        <v>94681</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -26378,49 +26382,46 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>5448</v>
+        <v>2180</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>577558</v>
+        <v>577444</v>
       </c>
       <c r="R205" t="n">
-        <v>6558970</v>
+        <v>6558882</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -26452,7 +26453,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26462,7 +26463,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26489,10 +26490,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119603201</v>
+        <v>119600824</v>
       </c>
       <c r="B206" t="n">
-        <v>97907</v>
+        <v>58166</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26501,50 +26502,54 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>577223</v>
+        <v>577588</v>
       </c>
       <c r="R206" t="n">
-        <v>6558959</v>
+        <v>6559049</v>
       </c>
       <c r="S206" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26573,7 +26578,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26583,7 +26588,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26594,31 +26599,26 @@
       </c>
       <c r="AG206" t="b">
         <v>0</v>
-      </c>
-      <c r="AH206" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119699345</v>
+        <v>119698812</v>
       </c>
       <c r="B207" t="n">
-        <v>91858</v>
+        <v>5169</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26627,41 +26627,46 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4368</v>
+        <v>100526</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>577474</v>
+        <v>577415</v>
       </c>
       <c r="R207" t="n">
-        <v>6559036</v>
+        <v>6559187</v>
       </c>
       <c r="S207" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26717,10 +26722,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119699553</v>
+        <v>119701628</v>
       </c>
       <c r="B208" t="n">
-        <v>91842</v>
+        <v>97907</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26729,38 +26734,38 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>577460</v>
+        <v>577186</v>
       </c>
       <c r="R208" t="n">
-        <v>6559048</v>
+        <v>6558951</v>
       </c>
       <c r="S208" t="n">
         <v>15</v>
@@ -26819,10 +26824,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119701851</v>
+        <v>119702381</v>
       </c>
       <c r="B209" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26831,38 +26836,38 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577273</v>
+        <v>577292</v>
       </c>
       <c r="R209" t="n">
-        <v>6559028</v>
+        <v>6559106</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26921,10 +26926,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119698814</v>
+        <v>119701751</v>
       </c>
       <c r="B210" t="n">
-        <v>5189</v>
+        <v>97907</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26933,46 +26938,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577415</v>
+        <v>577203</v>
       </c>
       <c r="R210" t="n">
-        <v>6559187</v>
+        <v>6558998</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27028,10 +27028,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119701601</v>
+        <v>119699969</v>
       </c>
       <c r="B211" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27040,38 +27040,38 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577176</v>
+        <v>577561</v>
       </c>
       <c r="R211" t="n">
-        <v>6558914</v>
+        <v>6558994</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -27130,10 +27130,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119699976</v>
+        <v>119701745</v>
       </c>
       <c r="B212" t="n">
-        <v>57463</v>
+        <v>91185</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -27142,47 +27142,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>103021</v>
+        <v>6031</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>577561</v>
+        <v>577203</v>
       </c>
       <c r="R212" t="n">
-        <v>6558994</v>
+        <v>6558998</v>
       </c>
       <c r="S212" t="n">
         <v>15</v>
@@ -27212,19 +27203,9 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>12:04</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27251,10 +27232,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119702381</v>
+        <v>119698814</v>
       </c>
       <c r="B213" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -27263,41 +27244,46 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>577292</v>
+        <v>577415</v>
       </c>
       <c r="R213" t="n">
-        <v>6559106</v>
+        <v>6559187</v>
       </c>
       <c r="S213" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27353,10 +27339,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119701705</v>
+        <v>119699976</v>
       </c>
       <c r="B214" t="n">
-        <v>91840</v>
+        <v>57463</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27365,38 +27351,47 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>577203</v>
+        <v>577561</v>
       </c>
       <c r="R214" t="n">
-        <v>6558998</v>
+        <v>6558994</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -27426,9 +27421,19 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -27455,7 +27460,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119702969</v>
+        <v>119701601</v>
       </c>
       <c r="B215" t="n">
         <v>97907</v>
@@ -27491,14 +27496,14 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>577658</v>
+        <v>577176</v>
       </c>
       <c r="R215" t="n">
-        <v>6558983</v>
+        <v>6558914</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -27557,10 +27562,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119701751</v>
+        <v>119699263</v>
       </c>
       <c r="B216" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27569,38 +27574,41 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>577203</v>
+        <v>577415</v>
       </c>
       <c r="R216" t="n">
-        <v>6558998</v>
+        <v>6559051</v>
       </c>
       <c r="S216" t="n">
         <v>15</v>
@@ -27641,6 +27649,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -27659,10 +27668,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119699969</v>
+        <v>119699541</v>
       </c>
       <c r="B217" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27671,25 +27680,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -27699,10 +27708,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577561</v>
+        <v>577460</v>
       </c>
       <c r="R217" t="n">
-        <v>6558994</v>
+        <v>6559048</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27761,10 +27770,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119699197</v>
+        <v>119701851</v>
       </c>
       <c r="B218" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27773,38 +27782,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577394</v>
+        <v>577273</v>
       </c>
       <c r="R218" t="n">
-        <v>6559096</v>
+        <v>6559028</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27863,10 +27872,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119701745</v>
+        <v>119699664</v>
       </c>
       <c r="B219" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27875,38 +27884,38 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577203</v>
+        <v>577505</v>
       </c>
       <c r="R219" t="n">
-        <v>6558998</v>
+        <v>6559057</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -27939,6 +27948,11 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -28067,7 +28081,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701628</v>
+        <v>119701512</v>
       </c>
       <c r="B221" t="n">
         <v>97907</v>
@@ -28107,10 +28121,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577186</v>
+        <v>577206</v>
       </c>
       <c r="R221" t="n">
-        <v>6558951</v>
+        <v>6558900</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28169,10 +28183,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119703722</v>
+        <v>119701705</v>
       </c>
       <c r="B222" t="n">
-        <v>91863</v>
+        <v>91840</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -28181,38 +28195,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577493</v>
+        <v>577203</v>
       </c>
       <c r="R222" t="n">
-        <v>6559186</v>
+        <v>6558998</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28271,10 +28285,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119698812</v>
+        <v>119703722</v>
       </c>
       <c r="B223" t="n">
-        <v>5169</v>
+        <v>91863</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28283,46 +28297,41 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577415</v>
+        <v>577493</v>
       </c>
       <c r="R223" t="n">
-        <v>6559187</v>
+        <v>6559186</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -28378,10 +28387,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119699664</v>
+        <v>119699345</v>
       </c>
       <c r="B224" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28390,25 +28399,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -28418,13 +28427,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>577505</v>
+        <v>577474</v>
       </c>
       <c r="R224" t="n">
-        <v>6559057</v>
+        <v>6559036</v>
       </c>
       <c r="S224" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -28454,11 +28463,6 @@
       <c r="AA224" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -28485,7 +28489,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119699541</v>
+        <v>119700995</v>
       </c>
       <c r="B225" t="n">
         <v>91832</v>
@@ -28521,14 +28525,14 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>577460</v>
+        <v>577330</v>
       </c>
       <c r="R225" t="n">
-        <v>6559048</v>
+        <v>6558852</v>
       </c>
       <c r="S225" t="n">
         <v>15</v>
@@ -28587,10 +28591,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119699263</v>
+        <v>119699553</v>
       </c>
       <c r="B226" t="n">
-        <v>91858</v>
+        <v>91842</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28603,37 +28607,34 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4368</v>
+        <v>788</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="J226" t="inlineStr"/>
-      <c r="K226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>577415</v>
+        <v>577460</v>
       </c>
       <c r="R226" t="n">
-        <v>6559051</v>
+        <v>6559048</v>
       </c>
       <c r="S226" t="n">
         <v>15</v>
@@ -28674,7 +28675,6 @@
       <c r="AE226" t="b">
         <v>0</v>
       </c>
-      <c r="AF226" t="inlineStr"/>
       <c r="AG226" t="b">
         <v>0</v>
       </c>
@@ -28693,10 +28693,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119701512</v>
+        <v>119699339</v>
       </c>
       <c r="B227" t="n">
-        <v>97907</v>
+        <v>57326</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -28705,41 +28705,50 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>577206</v>
+        <v>577474</v>
       </c>
       <c r="R227" t="n">
-        <v>6558900</v>
+        <v>6559036</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -28766,9 +28775,19 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -28795,10 +28814,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119699339</v>
+        <v>119699197</v>
       </c>
       <c r="B228" t="n">
-        <v>57326</v>
+        <v>91858</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28811,46 +28830,37 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>100049</v>
+        <v>4368</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>577474</v>
+        <v>577394</v>
       </c>
       <c r="R228" t="n">
-        <v>6559036</v>
+        <v>6559096</v>
       </c>
       <c r="S228" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -28877,19 +28887,9 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -28916,10 +28916,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119700995</v>
+        <v>119702969</v>
       </c>
       <c r="B229" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28928,38 +28928,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>577330</v>
+        <v>577658</v>
       </c>
       <c r="R229" t="n">
-        <v>6558852</v>
+        <v>6558983</v>
       </c>
       <c r="S229" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -23155,10 +23155,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119601750</v>
+        <v>119601840</v>
       </c>
       <c r="B179" t="n">
-        <v>97907</v>
+        <v>90057</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -23171,49 +23171,48 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>577554</v>
+        <v>577557</v>
       </c>
       <c r="R179" t="n">
-        <v>6558959</v>
+        <v>6558949</v>
       </c>
       <c r="S179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -23242,7 +23241,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23252,7 +23251,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23279,10 +23278,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119601840</v>
+        <v>119601750</v>
       </c>
       <c r="B180" t="n">
-        <v>90057</v>
+        <v>97907</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -23295,48 +23294,49 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>577557</v>
+        <v>577554</v>
       </c>
       <c r="R180" t="n">
-        <v>6558949</v>
+        <v>6558959</v>
       </c>
       <c r="S180" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -23375,7 +23375,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -24425,10 +24425,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119600012</v>
+        <v>119602564</v>
       </c>
       <c r="B189" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -24437,47 +24437,50 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr"/>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>577548</v>
+        <v>577409</v>
       </c>
       <c r="R189" t="n">
-        <v>6559163</v>
+        <v>6558923</v>
       </c>
       <c r="S189" t="n">
         <v>4</v>
@@ -24509,7 +24512,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -24519,7 +24522,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24534,19 +24537,19 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119602564</v>
+        <v>119602380</v>
       </c>
       <c r="B190" t="n">
         <v>97907</v>
@@ -24581,7 +24584,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -24598,10 +24601,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577409</v>
+        <v>577448</v>
       </c>
       <c r="R190" t="n">
-        <v>6558923</v>
+        <v>6558899</v>
       </c>
       <c r="S190" t="n">
         <v>4</v>
@@ -24633,7 +24636,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24643,7 +24646,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24670,10 +24673,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119602380</v>
+        <v>119600012</v>
       </c>
       <c r="B191" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -24682,50 +24685,47 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577448</v>
+        <v>577548</v>
       </c>
       <c r="R191" t="n">
-        <v>6558899</v>
+        <v>6559163</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -24757,7 +24757,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24782,12 +24782,12 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
@@ -24917,10 +24917,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119602497</v>
+        <v>119599959</v>
       </c>
       <c r="B193" t="n">
-        <v>105009</v>
+        <v>5189</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24933,42 +24933,47 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221144</v>
+        <v>105930</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577411</v>
+        <v>577484</v>
       </c>
       <c r="R193" t="n">
-        <v>6558925</v>
+        <v>6559147</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -25000,7 +25005,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -25010,7 +25015,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25025,22 +25030,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119599959</v>
+        <v>119602497</v>
       </c>
       <c r="B194" t="n">
-        <v>5189</v>
+        <v>105009</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -25053,47 +25058,42 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>105930</v>
+        <v>221144</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>577484</v>
+        <v>577411</v>
       </c>
       <c r="R194" t="n">
-        <v>6559147</v>
+        <v>6558925</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -25125,7 +25125,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25150,12 +25150,12 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
@@ -25890,10 +25890,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119599967</v>
+        <v>119601286</v>
       </c>
       <c r="B201" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25902,45 +25902,50 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>577484</v>
+        <v>577556</v>
       </c>
       <c r="R201" t="n">
-        <v>6559147</v>
+        <v>6558966</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25969,7 +25974,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -25979,7 +25984,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25990,26 +25995,31 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
+      </c>
+      <c r="AH201" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119599816</v>
+        <v>119599967</v>
       </c>
       <c r="B202" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -26018,49 +26028,42 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>577555</v>
+        <v>577484</v>
       </c>
       <c r="R202" t="n">
-        <v>6559157</v>
+        <v>6559147</v>
       </c>
       <c r="S202" t="n">
         <v>4</v>
@@ -26092,7 +26095,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26102,7 +26105,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26117,22 +26120,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119601286</v>
+        <v>119599816</v>
       </c>
       <c r="B203" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -26141,50 +26144,52 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>577556</v>
+        <v>577555</v>
       </c>
       <c r="R203" t="n">
-        <v>6558966</v>
+        <v>6559157</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -26213,7 +26218,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -26223,7 +26228,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -26234,21 +26239,16 @@
       </c>
       <c r="AG203" t="b">
         <v>0</v>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
@@ -27872,7 +27872,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119699664</v>
+        <v>119699201</v>
       </c>
       <c r="B219" t="n">
         <v>97907</v>
@@ -27912,10 +27912,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577505</v>
+        <v>577394</v>
       </c>
       <c r="R219" t="n">
-        <v>6559057</v>
+        <v>6559096</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -27948,11 +27948,6 @@
       <c r="AA219" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -27979,7 +27974,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119699201</v>
+        <v>119699664</v>
       </c>
       <c r="B220" t="n">
         <v>97907</v>
@@ -28019,10 +28014,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577394</v>
+        <v>577505</v>
       </c>
       <c r="R220" t="n">
-        <v>6559096</v>
+        <v>6559057</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -28055,6 +28050,11 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -28814,10 +28814,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119699197</v>
+        <v>119702969</v>
       </c>
       <c r="B228" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28826,25 +28826,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -28854,10 +28854,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>577394</v>
+        <v>577658</v>
       </c>
       <c r="R228" t="n">
-        <v>6559096</v>
+        <v>6558983</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -28916,10 +28916,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119702969</v>
+        <v>119699197</v>
       </c>
       <c r="B229" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28928,25 +28928,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -28956,10 +28956,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>577658</v>
+        <v>577394</v>
       </c>
       <c r="R229" t="n">
-        <v>6558983</v>
+        <v>6559096</v>
       </c>
       <c r="S229" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -21178,10 +21178,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119601987</v>
+        <v>119600824</v>
       </c>
       <c r="B163" t="n">
-        <v>94681</v>
+        <v>58166</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -21194,45 +21194,50 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2180</v>
+        <v>208249</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>577535</v>
+        <v>577588</v>
       </c>
       <c r="R163" t="n">
-        <v>6558941</v>
+        <v>6559049</v>
       </c>
       <c r="S163" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -21261,7 +21266,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -21271,7 +21276,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -21286,22 +21291,22 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119601316</v>
+        <v>119612900</v>
       </c>
       <c r="B164" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -21310,57 +21315,61 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen 4, knärot 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>577573</v>
+        <v>577583</v>
       </c>
       <c r="R164" t="n">
-        <v>6558989</v>
+        <v>6559135</v>
       </c>
       <c r="S164" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -21382,54 +21391,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>D-Kat-0636</t>
+        </is>
+      </c>
       <c r="Y164" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119602671</v>
+        <v>119600732</v>
       </c>
       <c r="B165" t="n">
-        <v>91832</v>
+        <v>94681</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21438,45 +21457,50 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4361</v>
+        <v>2180</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>577392</v>
+        <v>577625</v>
       </c>
       <c r="R165" t="n">
-        <v>6558896</v>
+        <v>6559039</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -21508,7 +21532,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -21518,7 +21542,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -21545,10 +21569,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119603201</v>
+        <v>119601454</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -21557,50 +21581,52 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>577223</v>
+        <v>577558</v>
       </c>
       <c r="R166" t="n">
-        <v>6558959</v>
+        <v>6558970</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21629,7 +21655,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -21639,7 +21665,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -21650,31 +21676,26 @@
       </c>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119599963</v>
+        <v>119602671</v>
       </c>
       <c r="B167" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -21683,49 +21704,48 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>577548</v>
+        <v>577392</v>
       </c>
       <c r="R167" t="n">
-        <v>6559163</v>
+        <v>6558896</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -21754,7 +21774,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -21764,7 +21784,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -21779,22 +21799,22 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119601728</v>
+        <v>119599395</v>
       </c>
       <c r="B168" t="n">
-        <v>90334</v>
+        <v>90582</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -21803,25 +21823,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3215</v>
+        <v>5442</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -21838,17 +21858,17 @@
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>577557</v>
+        <v>577449</v>
       </c>
       <c r="R168" t="n">
-        <v>6558969</v>
+        <v>6559178</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21877,7 +21897,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -21887,7 +21907,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -21902,22 +21922,22 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119602562</v>
+        <v>119602280</v>
       </c>
       <c r="B169" t="n">
-        <v>105009</v>
+        <v>97907</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -21926,30 +21946,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -21957,22 +21977,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>577392</v>
+        <v>577412</v>
       </c>
       <c r="R169" t="n">
-        <v>6558906</v>
+        <v>6558928</v>
       </c>
       <c r="S169" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -22001,7 +22018,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -22011,7 +22028,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -22026,22 +22043,22 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119601087</v>
+        <v>119601750</v>
       </c>
       <c r="B170" t="n">
-        <v>91228</v>
+        <v>97907</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -22054,34 +22071,35 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
@@ -22089,13 +22107,13 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>577575</v>
+        <v>577554</v>
       </c>
       <c r="R170" t="n">
-        <v>6558990</v>
+        <v>6558959</v>
       </c>
       <c r="S170" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -22124,7 +22142,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -22134,7 +22152,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22161,10 +22179,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119603449</v>
+        <v>119599959</v>
       </c>
       <c r="B171" t="n">
-        <v>79144</v>
+        <v>5189</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -22173,45 +22191,51 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>577598</v>
+        <v>577484</v>
       </c>
       <c r="R171" t="n">
-        <v>6559069</v>
+        <v>6559147</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -22243,7 +22267,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -22253,7 +22277,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22280,10 +22304,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119599396</v>
+        <v>119600012</v>
       </c>
       <c r="B172" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -22292,35 +22316,36 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
@@ -22328,10 +22353,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>577460</v>
+        <v>577548</v>
       </c>
       <c r="R172" t="n">
-        <v>6559174</v>
+        <v>6559163</v>
       </c>
       <c r="S172" t="n">
         <v>4</v>
@@ -22363,7 +22388,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -22373,7 +22398,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -22393,17 +22418,17 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119599958</v>
+        <v>119601840</v>
       </c>
       <c r="B173" t="n">
-        <v>5169</v>
+        <v>90057</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -22412,51 +22437,49 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100526</v>
+        <v>2051</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>577484</v>
+        <v>577557</v>
       </c>
       <c r="R173" t="n">
-        <v>6559147</v>
+        <v>6558949</v>
       </c>
       <c r="S173" t="n">
         <v>4</v>
@@ -22488,7 +22511,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -22498,7 +22521,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -22513,22 +22536,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119602000</v>
+        <v>119599816</v>
       </c>
       <c r="B174" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -22537,46 +22560,49 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>577523</v>
+        <v>577555</v>
       </c>
       <c r="R174" t="n">
-        <v>6558933</v>
+        <v>6559157</v>
       </c>
       <c r="S174" t="n">
         <v>4</v>
@@ -22608,7 +22634,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -22618,7 +22644,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -22645,10 +22671,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119602238</v>
+        <v>119612765</v>
       </c>
       <c r="B175" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -22657,52 +22683,61 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 2, knärot 350 m s, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>577459</v>
+        <v>577495</v>
       </c>
       <c r="R175" t="n">
-        <v>6558921</v>
+        <v>6559150</v>
       </c>
       <c r="S175" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -22724,54 +22759,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>D-kat-0633</t>
+        </is>
+      </c>
       <c r="Y175" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
+      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119612860</v>
+        <v>119602497</v>
       </c>
       <c r="B176" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -22780,61 +22825,49 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Strandmossen 3, knärot 325 m s, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>577550</v>
+        <v>577411</v>
       </c>
       <c r="R176" t="n">
-        <v>6559170</v>
+        <v>6558925</v>
       </c>
       <c r="S176" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -22856,64 +22889,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X176" t="inlineStr">
-        <is>
-          <t>D-Kat-0635</t>
-        </is>
-      </c>
       <c r="Y176" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AD176" t="b">
         <v>0</v>
       </c>
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
-      </c>
-      <c r="AH176" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI176" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119601607</v>
+        <v>119601087</v>
       </c>
       <c r="B177" t="n">
-        <v>97907</v>
+        <v>91228</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -22926,35 +22949,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
@@ -22962,13 +22984,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>577578</v>
+        <v>577575</v>
       </c>
       <c r="R177" t="n">
-        <v>6558968</v>
+        <v>6558990</v>
       </c>
       <c r="S177" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -22997,7 +23019,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -23007,7 +23029,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23022,22 +23044,22 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119599599</v>
+        <v>119602238</v>
       </c>
       <c r="B178" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -23046,25 +23068,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -23077,19 +23099,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>577474</v>
+        <v>577459</v>
       </c>
       <c r="R178" t="n">
-        <v>6559269</v>
+        <v>6558921</v>
       </c>
       <c r="S178" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -23118,7 +23142,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -23128,7 +23152,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23143,22 +23167,22 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119601840</v>
+        <v>119600170</v>
       </c>
       <c r="B179" t="n">
-        <v>90057</v>
+        <v>97907</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -23171,45 +23195,46 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>577557</v>
+        <v>577585</v>
       </c>
       <c r="R179" t="n">
-        <v>6558949</v>
+        <v>6559134</v>
       </c>
       <c r="S179" t="n">
         <v>4</v>
@@ -23241,7 +23266,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23251,7 +23276,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23278,7 +23303,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119601750</v>
+        <v>119603201</v>
       </c>
       <c r="B180" t="n">
         <v>97907</v>
@@ -23313,30 +23338,27 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>577554</v>
+        <v>577223</v>
       </c>
       <c r="R180" t="n">
         <v>6558959</v>
       </c>
       <c r="S180" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -23365,7 +23387,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -23375,7 +23397,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23386,26 +23408,31 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119601454</v>
+        <v>119603450</v>
       </c>
       <c r="B181" t="n">
-        <v>91883</v>
+        <v>91884</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -23418,45 +23445,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>577558</v>
+        <v>577315</v>
       </c>
       <c r="R181" t="n">
-        <v>6558970</v>
+        <v>6558912</v>
       </c>
       <c r="S181" t="n">
         <v>4</v>
@@ -23488,7 +23507,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23498,7 +23517,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23513,22 +23532,22 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119612900</v>
+        <v>119599958</v>
       </c>
       <c r="B182" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -23537,61 +23556,54 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Strandmossen 4, knärot 360 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>577583</v>
+        <v>577484</v>
       </c>
       <c r="R182" t="n">
-        <v>6559135</v>
+        <v>6559147</v>
       </c>
       <c r="S182" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -23613,64 +23625,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>D-Kat-0636</t>
-        </is>
-      </c>
       <c r="Y182" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AD182" t="b">
         <v>0</v>
       </c>
       <c r="AE182" t="b">
         <v>0</v>
       </c>
-      <c r="AF182" t="inlineStr"/>
       <c r="AG182" t="b">
         <v>0</v>
-      </c>
-      <c r="AH182" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI182" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119602593</v>
+        <v>119603442</v>
       </c>
       <c r="B183" t="n">
-        <v>94681</v>
+        <v>58138</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -23683,41 +23685,50 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>2180</v>
+        <v>208245</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>577389</v>
+        <v>577549</v>
       </c>
       <c r="R183" t="n">
-        <v>6558904</v>
+        <v>6558967</v>
       </c>
       <c r="S183" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -23746,7 +23757,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -23756,7 +23767,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -23771,22 +23782,22 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119603453</v>
+        <v>119602564</v>
       </c>
       <c r="B184" t="n">
-        <v>4772</v>
+        <v>97907</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -23795,43 +23806,50 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr"/>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>577583</v>
+        <v>577409</v>
       </c>
       <c r="R184" t="n">
-        <v>6559135</v>
+        <v>6558923</v>
       </c>
       <c r="S184" t="n">
         <v>4</v>
@@ -23863,7 +23881,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -23873,7 +23891,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -23888,22 +23906,22 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119603442</v>
+        <v>119602448</v>
       </c>
       <c r="B185" t="n">
-        <v>58138</v>
+        <v>94681</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -23916,47 +23934,42 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>208245</v>
+        <v>2180</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>577549</v>
+        <v>577444</v>
       </c>
       <c r="R185" t="n">
-        <v>6558967</v>
+        <v>6558882</v>
       </c>
       <c r="S185" t="n">
         <v>4</v>
@@ -23988,7 +24001,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -23998,7 +24011,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24013,22 +24026,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119612701</v>
+        <v>119603449</v>
       </c>
       <c r="B186" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -24037,61 +24050,48 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Strandmossen, knärot 300 m s, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>577461</v>
+        <v>577598</v>
       </c>
       <c r="R186" t="n">
-        <v>6559175</v>
+        <v>6559069</v>
       </c>
       <c r="S186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24113,61 +24113,51 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>D-Kat-0634</t>
-        </is>
-      </c>
       <c r="Y186" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
-      </c>
-      <c r="AH186" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI186" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY186" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119612765</v>
+        <v>119612701</v>
       </c>
       <c r="B187" t="n">
         <v>97907</v>
@@ -24202,7 +24192,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -24223,17 +24213,17 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Strandmossen 2, knärot 350 m s, Srm</t>
+          <t>Strandmossen, knärot 300 m s, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>577495</v>
+        <v>577461</v>
       </c>
       <c r="R187" t="n">
-        <v>6559150</v>
+        <v>6559175</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -24257,7 +24247,7 @@
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>D-kat-0633</t>
+          <t>D-Kat-0634</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -24287,7 +24277,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr"/>
@@ -24298,7 +24288,7 @@
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -24309,10 +24299,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119603451</v>
+        <v>119601023</v>
       </c>
       <c r="B188" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -24321,42 +24311,50 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>577601</v>
+        <v>577571</v>
       </c>
       <c r="R188" t="n">
-        <v>6559060</v>
+        <v>6558987</v>
       </c>
       <c r="S188" t="n">
         <v>4</v>
@@ -24388,7 +24386,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24398,7 +24396,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24413,22 +24411,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119602564</v>
+        <v>119602000</v>
       </c>
       <c r="B189" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -24437,37 +24435,33 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
@@ -24477,10 +24471,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>577409</v>
+        <v>577523</v>
       </c>
       <c r="R189" t="n">
-        <v>6558923</v>
+        <v>6558933</v>
       </c>
       <c r="S189" t="n">
         <v>4</v>
@@ -24512,7 +24506,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -24522,7 +24516,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24549,10 +24543,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119602380</v>
+        <v>119601728</v>
       </c>
       <c r="B190" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -24561,53 +24555,52 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577448</v>
+        <v>577557</v>
       </c>
       <c r="R190" t="n">
-        <v>6558899</v>
+        <v>6558969</v>
       </c>
       <c r="S190" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24636,7 +24629,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24646,7 +24639,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24661,22 +24654,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119600012</v>
+        <v>119602836</v>
       </c>
       <c r="B191" t="n">
-        <v>5169</v>
+        <v>94681</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -24689,46 +24682,41 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577548</v>
+        <v>577328</v>
       </c>
       <c r="R191" t="n">
-        <v>6559163</v>
+        <v>6558894</v>
       </c>
       <c r="S191" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24757,7 +24745,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -24767,7 +24755,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24782,22 +24770,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119599395</v>
+        <v>119601987</v>
       </c>
       <c r="B192" t="n">
-        <v>90582</v>
+        <v>94681</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -24806,52 +24794,49 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>577449</v>
+        <v>577535</v>
       </c>
       <c r="R192" t="n">
-        <v>6559178</v>
+        <v>6558941</v>
       </c>
       <c r="S192" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24880,7 +24865,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -24890,7 +24875,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -24905,22 +24890,22 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119599959</v>
+        <v>119601316</v>
       </c>
       <c r="B193" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24929,20 +24914,20 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -24955,12 +24940,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N193" t="inlineStr"/>
@@ -24970,10 +24958,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577484</v>
+        <v>577573</v>
       </c>
       <c r="R193" t="n">
-        <v>6559147</v>
+        <v>6558989</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -25005,7 +24993,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -25015,7 +25003,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25030,22 +25018,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119602497</v>
+        <v>119603452</v>
       </c>
       <c r="B194" t="n">
-        <v>105009</v>
+        <v>94681</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -25058,42 +25046,38 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>577411</v>
+        <v>577601</v>
       </c>
       <c r="R194" t="n">
-        <v>6558925</v>
+        <v>6559060</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -25125,7 +25109,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -25135,7 +25119,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25150,22 +25134,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119602836</v>
+        <v>119599963</v>
       </c>
       <c r="B195" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -25174,45 +25158,49 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>577328</v>
+        <v>577548</v>
       </c>
       <c r="R195" t="n">
-        <v>6558894</v>
+        <v>6559163</v>
       </c>
       <c r="S195" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -25241,7 +25229,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25251,7 +25239,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25266,22 +25254,22 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119602280</v>
+        <v>119599599</v>
       </c>
       <c r="B196" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -25290,47 +25278,47 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>577412</v>
+        <v>577474</v>
       </c>
       <c r="R196" t="n">
-        <v>6558928</v>
+        <v>6559269</v>
       </c>
       <c r="S196" t="n">
         <v>1</v>
@@ -25362,7 +25350,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25372,7 +25360,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25399,7 +25387,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119600170</v>
+        <v>119599396</v>
       </c>
       <c r="B197" t="n">
         <v>97907</v>
@@ -25434,27 +25422,23 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>577585</v>
+        <v>577460</v>
       </c>
       <c r="R197" t="n">
-        <v>6559134</v>
+        <v>6559174</v>
       </c>
       <c r="S197" t="n">
         <v>4</v>
@@ -25486,7 +25470,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25496,7 +25480,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25511,22 +25495,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119601023</v>
+        <v>119602562</v>
       </c>
       <c r="B198" t="n">
-        <v>97907</v>
+        <v>105009</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -25535,30 +25519,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -25571,17 +25555,17 @@
       <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>577571</v>
+        <v>577392</v>
       </c>
       <c r="R198" t="n">
-        <v>6558987</v>
+        <v>6558906</v>
       </c>
       <c r="S198" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25610,7 +25594,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25620,7 +25604,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25647,10 +25631,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119600732</v>
+        <v>119602380</v>
       </c>
       <c r="B199" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -25659,35 +25643,35 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -25695,14 +25679,14 @@
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>577625</v>
+        <v>577448</v>
       </c>
       <c r="R199" t="n">
-        <v>6559039</v>
+        <v>6558899</v>
       </c>
       <c r="S199" t="n">
         <v>4</v>
@@ -25734,7 +25718,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -25744,7 +25728,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25771,10 +25755,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119603136</v>
+        <v>119601607</v>
       </c>
       <c r="B200" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -25783,25 +25767,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -25809,19 +25793,24 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>577241</v>
+        <v>577578</v>
       </c>
       <c r="R200" t="n">
-        <v>6558978</v>
+        <v>6558968</v>
       </c>
       <c r="S200" t="n">
         <v>6</v>
@@ -25853,7 +25842,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -25863,7 +25852,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25890,10 +25879,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119601286</v>
+        <v>119602593</v>
       </c>
       <c r="B201" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25902,50 +25891,45 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>577556</v>
+        <v>577389</v>
       </c>
       <c r="R201" t="n">
-        <v>6558966</v>
+        <v>6558904</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25974,7 +25958,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -25984,7 +25968,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25995,31 +25979,26 @@
       </c>
       <c r="AG201" t="b">
         <v>0</v>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119599967</v>
+        <v>119603136</v>
       </c>
       <c r="B202" t="n">
-        <v>94681</v>
+        <v>91832</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -26028,45 +26007,48 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>577484</v>
+        <v>577241</v>
       </c>
       <c r="R202" t="n">
-        <v>6559147</v>
+        <v>6558978</v>
       </c>
       <c r="S202" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -26095,7 +26077,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26105,7 +26087,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26120,22 +26102,22 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119599816</v>
+        <v>119612860</v>
       </c>
       <c r="B203" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -26144,52 +26126,61 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen 3, knärot 325 m s, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>577555</v>
+        <v>577550</v>
       </c>
       <c r="R203" t="n">
-        <v>6559157</v>
+        <v>6559170</v>
       </c>
       <c r="S203" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -26211,54 +26202,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>D-Kat-0635</t>
+        </is>
+      </c>
       <c r="Y203" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY203" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119603450</v>
+        <v>119601286</v>
       </c>
       <c r="B204" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -26267,44 +26268,50 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>577315</v>
+        <v>577556</v>
       </c>
       <c r="R204" t="n">
-        <v>6558912</v>
+        <v>6558966</v>
       </c>
       <c r="S204" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -26333,7 +26340,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26343,7 +26350,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26354,23 +26361,28 @@
       </c>
       <c r="AG204" t="b">
         <v>0</v>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119602448</v>
+        <v>119599967</v>
       </c>
       <c r="B205" t="n">
         <v>94681</v>
@@ -26408,20 +26420,16 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>577444</v>
+        <v>577484</v>
       </c>
       <c r="R205" t="n">
-        <v>6558882</v>
+        <v>6559147</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -26453,7 +26461,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26463,7 +26471,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26478,22 +26486,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119600824</v>
+        <v>119603453</v>
       </c>
       <c r="B206" t="n">
-        <v>58166</v>
+        <v>4772</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26506,47 +26514,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>208249</v>
+        <v>102306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>577588</v>
+        <v>577583</v>
       </c>
       <c r="R206" t="n">
-        <v>6559049</v>
+        <v>6559135</v>
       </c>
       <c r="S206" t="n">
         <v>4</v>
@@ -26578,7 +26578,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26603,22 +26603,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119698812</v>
+        <v>119699339</v>
       </c>
       <c r="B207" t="n">
-        <v>5169</v>
+        <v>57326</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26627,31 +26627,35 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -26660,13 +26664,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>577415</v>
+        <v>577474</v>
       </c>
       <c r="R207" t="n">
-        <v>6559187</v>
+        <v>6559036</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26693,9 +26697,19 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB207" t="inlineStr">
+        <is>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26722,10 +26736,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119701628</v>
+        <v>119698812</v>
       </c>
       <c r="B208" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26734,41 +26748,46 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>577186</v>
+        <v>577415</v>
       </c>
       <c r="R208" t="n">
-        <v>6558951</v>
+        <v>6559187</v>
       </c>
       <c r="S208" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26824,10 +26843,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119702381</v>
+        <v>119699541</v>
       </c>
       <c r="B209" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26836,25 +26855,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26864,10 +26883,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577292</v>
+        <v>577460</v>
       </c>
       <c r="R209" t="n">
-        <v>6559106</v>
+        <v>6559048</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26926,10 +26945,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119701751</v>
+        <v>119701851</v>
       </c>
       <c r="B210" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26938,25 +26957,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -26966,10 +26985,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577203</v>
+        <v>577273</v>
       </c>
       <c r="R210" t="n">
-        <v>6558998</v>
+        <v>6559028</v>
       </c>
       <c r="S210" t="n">
         <v>15</v>
@@ -27028,10 +27047,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119699969</v>
+        <v>119702969</v>
       </c>
       <c r="B211" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27040,25 +27059,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -27068,10 +27087,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577561</v>
+        <v>577658</v>
       </c>
       <c r="R211" t="n">
-        <v>6558994</v>
+        <v>6558983</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -27130,10 +27149,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119701745</v>
+        <v>119699664</v>
       </c>
       <c r="B212" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -27142,38 +27161,38 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>577203</v>
+        <v>577505</v>
       </c>
       <c r="R212" t="n">
-        <v>6558998</v>
+        <v>6559057</v>
       </c>
       <c r="S212" t="n">
         <v>15</v>
@@ -27206,6 +27225,11 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -27232,10 +27256,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119698814</v>
+        <v>119699553</v>
       </c>
       <c r="B213" t="n">
-        <v>5189</v>
+        <v>91842</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -27244,46 +27268,41 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
-      <c r="M213" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P213" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>577415</v>
+        <v>577460</v>
       </c>
       <c r="R213" t="n">
-        <v>6559187</v>
+        <v>6559048</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -27339,10 +27358,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119699976</v>
+        <v>119699263</v>
       </c>
       <c r="B214" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27355,43 +27374,37 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>577561</v>
+        <v>577415</v>
       </c>
       <c r="R214" t="n">
-        <v>6558994</v>
+        <v>6559051</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -27421,27 +27434,18 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AD214" t="b">
         <v>0</v>
       </c>
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -27460,10 +27464,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119701601</v>
+        <v>119700995</v>
       </c>
       <c r="B215" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27472,25 +27476,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -27500,10 +27504,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>577176</v>
+        <v>577330</v>
       </c>
       <c r="R215" t="n">
-        <v>6558914</v>
+        <v>6558852</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -27562,10 +27566,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119699263</v>
+        <v>119701628</v>
       </c>
       <c r="B216" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27574,41 +27578,38 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>577415</v>
+        <v>577186</v>
       </c>
       <c r="R216" t="n">
-        <v>6559051</v>
+        <v>6558951</v>
       </c>
       <c r="S216" t="n">
         <v>15</v>
@@ -27649,7 +27650,6 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -27668,10 +27668,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119699541</v>
+        <v>119701751</v>
       </c>
       <c r="B217" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27680,38 +27680,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577460</v>
+        <v>577203</v>
       </c>
       <c r="R217" t="n">
-        <v>6559048</v>
+        <v>6558998</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27770,10 +27770,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119701851</v>
+        <v>119703722</v>
       </c>
       <c r="B218" t="n">
-        <v>91861</v>
+        <v>91863</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27782,38 +27782,38 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5964</v>
+        <v>5966</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577273</v>
+        <v>577493</v>
       </c>
       <c r="R218" t="n">
-        <v>6559028</v>
+        <v>6559186</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27872,10 +27872,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119699201</v>
+        <v>119698814</v>
       </c>
       <c r="B219" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27884,41 +27884,46 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577394</v>
+        <v>577415</v>
       </c>
       <c r="R219" t="n">
-        <v>6559096</v>
+        <v>6559187</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -27974,7 +27979,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119699664</v>
+        <v>119701512</v>
       </c>
       <c r="B220" t="n">
         <v>97907</v>
@@ -28010,14 +28015,14 @@
       <c r="I220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577505</v>
+        <v>577206</v>
       </c>
       <c r="R220" t="n">
-        <v>6559057</v>
+        <v>6558900</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -28050,11 +28055,6 @@
       <c r="AA220" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -28081,7 +28081,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701512</v>
+        <v>119699201</v>
       </c>
       <c r="B221" t="n">
         <v>97907</v>
@@ -28117,14 +28117,14 @@
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577206</v>
+        <v>577394</v>
       </c>
       <c r="R221" t="n">
-        <v>6558900</v>
+        <v>6559096</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28183,10 +28183,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119701705</v>
+        <v>119699197</v>
       </c>
       <c r="B222" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -28195,38 +28195,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4364</v>
+        <v>4368</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577203</v>
+        <v>577394</v>
       </c>
       <c r="R222" t="n">
-        <v>6558998</v>
+        <v>6559096</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28285,10 +28285,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119703722</v>
+        <v>119702381</v>
       </c>
       <c r="B223" t="n">
-        <v>91863</v>
+        <v>97907</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28297,25 +28297,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -28325,10 +28325,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577493</v>
+        <v>577292</v>
       </c>
       <c r="R223" t="n">
-        <v>6559186</v>
+        <v>6559106</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -28387,10 +28387,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119699345</v>
+        <v>119699969</v>
       </c>
       <c r="B224" t="n">
-        <v>91858</v>
+        <v>91840</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28399,25 +28399,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -28427,13 +28427,13 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>577474</v>
+        <v>577561</v>
       </c>
       <c r="R224" t="n">
-        <v>6559036</v>
+        <v>6558994</v>
       </c>
       <c r="S224" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -28489,10 +28489,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119700995</v>
+        <v>119699345</v>
       </c>
       <c r="B225" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28505,37 +28505,37 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>577330</v>
+        <v>577474</v>
       </c>
       <c r="R225" t="n">
-        <v>6558852</v>
+        <v>6559036</v>
       </c>
       <c r="S225" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -28591,10 +28591,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119699553</v>
+        <v>119701601</v>
       </c>
       <c r="B226" t="n">
-        <v>91842</v>
+        <v>97907</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28603,38 +28603,38 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>577460</v>
+        <v>577176</v>
       </c>
       <c r="R226" t="n">
-        <v>6559048</v>
+        <v>6558914</v>
       </c>
       <c r="S226" t="n">
         <v>15</v>
@@ -28693,10 +28693,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119699339</v>
+        <v>119701705</v>
       </c>
       <c r="B227" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -28705,50 +28705,41 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>577474</v>
+        <v>577203</v>
       </c>
       <c r="R227" t="n">
-        <v>6559036</v>
+        <v>6558998</v>
       </c>
       <c r="S227" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -28775,19 +28766,9 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>11:28</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -28814,10 +28795,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119702969</v>
+        <v>119699976</v>
       </c>
       <c r="B228" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28826,38 +28807,47 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>577658</v>
+        <v>577561</v>
       </c>
       <c r="R228" t="n">
-        <v>6558983</v>
+        <v>6558994</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -28887,9 +28877,19 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -28916,10 +28916,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119699197</v>
+        <v>119701745</v>
       </c>
       <c r="B229" t="n">
-        <v>91858</v>
+        <v>91185</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28928,38 +28928,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4368</v>
+        <v>6031</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>577394</v>
+        <v>577203</v>
       </c>
       <c r="R229" t="n">
-        <v>6559096</v>
+        <v>6558998</v>
       </c>
       <c r="S229" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -21303,10 +21303,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119612900</v>
+        <v>119601454</v>
       </c>
       <c r="B164" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -21315,61 +21315,52 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Strandmossen 4, knärot 360 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>577583</v>
+        <v>577558</v>
       </c>
       <c r="R164" t="n">
-        <v>6559135</v>
+        <v>6558970</v>
       </c>
       <c r="S164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -21391,57 +21382,47 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>D-Kat-0636</t>
-        </is>
-      </c>
       <c r="Y164" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD164" t="b">
         <v>0</v>
       </c>
       <c r="AE164" t="b">
         <v>0</v>
       </c>
-      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -21569,10 +21550,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119601454</v>
+        <v>119612900</v>
       </c>
       <c r="B166" t="n">
-        <v>91883</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -21581,52 +21562,61 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen 4, knärot 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>577558</v>
+        <v>577583</v>
       </c>
       <c r="R166" t="n">
-        <v>6558970</v>
+        <v>6559135</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21648,47 +21638,57 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>D-Kat-0636</t>
+        </is>
+      </c>
       <c r="Y166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -23303,10 +23303,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119603201</v>
+        <v>119603450</v>
       </c>
       <c r="B180" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -23315,50 +23315,44 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>577223</v>
+        <v>577315</v>
       </c>
       <c r="R180" t="n">
-        <v>6558959</v>
+        <v>6558912</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -23387,7 +23381,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -23397,7 +23391,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -23408,31 +23402,26 @@
       </c>
       <c r="AG180" t="b">
         <v>0</v>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119603450</v>
+        <v>119603201</v>
       </c>
       <c r="B181" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -23441,44 +23430,50 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>577315</v>
+        <v>577223</v>
       </c>
       <c r="R181" t="n">
-        <v>6558912</v>
+        <v>6558959</v>
       </c>
       <c r="S181" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -23507,7 +23502,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23517,7 +23512,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23528,16 +23523,21 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
+      </c>
+      <c r="AH181" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
@@ -24157,10 +24157,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119612701</v>
+        <v>119602000</v>
       </c>
       <c r="B187" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -24169,61 +24169,49 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Strandmossen, knärot 300 m s, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>577461</v>
+        <v>577523</v>
       </c>
       <c r="R187" t="n">
-        <v>6559175</v>
+        <v>6558933</v>
       </c>
       <c r="S187" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -24245,64 +24233,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>D-Kat-0634</t>
-        </is>
-      </c>
       <c r="Y187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AD187" t="b">
         <v>0</v>
       </c>
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
-      </c>
-      <c r="AH187" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI187" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY187" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119601023</v>
+        <v>119601728</v>
       </c>
       <c r="B188" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -24311,39 +24289,38 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
@@ -24351,13 +24328,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>577571</v>
+        <v>577557</v>
       </c>
       <c r="R188" t="n">
-        <v>6558987</v>
+        <v>6558969</v>
       </c>
       <c r="S188" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24386,7 +24363,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24396,7 +24373,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24423,7 +24400,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119602000</v>
+        <v>119602836</v>
       </c>
       <c r="B189" t="n">
         <v>94681</v>
@@ -24456,11 +24433,7 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
@@ -24471,13 +24444,13 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>577523</v>
+        <v>577328</v>
       </c>
       <c r="R189" t="n">
-        <v>6558933</v>
+        <v>6558894</v>
       </c>
       <c r="S189" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -24506,7 +24479,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -24516,7 +24489,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -24531,22 +24504,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119601728</v>
+        <v>119601987</v>
       </c>
       <c r="B190" t="n">
-        <v>90334</v>
+        <v>94681</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -24559,48 +24532,45 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>3215</v>
+        <v>2180</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577557</v>
+        <v>577535</v>
       </c>
       <c r="R190" t="n">
-        <v>6558969</v>
+        <v>6558941</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24629,7 +24599,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24639,7 +24609,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24666,10 +24636,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119602836</v>
+        <v>119601316</v>
       </c>
       <c r="B191" t="n">
-        <v>94681</v>
+        <v>57326</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -24678,45 +24648,57 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577328</v>
+        <v>577573</v>
       </c>
       <c r="R191" t="n">
-        <v>6558894</v>
+        <v>6558989</v>
       </c>
       <c r="S191" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -24745,7 +24727,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -24755,7 +24737,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24770,22 +24752,22 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119601987</v>
+        <v>119612701</v>
       </c>
       <c r="B192" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -24794,49 +24776,61 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, knärot 300 m s, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>577535</v>
+        <v>577461</v>
       </c>
       <c r="R192" t="n">
-        <v>6558941</v>
+        <v>6559175</v>
       </c>
       <c r="S192" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24858,54 +24852,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X192" t="inlineStr">
+        <is>
+          <t>D-Kat-0634</t>
+        </is>
+      </c>
       <c r="Y192" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
+      </c>
+      <c r="AH192" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI192" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119601316</v>
+        <v>119601023</v>
       </c>
       <c r="B193" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24914,43 +24918,39 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
@@ -24958,10 +24958,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577573</v>
+        <v>577571</v>
       </c>
       <c r="R193" t="n">
-        <v>6558989</v>
+        <v>6558987</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -24993,7 +24993,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -25003,7 +25003,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25018,12 +25018,12 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
@@ -27047,7 +27047,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119702969</v>
+        <v>119699664</v>
       </c>
       <c r="B211" t="n">
         <v>97907</v>
@@ -27087,10 +27087,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577658</v>
+        <v>577505</v>
       </c>
       <c r="R211" t="n">
-        <v>6558983</v>
+        <v>6559057</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -27123,6 +27123,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -27149,7 +27154,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119699664</v>
+        <v>119702969</v>
       </c>
       <c r="B212" t="n">
         <v>97907</v>
@@ -27189,10 +27194,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>577505</v>
+        <v>577658</v>
       </c>
       <c r="R212" t="n">
-        <v>6559057</v>
+        <v>6558983</v>
       </c>
       <c r="S212" t="n">
         <v>15</v>
@@ -27225,11 +27230,6 @@
       <c r="AA212" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -28387,10 +28387,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119699969</v>
+        <v>119701601</v>
       </c>
       <c r="B224" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28399,38 +28399,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>577561</v>
+        <v>577176</v>
       </c>
       <c r="R224" t="n">
-        <v>6558994</v>
+        <v>6558914</v>
       </c>
       <c r="S224" t="n">
         <v>15</v>
@@ -28489,10 +28489,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119699345</v>
+        <v>119699969</v>
       </c>
       <c r="B225" t="n">
-        <v>91858</v>
+        <v>91840</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28501,25 +28501,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4368</v>
+        <v>4364</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -28529,13 +28529,13 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>577474</v>
+        <v>577561</v>
       </c>
       <c r="R225" t="n">
-        <v>6559036</v>
+        <v>6558994</v>
       </c>
       <c r="S225" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -28591,10 +28591,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119701601</v>
+        <v>119699345</v>
       </c>
       <c r="B226" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28603,41 +28603,41 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>577176</v>
+        <v>577474</v>
       </c>
       <c r="R226" t="n">
-        <v>6558914</v>
+        <v>6559036</v>
       </c>
       <c r="S226" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY229"/>
+  <dimension ref="A1:AY230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21178,10 +21178,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119600824</v>
+        <v>119602238</v>
       </c>
       <c r="B163" t="n">
-        <v>58166</v>
+        <v>91840</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -21194,47 +21194,45 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>577588</v>
+        <v>577459</v>
       </c>
       <c r="R163" t="n">
-        <v>6559049</v>
+        <v>6558921</v>
       </c>
       <c r="S163" t="n">
         <v>4</v>
@@ -21266,7 +21264,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -21276,7 +21274,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -21303,10 +21301,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119601454</v>
+        <v>119603449</v>
       </c>
       <c r="B164" t="n">
-        <v>91883</v>
+        <v>79144</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -21319,45 +21317,41 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>577558</v>
+        <v>577598</v>
       </c>
       <c r="R164" t="n">
-        <v>6558970</v>
+        <v>6559069</v>
       </c>
       <c r="S164" t="n">
         <v>4</v>
@@ -21389,7 +21383,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -21399,7 +21393,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -21414,19 +21408,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119600732</v>
+        <v>119603451</v>
       </c>
       <c r="B165" t="n">
         <v>94681</v>
@@ -21459,29 +21453,21 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>577625</v>
+        <v>577601</v>
       </c>
       <c r="R165" t="n">
-        <v>6559039</v>
+        <v>6559060</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -21538,22 +21524,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119612900</v>
+        <v>119603453</v>
       </c>
       <c r="B166" t="n">
-        <v>97907</v>
+        <v>4772</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -21562,51 +21548,36 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>102306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Strandmossen 4, knärot 360 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
@@ -21616,7 +21587,7 @@
         <v>6559135</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21638,64 +21609,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>D-Kat-0636</t>
-        </is>
-      </c>
       <c r="Y166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119602671</v>
+        <v>119612765</v>
       </c>
       <c r="B167" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -21704,48 +21665,61 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr"/>
-      <c r="K167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 2, knärot 350 m s, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>577392</v>
+        <v>577495</v>
       </c>
       <c r="R167" t="n">
-        <v>6558896</v>
+        <v>6559150</v>
       </c>
       <c r="S167" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -21767,54 +21741,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>D-kat-0633</t>
+        </is>
+      </c>
       <c r="Y167" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119599395</v>
+        <v>119600824</v>
       </c>
       <c r="B168" t="n">
-        <v>90582</v>
+        <v>58166</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -21823,25 +21807,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5442</v>
+        <v>208249</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -21849,26 +21833,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>577449</v>
+        <v>577588</v>
       </c>
       <c r="R168" t="n">
-        <v>6559178</v>
+        <v>6559049</v>
       </c>
       <c r="S168" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -21897,7 +21883,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -21907,7 +21893,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -21922,19 +21908,19 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119602280</v>
+        <v>119603201</v>
       </c>
       <c r="B169" t="n">
         <v>97907</v>
@@ -21969,12 +21955,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -21983,13 +21969,13 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>577412</v>
+        <v>577223</v>
       </c>
       <c r="R169" t="n">
-        <v>6558928</v>
+        <v>6558959</v>
       </c>
       <c r="S169" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -22018,7 +22004,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -22028,7 +22014,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -22039,23 +22025,28 @@
       </c>
       <c r="AG169" t="b">
         <v>0</v>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119601750</v>
+        <v>119599963</v>
       </c>
       <c r="B170" t="n">
         <v>97907</v>
@@ -22090,30 +22081,26 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>577554</v>
+        <v>577548</v>
       </c>
       <c r="R170" t="n">
-        <v>6558959</v>
+        <v>6559163</v>
       </c>
       <c r="S170" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -22142,7 +22129,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -22152,7 +22139,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22167,22 +22154,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119599959</v>
+        <v>119601840</v>
       </c>
       <c r="B171" t="n">
-        <v>5189</v>
+        <v>90057</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -22191,51 +22178,49 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>105930</v>
+        <v>2051</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr"/>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>577484</v>
+        <v>577557</v>
       </c>
       <c r="R171" t="n">
-        <v>6559147</v>
+        <v>6558949</v>
       </c>
       <c r="S171" t="n">
         <v>4</v>
@@ -22267,7 +22252,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -22277,7 +22262,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22292,22 +22277,22 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119600012</v>
+        <v>119601607</v>
       </c>
       <c r="B172" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -22316,50 +22301,53 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>577548</v>
+        <v>577578</v>
       </c>
       <c r="R172" t="n">
-        <v>6559163</v>
+        <v>6558968</v>
       </c>
       <c r="S172" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -22388,7 +22376,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -22398,7 +22386,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -22413,22 +22401,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119601840</v>
+        <v>119599396</v>
       </c>
       <c r="B173" t="n">
-        <v>90057</v>
+        <v>97907</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -22441,45 +22429,42 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>577557</v>
+        <v>577460</v>
       </c>
       <c r="R173" t="n">
-        <v>6558949</v>
+        <v>6559174</v>
       </c>
       <c r="S173" t="n">
         <v>4</v>
@@ -22511,7 +22496,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -22521,7 +22506,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -22536,22 +22521,22 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119599816</v>
+        <v>119600012</v>
       </c>
       <c r="B174" t="n">
-        <v>90582</v>
+        <v>5169</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -22560,25 +22545,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5442</v>
+        <v>100526</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -22586,23 +22571,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>577555</v>
+        <v>577548</v>
       </c>
       <c r="R174" t="n">
-        <v>6559157</v>
+        <v>6559163</v>
       </c>
       <c r="S174" t="n">
         <v>4</v>
@@ -22634,7 +22617,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -22644,7 +22627,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -22659,22 +22642,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119612765</v>
+        <v>119600732</v>
       </c>
       <c r="B175" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -22683,61 +22666,53 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Strandmossen 2, knärot 350 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>577495</v>
+        <v>577625</v>
       </c>
       <c r="R175" t="n">
-        <v>6559150</v>
+        <v>6559039</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -22759,64 +22734,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>D-kat-0633</t>
-        </is>
-      </c>
       <c r="Y175" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AD175" t="b">
         <v>0</v>
       </c>
       <c r="AE175" t="b">
         <v>0</v>
       </c>
-      <c r="AF175" t="inlineStr"/>
       <c r="AG175" t="b">
         <v>0</v>
-      </c>
-      <c r="AH175" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI175" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
       </c>
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119602497</v>
+        <v>119601987</v>
       </c>
       <c r="B176" t="n">
-        <v>105009</v>
+        <v>94681</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -22829,29 +22794,29 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
@@ -22861,13 +22826,13 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>577411</v>
+        <v>577535</v>
       </c>
       <c r="R176" t="n">
-        <v>6558925</v>
+        <v>6558941</v>
       </c>
       <c r="S176" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -22896,7 +22861,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -22906,7 +22871,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -22921,22 +22886,22 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119601087</v>
+        <v>119602380</v>
       </c>
       <c r="B177" t="n">
-        <v>91228</v>
+        <v>97907</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -22949,45 +22914,46 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>577575</v>
+        <v>577448</v>
       </c>
       <c r="R177" t="n">
-        <v>6558990</v>
+        <v>6558899</v>
       </c>
       <c r="S177" t="n">
         <v>4</v>
@@ -23019,7 +22985,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -23029,7 +22995,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -23056,10 +23022,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119602238</v>
+        <v>119602448</v>
       </c>
       <c r="B178" t="n">
-        <v>91840</v>
+        <v>94681</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -23072,34 +23038,31 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4364</v>
+        <v>2180</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
@@ -23107,10 +23070,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>577459</v>
+        <v>577444</v>
       </c>
       <c r="R178" t="n">
-        <v>6558921</v>
+        <v>6558882</v>
       </c>
       <c r="S178" t="n">
         <v>4</v>
@@ -23142,7 +23105,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -23152,7 +23115,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23179,10 +23142,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119600170</v>
+        <v>119601087</v>
       </c>
       <c r="B179" t="n">
-        <v>97907</v>
+        <v>91228</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -23195,35 +23158,34 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
@@ -23231,10 +23193,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>577585</v>
+        <v>577575</v>
       </c>
       <c r="R179" t="n">
-        <v>6559134</v>
+        <v>6558990</v>
       </c>
       <c r="S179" t="n">
         <v>4</v>
@@ -23266,7 +23228,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23276,7 +23238,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -23418,10 +23380,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119603201</v>
+        <v>119602593</v>
       </c>
       <c r="B181" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -23430,50 +23392,45 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>577223</v>
+        <v>577389</v>
       </c>
       <c r="R181" t="n">
-        <v>6558959</v>
+        <v>6558904</v>
       </c>
       <c r="S181" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -23502,7 +23459,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -23512,7 +23469,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -23523,31 +23480,26 @@
       </c>
       <c r="AG181" t="b">
         <v>0</v>
-      </c>
-      <c r="AH181" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119599958</v>
+        <v>119602836</v>
       </c>
       <c r="B182" t="n">
-        <v>5169</v>
+        <v>94681</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -23560,50 +23512,41 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100526</v>
+        <v>2180</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>577484</v>
+        <v>577328</v>
       </c>
       <c r="R182" t="n">
-        <v>6559147</v>
+        <v>6558894</v>
       </c>
       <c r="S182" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -23632,7 +23575,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -23642,7 +23585,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -23657,22 +23600,22 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119603442</v>
+        <v>119612860</v>
       </c>
       <c r="B183" t="n">
-        <v>58138</v>
+        <v>97907</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -23681,54 +23624,61 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>208245</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J183" t="inlineStr"/>
-      <c r="K183" t="inlineStr"/>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr"/>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen 3, knärot 325 m s, Srm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>577549</v>
+        <v>577550</v>
       </c>
       <c r="R183" t="n">
-        <v>6558967</v>
+        <v>6559170</v>
       </c>
       <c r="S183" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -23750,51 +23700,61 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>D-Kat-0635</t>
+        </is>
+      </c>
       <c r="Y183" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY183" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119602564</v>
+        <v>119612701</v>
       </c>
       <c r="B184" t="n">
         <v>97907</v>
@@ -23829,30 +23789,38 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, knärot 300 m s, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>577409</v>
+        <v>577461</v>
       </c>
       <c r="R184" t="n">
-        <v>6558923</v>
+        <v>6559175</v>
       </c>
       <c r="S184" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -23874,54 +23842,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>D-Kat-0634</t>
+        </is>
+      </c>
       <c r="Y184" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
+      </c>
+      <c r="AH184" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI184" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY184" t="inlineStr"/>
+          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119602448</v>
+        <v>119603136</v>
       </c>
       <c r="B185" t="n">
-        <v>94681</v>
+        <v>91832</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -23930,35 +23908,34 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
@@ -23966,13 +23943,13 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>577444</v>
+        <v>577241</v>
       </c>
       <c r="R185" t="n">
-        <v>6558882</v>
+        <v>6558978</v>
       </c>
       <c r="S185" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -24001,7 +23978,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -24011,7 +23988,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -24026,22 +24003,22 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119603449</v>
+        <v>119599599</v>
       </c>
       <c r="B186" t="n">
-        <v>79144</v>
+        <v>90582</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -24054,44 +24031,46 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>577598</v>
+        <v>577474</v>
       </c>
       <c r="R186" t="n">
-        <v>6559069</v>
+        <v>6559269</v>
       </c>
       <c r="S186" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -24120,7 +24099,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -24130,7 +24109,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -24145,22 +24124,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119602000</v>
+        <v>119599958</v>
       </c>
       <c r="B187" t="n">
-        <v>94681</v>
+        <v>5169</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -24173,42 +24152,47 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>577523</v>
+        <v>577484</v>
       </c>
       <c r="R187" t="n">
-        <v>6558933</v>
+        <v>6559147</v>
       </c>
       <c r="S187" t="n">
         <v>4</v>
@@ -24240,7 +24224,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -24250,7 +24234,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -24265,22 +24249,22 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119601728</v>
+        <v>119601316</v>
       </c>
       <c r="B188" t="n">
-        <v>90334</v>
+        <v>57326</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -24289,25 +24273,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -24315,12 +24299,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
@@ -24328,13 +24317,13 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>577557</v>
+        <v>577573</v>
       </c>
       <c r="R188" t="n">
-        <v>6558969</v>
+        <v>6558989</v>
       </c>
       <c r="S188" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -24363,7 +24352,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -24373,7 +24362,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -24388,22 +24377,22 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119602836</v>
+        <v>119612900</v>
       </c>
       <c r="B189" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -24412,45 +24401,61 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen 4, knärot 360 m s, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>577328</v>
+        <v>577583</v>
       </c>
       <c r="R189" t="n">
-        <v>6558894</v>
+        <v>6559135</v>
       </c>
       <c r="S189" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -24472,54 +24477,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>D-Kat-0636</t>
+        </is>
+      </c>
       <c r="Y189" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AD189" t="b">
         <v>0</v>
       </c>
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
+      </c>
+      <c r="AH189" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI189" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
-        </is>
-      </c>
-      <c r="AY189" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119601987</v>
+        <v>119599816</v>
       </c>
       <c r="B190" t="n">
-        <v>94681</v>
+        <v>90582</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -24528,49 +24543,52 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>577535</v>
+        <v>577555</v>
       </c>
       <c r="R190" t="n">
-        <v>6558941</v>
+        <v>6559157</v>
       </c>
       <c r="S190" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -24599,7 +24617,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -24609,7 +24627,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -24624,22 +24642,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119601316</v>
+        <v>119600170</v>
       </c>
       <c r="B191" t="n">
-        <v>57326</v>
+        <v>97907</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -24648,43 +24666,39 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
@@ -24692,10 +24706,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>577573</v>
+        <v>577585</v>
       </c>
       <c r="R191" t="n">
-        <v>6558989</v>
+        <v>6559134</v>
       </c>
       <c r="S191" t="n">
         <v>4</v>
@@ -24727,7 +24741,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -24737,7 +24751,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -24764,10 +24778,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119612701</v>
+        <v>119599959</v>
       </c>
       <c r="B192" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -24776,61 +24790,54 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J192" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Strandmossen, knärot 300 m s, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>577461</v>
+        <v>577484</v>
       </c>
       <c r="R192" t="n">
-        <v>6559175</v>
+        <v>6559147</v>
       </c>
       <c r="S192" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -24852,64 +24859,54 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>D-Kat-0634</t>
-        </is>
-      </c>
       <c r="Y192" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
       <c r="AD192" t="b">
         <v>0</v>
       </c>
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Göran Ekström, Hanna Nordin</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119601023</v>
+        <v>119602000</v>
       </c>
       <c r="B193" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24918,50 +24915,46 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577571</v>
+        <v>577523</v>
       </c>
       <c r="R193" t="n">
-        <v>6558987</v>
+        <v>6558933</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -24993,7 +24986,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -25003,7 +24996,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25018,22 +25011,22 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119603452</v>
+        <v>119602564</v>
       </c>
       <c r="B194" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -25042,42 +25035,50 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>577601</v>
+        <v>577409</v>
       </c>
       <c r="R194" t="n">
-        <v>6559060</v>
+        <v>6558923</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -25109,7 +25110,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -25119,7 +25120,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -25134,22 +25135,22 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119599963</v>
+        <v>119599967</v>
       </c>
       <c r="B195" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -25158,49 +25159,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>577548</v>
+        <v>577484</v>
       </c>
       <c r="R195" t="n">
-        <v>6559163</v>
+        <v>6559147</v>
       </c>
       <c r="S195" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -25229,7 +25226,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -25239,7 +25236,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -25266,7 +25263,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119599599</v>
+        <v>119599395</v>
       </c>
       <c r="B196" t="n">
         <v>90582</v>
@@ -25301,7 +25298,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -25309,19 +25306,21 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>577474</v>
+        <v>577449</v>
       </c>
       <c r="R196" t="n">
-        <v>6559269</v>
+        <v>6559178</v>
       </c>
       <c r="S196" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -25350,7 +25349,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -25360,7 +25359,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -25375,22 +25374,22 @@
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Tobias Hellberg</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119599396</v>
+        <v>119601728</v>
       </c>
       <c r="B197" t="n">
-        <v>97907</v>
+        <v>90334</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -25399,49 +25398,52 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K197" t="inlineStr"/>
-      <c r="L197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>577460</v>
+        <v>577557</v>
       </c>
       <c r="R197" t="n">
-        <v>6559174</v>
+        <v>6558969</v>
       </c>
       <c r="S197" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -25470,7 +25472,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -25480,7 +25482,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -25495,22 +25497,22 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119602562</v>
+        <v>119603442</v>
       </c>
       <c r="B198" t="n">
-        <v>105009</v>
+        <v>58138</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -25523,49 +25525,50 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221144</v>
+        <v>208245</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>577392</v>
+        <v>577549</v>
       </c>
       <c r="R198" t="n">
-        <v>6558906</v>
+        <v>6558967</v>
       </c>
       <c r="S198" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -25594,7 +25597,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -25604,7 +25607,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -25619,19 +25622,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119602380</v>
+        <v>119601750</v>
       </c>
       <c r="B199" t="n">
         <v>97907</v>
@@ -25666,7 +25669,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -25679,17 +25682,17 @@
       <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>577448</v>
+        <v>577554</v>
       </c>
       <c r="R199" t="n">
-        <v>6558899</v>
+        <v>6558959</v>
       </c>
       <c r="S199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -25718,7 +25721,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -25728,7 +25731,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -25755,7 +25758,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119601607</v>
+        <v>119601023</v>
       </c>
       <c r="B200" t="n">
         <v>97907</v>
@@ -25790,7 +25793,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -25807,13 +25810,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>577578</v>
+        <v>577571</v>
       </c>
       <c r="R200" t="n">
-        <v>6558968</v>
+        <v>6558987</v>
       </c>
       <c r="S200" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -25842,7 +25845,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -25852,7 +25855,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -25879,10 +25882,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119602593</v>
+        <v>119602497</v>
       </c>
       <c r="B201" t="n">
-        <v>94681</v>
+        <v>105009</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -25895,24 +25898,28 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
@@ -25923,13 +25930,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>577389</v>
+        <v>577411</v>
       </c>
       <c r="R201" t="n">
-        <v>6558904</v>
+        <v>6558925</v>
       </c>
       <c r="S201" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -25958,7 +25965,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -25968,7 +25975,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -25983,22 +25990,22 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119603136</v>
+        <v>119601286</v>
       </c>
       <c r="B202" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -26007,48 +26014,50 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>577241</v>
+        <v>577556</v>
       </c>
       <c r="R202" t="n">
-        <v>6558978</v>
+        <v>6558966</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -26077,7 +26086,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -26087,7 +26096,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -26098,26 +26107,31 @@
       </c>
       <c r="AG202" t="b">
         <v>0</v>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>Skog på blockmark</t>
+        </is>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Jessica Loddby de Neergaard</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119612860</v>
+        <v>119602671</v>
       </c>
       <c r="B203" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -26126,61 +26140,48 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Strandmossen 3, knärot 325 m s, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>577550</v>
+        <v>577392</v>
       </c>
       <c r="R203" t="n">
-        <v>6559170</v>
+        <v>6558896</v>
       </c>
       <c r="S203" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -26202,61 +26203,51 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>D-Kat-0635</t>
-        </is>
-      </c>
       <c r="Y203" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY203" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119601286</v>
+        <v>119602280</v>
       </c>
       <c r="B204" t="n">
         <v>97907</v>
@@ -26291,12 +26282,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
@@ -26305,13 +26296,13 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>577556</v>
+        <v>577412</v>
       </c>
       <c r="R204" t="n">
-        <v>6558966</v>
+        <v>6558928</v>
       </c>
       <c r="S204" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -26340,7 +26331,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -26350,7 +26341,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -26361,31 +26352,26 @@
       </c>
       <c r="AG204" t="b">
         <v>0</v>
-      </c>
-      <c r="AH204" t="inlineStr">
-        <is>
-          <t>Skog på blockmark</t>
-        </is>
       </c>
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119599967</v>
+        <v>119601454</v>
       </c>
       <c r="B205" t="n">
-        <v>94681</v>
+        <v>91883</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -26394,42 +26380,49 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>2180</v>
+        <v>5448</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>577484</v>
+        <v>577558</v>
       </c>
       <c r="R205" t="n">
-        <v>6559147</v>
+        <v>6558970</v>
       </c>
       <c r="S205" t="n">
         <v>4</v>
@@ -26461,7 +26454,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -26471,7 +26464,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -26486,22 +26479,22 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119603453</v>
+        <v>119602562</v>
       </c>
       <c r="B206" t="n">
-        <v>4772</v>
+        <v>105009</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -26514,42 +26507,49 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>102306</v>
+        <v>221144</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>577583</v>
+        <v>577392</v>
       </c>
       <c r="R206" t="n">
-        <v>6559135</v>
+        <v>6558906</v>
       </c>
       <c r="S206" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -26578,7 +26578,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -26603,22 +26603,22 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Jessica Loddby de Neergaard</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119699339</v>
+        <v>119699976</v>
       </c>
       <c r="B207" t="n">
-        <v>57326</v>
+        <v>57463</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -26631,21 +26631,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -26655,7 +26655,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -26664,13 +26664,13 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>577474</v>
+        <v>577561</v>
       </c>
       <c r="R207" t="n">
-        <v>6559036</v>
+        <v>6558994</v>
       </c>
       <c r="S207" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -26736,10 +26736,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119698812</v>
+        <v>119703722</v>
       </c>
       <c r="B208" t="n">
-        <v>5169</v>
+        <v>91863</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -26748,46 +26748,41 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>577415</v>
+        <v>577493</v>
       </c>
       <c r="R208" t="n">
-        <v>6559187</v>
+        <v>6559186</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -26843,10 +26838,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699541</v>
+        <v>119699664</v>
       </c>
       <c r="B209" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26855,25 +26850,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26883,10 +26878,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577460</v>
+        <v>577505</v>
       </c>
       <c r="R209" t="n">
-        <v>6559048</v>
+        <v>6559057</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26919,6 +26914,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26945,10 +26945,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119701851</v>
+        <v>119698814</v>
       </c>
       <c r="B210" t="n">
-        <v>91861</v>
+        <v>5189</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26961,37 +26961,42 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5964</v>
+        <v>105930</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577273</v>
+        <v>577415</v>
       </c>
       <c r="R210" t="n">
-        <v>6559028</v>
+        <v>6559187</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27047,10 +27052,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119699664</v>
+        <v>119699541</v>
       </c>
       <c r="B211" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27059,25 +27064,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -27087,10 +27092,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577505</v>
+        <v>577460</v>
       </c>
       <c r="R211" t="n">
-        <v>6559057</v>
+        <v>6559048</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -27123,11 +27128,6 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -27154,10 +27154,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119702969</v>
+        <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -27166,25 +27166,25 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -27194,13 +27194,13 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>577658</v>
+        <v>577474</v>
       </c>
       <c r="R212" t="n">
-        <v>6558983</v>
+        <v>6559036</v>
       </c>
       <c r="S212" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -27256,10 +27256,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119699553</v>
+        <v>119699263</v>
       </c>
       <c r="B213" t="n">
-        <v>91842</v>
+        <v>91858</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -27272,34 +27272,37 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>788</v>
+        <v>4368</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>577460</v>
+        <v>577415</v>
       </c>
       <c r="R213" t="n">
-        <v>6559048</v>
+        <v>6559051</v>
       </c>
       <c r="S213" t="n">
         <v>15</v>
@@ -27340,6 +27343,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -27358,10 +27362,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119699263</v>
+        <v>119699339</v>
       </c>
       <c r="B214" t="n">
-        <v>91858</v>
+        <v>57326</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -27374,40 +27378,46 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
-      <c r="K214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>577415</v>
+        <v>577474</v>
       </c>
       <c r="R214" t="n">
-        <v>6559051</v>
+        <v>6559036</v>
       </c>
       <c r="S214" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -27434,18 +27444,27 @@
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>2024-09-12</t>
         </is>
       </c>
+      <c r="AB214" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
       <c r="AD214" t="b">
         <v>0</v>
       </c>
       <c r="AE214" t="b">
         <v>0</v>
       </c>
-      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
@@ -27464,10 +27483,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119700995</v>
+        <v>119701705</v>
       </c>
       <c r="B215" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -27476,25 +27495,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -27504,10 +27523,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>577330</v>
+        <v>577203</v>
       </c>
       <c r="R215" t="n">
-        <v>6558852</v>
+        <v>6558998</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -27566,10 +27585,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119701628</v>
+        <v>119700995</v>
       </c>
       <c r="B216" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -27578,25 +27597,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -27606,10 +27625,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>577186</v>
+        <v>577330</v>
       </c>
       <c r="R216" t="n">
-        <v>6558951</v>
+        <v>6558852</v>
       </c>
       <c r="S216" t="n">
         <v>15</v>
@@ -27668,10 +27687,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119701751</v>
+        <v>119699969</v>
       </c>
       <c r="B217" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27680,38 +27699,38 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577203</v>
+        <v>577561</v>
       </c>
       <c r="R217" t="n">
-        <v>6558998</v>
+        <v>6558994</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27770,10 +27789,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119703722</v>
+        <v>119702969</v>
       </c>
       <c r="B218" t="n">
-        <v>91863</v>
+        <v>97907</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27782,25 +27801,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27810,10 +27829,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577493</v>
+        <v>577658</v>
       </c>
       <c r="R218" t="n">
-        <v>6559186</v>
+        <v>6558983</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27872,10 +27891,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119698814</v>
+        <v>119699553</v>
       </c>
       <c r="B219" t="n">
-        <v>5189</v>
+        <v>91842</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27884,46 +27903,41 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>105930</v>
+        <v>788</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577415</v>
+        <v>577460</v>
       </c>
       <c r="R219" t="n">
-        <v>6559187</v>
+        <v>6559048</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -27979,10 +27993,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119701512</v>
+        <v>119698812</v>
       </c>
       <c r="B220" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -27991,41 +28005,46 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577206</v>
+        <v>577415</v>
       </c>
       <c r="R220" t="n">
-        <v>6558900</v>
+        <v>6559187</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28081,10 +28100,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119699201</v>
+        <v>119701851</v>
       </c>
       <c r="B221" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -28093,38 +28112,38 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577394</v>
+        <v>577273</v>
       </c>
       <c r="R221" t="n">
-        <v>6559096</v>
+        <v>6559028</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28183,10 +28202,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119699197</v>
+        <v>119701751</v>
       </c>
       <c r="B222" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -28195,38 +28214,38 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577394</v>
+        <v>577203</v>
       </c>
       <c r="R222" t="n">
-        <v>6559096</v>
+        <v>6558998</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28285,7 +28304,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119702381</v>
+        <v>119701628</v>
       </c>
       <c r="B223" t="n">
         <v>97907</v>
@@ -28321,14 +28340,14 @@
       <c r="I223" t="inlineStr"/>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577292</v>
+        <v>577186</v>
       </c>
       <c r="R223" t="n">
-        <v>6559106</v>
+        <v>6558951</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -28387,10 +28406,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119701601</v>
+        <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -28399,38 +28418,38 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>577176</v>
+        <v>577394</v>
       </c>
       <c r="R224" t="n">
-        <v>6558914</v>
+        <v>6559096</v>
       </c>
       <c r="S224" t="n">
         <v>15</v>
@@ -28489,10 +28508,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119699969</v>
+        <v>119701745</v>
       </c>
       <c r="B225" t="n">
-        <v>91840</v>
+        <v>91185</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -28505,34 +28524,34 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>4364</v>
+        <v>6031</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>577561</v>
+        <v>577203</v>
       </c>
       <c r="R225" t="n">
-        <v>6558994</v>
+        <v>6558998</v>
       </c>
       <c r="S225" t="n">
         <v>15</v>
@@ -28591,10 +28610,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119699345</v>
+        <v>119701512</v>
       </c>
       <c r="B226" t="n">
-        <v>91858</v>
+        <v>97907</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -28603,41 +28622,41 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>577474</v>
+        <v>577206</v>
       </c>
       <c r="R226" t="n">
-        <v>6559036</v>
+        <v>6558900</v>
       </c>
       <c r="S226" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -28693,10 +28712,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119701705</v>
+        <v>119701601</v>
       </c>
       <c r="B227" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -28705,25 +28724,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -28733,10 +28752,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>577203</v>
+        <v>577176</v>
       </c>
       <c r="R227" t="n">
-        <v>6558998</v>
+        <v>6558914</v>
       </c>
       <c r="S227" t="n">
         <v>15</v>
@@ -28795,10 +28814,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119699976</v>
+        <v>119699201</v>
       </c>
       <c r="B228" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -28807,47 +28826,38 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>577561</v>
+        <v>577394</v>
       </c>
       <c r="R228" t="n">
-        <v>6558994</v>
+        <v>6559096</v>
       </c>
       <c r="S228" t="n">
         <v>15</v>
@@ -28877,19 +28887,9 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="Z228" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB228" t="inlineStr">
-        <is>
-          <t>12:04</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -28916,10 +28916,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119701745</v>
+        <v>119702381</v>
       </c>
       <c r="B229" t="n">
-        <v>91185</v>
+        <v>97907</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -28928,38 +28928,38 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>577203</v>
+        <v>577292</v>
       </c>
       <c r="R229" t="n">
-        <v>6558998</v>
+        <v>6559106</v>
       </c>
       <c r="S229" t="n">
         <v>15</v>
@@ -29015,6 +29015,129 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>120223306</v>
+      </c>
+      <c r="B230" t="n">
+        <v>90562</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>577338</v>
+      </c>
+      <c r="R230" t="n">
+        <v>6558884</v>
+      </c>
+      <c r="S230" t="n">
+        <v>4</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AB230" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -21420,10 +21420,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119603451</v>
+        <v>119603453</v>
       </c>
       <c r="B165" t="n">
-        <v>94681</v>
+        <v>4772</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -21436,38 +21436,39 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2180</v>
+        <v>102306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>577601</v>
+        <v>577583</v>
       </c>
       <c r="R165" t="n">
-        <v>6559060</v>
+        <v>6559135</v>
       </c>
       <c r="S165" t="n">
         <v>4</v>
@@ -21499,7 +21500,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -21509,7 +21510,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -21536,10 +21537,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119603453</v>
+        <v>119612765</v>
       </c>
       <c r="B166" t="n">
-        <v>4772</v>
+        <v>97907</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -21548,46 +21549,61 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>102306</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr"/>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen 2, knärot 350 m s, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>577583</v>
+        <v>577495</v>
       </c>
       <c r="R166" t="n">
-        <v>6559135</v>
+        <v>6559150</v>
       </c>
       <c r="S166" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -21609,54 +21625,64 @@
           <t>Floda</t>
         </is>
       </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>D-kat-0633</t>
+        </is>
+      </c>
       <c r="Y166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>14:50</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>14:54</t>
-        </is>
-      </c>
       <c r="AD166" t="b">
         <v>0</v>
       </c>
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>barrblandskog</t>
+        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Karlsson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
-        </is>
-      </c>
-      <c r="AY166" t="inlineStr"/>
+          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119612765</v>
+        <v>119603451</v>
       </c>
       <c r="B167" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -21665,61 +21691,45 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Strandmossen 2, knärot 350 m s, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>577495</v>
+        <v>577601</v>
       </c>
       <c r="R167" t="n">
-        <v>6559150</v>
+        <v>6559060</v>
       </c>
       <c r="S167" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -21741,57 +21751,47 @@
           <t>Floda</t>
         </is>
       </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>D-kat-0633</t>
-        </is>
-      </c>
       <c r="Y167" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>2024-09-07</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AD167" t="b">
         <v>0</v>
       </c>
       <c r="AE167" t="b">
         <v>0</v>
       </c>
-      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AH167" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI167" t="inlineStr">
-        <is>
-          <t>barrblandskog</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Bo Karlsson, Hanna Nordin, Göran Ekström</t>
-        </is>
-      </c>
-      <c r="AY167" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Göran Ekström, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -22046,10 +22046,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119599963</v>
+        <v>119601840</v>
       </c>
       <c r="B170" t="n">
-        <v>97907</v>
+        <v>90057</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -22062,45 +22062,48 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>2051</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>577548</v>
+        <v>577557</v>
       </c>
       <c r="R170" t="n">
-        <v>6559163</v>
+        <v>6558949</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -22129,7 +22132,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -22139,7 +22142,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -22154,22 +22157,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Göran Ekström, Bo Karlsson</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119601840</v>
+        <v>119599963</v>
       </c>
       <c r="B171" t="n">
-        <v>90057</v>
+        <v>97907</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -22182,48 +22185,45 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>2051</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>577557</v>
+        <v>577548</v>
       </c>
       <c r="R171" t="n">
-        <v>6558949</v>
+        <v>6559163</v>
       </c>
       <c r="S171" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -22262,7 +22262,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -22277,12 +22277,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Göran Ekström, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
@@ -23022,10 +23022,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119602448</v>
+        <v>119601087</v>
       </c>
       <c r="B178" t="n">
-        <v>94681</v>
+        <v>91228</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -23034,46 +23034,49 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2180</v>
+        <v>898</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>577444</v>
+        <v>577575</v>
       </c>
       <c r="R178" t="n">
-        <v>6558882</v>
+        <v>6558990</v>
       </c>
       <c r="S178" t="n">
         <v>4</v>
@@ -23105,7 +23108,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -23115,7 +23118,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -23142,10 +23145,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119601087</v>
+        <v>119602448</v>
       </c>
       <c r="B179" t="n">
-        <v>91228</v>
+        <v>94681</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -23154,49 +23157,46 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>898</v>
+        <v>2180</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>577575</v>
+        <v>577444</v>
       </c>
       <c r="R179" t="n">
-        <v>6558990</v>
+        <v>6558882</v>
       </c>
       <c r="S179" t="n">
         <v>4</v>
@@ -23228,7 +23228,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -23238,7 +23238,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -24903,10 +24903,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119602000</v>
+        <v>119602564</v>
       </c>
       <c r="B193" t="n">
-        <v>94681</v>
+        <v>97907</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -24915,33 +24915,37 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr"/>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
@@ -24951,10 +24955,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>577523</v>
+        <v>577409</v>
       </c>
       <c r="R193" t="n">
-        <v>6558933</v>
+        <v>6558923</v>
       </c>
       <c r="S193" t="n">
         <v>4</v>
@@ -24986,7 +24990,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -24996,7 +25000,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -25023,10 +25027,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119602564</v>
+        <v>119602000</v>
       </c>
       <c r="B194" t="n">
-        <v>97907</v>
+        <v>94681</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -25035,37 +25039,33 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
@@ -25075,10 +25075,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>577409</v>
+        <v>577523</v>
       </c>
       <c r="R194" t="n">
-        <v>6558923</v>
+        <v>6558933</v>
       </c>
       <c r="S194" t="n">
         <v>4</v>
@@ -25110,7 +25110,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -26838,10 +26838,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699664</v>
+        <v>119699541</v>
       </c>
       <c r="B209" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26850,25 +26850,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577505</v>
+        <v>577460</v>
       </c>
       <c r="R209" t="n">
-        <v>6559057</v>
+        <v>6559048</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26914,11 +26914,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26945,10 +26940,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119698814</v>
+        <v>119699664</v>
       </c>
       <c r="B210" t="n">
-        <v>5189</v>
+        <v>97907</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26957,46 +26952,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577415</v>
+        <v>577505</v>
       </c>
       <c r="R210" t="n">
-        <v>6559187</v>
+        <v>6559057</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27026,6 +27016,11 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27052,10 +27047,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119699541</v>
+        <v>119698814</v>
       </c>
       <c r="B211" t="n">
-        <v>91832</v>
+        <v>5189</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27064,41 +27059,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4361</v>
+        <v>105930</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577460</v>
+        <v>577415</v>
       </c>
       <c r="R211" t="n">
-        <v>6559048</v>
+        <v>6559187</v>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27687,10 +27687,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119699969</v>
+        <v>119699553</v>
       </c>
       <c r="B217" t="n">
-        <v>91840</v>
+        <v>91842</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27699,25 +27699,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>788</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -27727,10 +27727,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577561</v>
+        <v>577460</v>
       </c>
       <c r="R217" t="n">
-        <v>6558994</v>
+        <v>6559048</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27789,10 +27789,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119702969</v>
+        <v>119699969</v>
       </c>
       <c r="B218" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27801,25 +27801,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27829,10 +27829,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577658</v>
+        <v>577561</v>
       </c>
       <c r="R218" t="n">
-        <v>6558983</v>
+        <v>6558994</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27891,10 +27891,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119699553</v>
+        <v>119702969</v>
       </c>
       <c r="B219" t="n">
-        <v>91842</v>
+        <v>97907</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27903,25 +27903,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -27931,10 +27931,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577460</v>
+        <v>577658</v>
       </c>
       <c r="R219" t="n">
-        <v>6559048</v>
+        <v>6558983</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -27993,10 +27993,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119698812</v>
+        <v>119701851</v>
       </c>
       <c r="B220" t="n">
-        <v>5169</v>
+        <v>91861</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -28009,42 +28009,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577415</v>
+        <v>577273</v>
       </c>
       <c r="R220" t="n">
-        <v>6559187</v>
+        <v>6559028</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28100,10 +28095,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701851</v>
+        <v>119701751</v>
       </c>
       <c r="B221" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -28112,25 +28107,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -28140,10 +28135,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577273</v>
+        <v>577203</v>
       </c>
       <c r="R221" t="n">
-        <v>6559028</v>
+        <v>6558998</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28202,7 +28197,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119701751</v>
+        <v>119701628</v>
       </c>
       <c r="B222" t="n">
         <v>97907</v>
@@ -28242,10 +28237,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577203</v>
+        <v>577186</v>
       </c>
       <c r="R222" t="n">
-        <v>6558998</v>
+        <v>6558951</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28304,10 +28299,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119701628</v>
+        <v>119698812</v>
       </c>
       <c r="B223" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28316,41 +28311,46 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577186</v>
+        <v>577415</v>
       </c>
       <c r="R223" t="n">
-        <v>6558951</v>
+        <v>6559187</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27993,10 +27993,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119701851</v>
+        <v>119698812</v>
       </c>
       <c r="B220" t="n">
-        <v>91861</v>
+        <v>5169</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -28009,37 +28009,42 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577273</v>
+        <v>577415</v>
       </c>
       <c r="R220" t="n">
-        <v>6559028</v>
+        <v>6559187</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28095,10 +28100,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701751</v>
+        <v>119701851</v>
       </c>
       <c r="B221" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -28107,25 +28112,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -28135,10 +28140,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577203</v>
+        <v>577273</v>
       </c>
       <c r="R221" t="n">
-        <v>6558998</v>
+        <v>6559028</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28197,7 +28202,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119701628</v>
+        <v>119701751</v>
       </c>
       <c r="B222" t="n">
         <v>97907</v>
@@ -28237,10 +28242,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577186</v>
+        <v>577203</v>
       </c>
       <c r="R222" t="n">
-        <v>6558951</v>
+        <v>6558998</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28299,10 +28304,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119698812</v>
+        <v>119701628</v>
       </c>
       <c r="B223" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28311,46 +28316,41 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577415</v>
+        <v>577186</v>
       </c>
       <c r="R223" t="n">
-        <v>6559187</v>
+        <v>6558951</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -26838,10 +26838,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699541</v>
+        <v>119699664</v>
       </c>
       <c r="B209" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26850,25 +26850,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577460</v>
+        <v>577505</v>
       </c>
       <c r="R209" t="n">
-        <v>6559048</v>
+        <v>6559057</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26914,6 +26914,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26940,10 +26945,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119699664</v>
+        <v>119698814</v>
       </c>
       <c r="B210" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26952,41 +26957,46 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577505</v>
+        <v>577415</v>
       </c>
       <c r="R210" t="n">
-        <v>6559057</v>
+        <v>6559187</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27016,11 +27026,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27047,10 +27052,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119698814</v>
+        <v>119699541</v>
       </c>
       <c r="B211" t="n">
-        <v>5189</v>
+        <v>91832</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27059,46 +27064,41 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577415</v>
+        <v>577460</v>
       </c>
       <c r="R211" t="n">
-        <v>6559187</v>
+        <v>6559048</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27687,10 +27687,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119699553</v>
+        <v>119699969</v>
       </c>
       <c r="B217" t="n">
-        <v>91842</v>
+        <v>91840</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -27699,25 +27699,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>788</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -27727,10 +27727,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>577460</v>
+        <v>577561</v>
       </c>
       <c r="R217" t="n">
-        <v>6559048</v>
+        <v>6558994</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -27789,10 +27789,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119699969</v>
+        <v>119702969</v>
       </c>
       <c r="B218" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -27801,25 +27801,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -27829,10 +27829,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>577561</v>
+        <v>577658</v>
       </c>
       <c r="R218" t="n">
-        <v>6558994</v>
+        <v>6558983</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -27891,10 +27891,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119702969</v>
+        <v>119699553</v>
       </c>
       <c r="B219" t="n">
-        <v>97907</v>
+        <v>91842</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -27903,25 +27903,25 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -27931,10 +27931,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>577658</v>
+        <v>577460</v>
       </c>
       <c r="R219" t="n">
-        <v>6558983</v>
+        <v>6559048</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -26838,10 +26838,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699664</v>
+        <v>119699541</v>
       </c>
       <c r="B209" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26850,25 +26850,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577505</v>
+        <v>577460</v>
       </c>
       <c r="R209" t="n">
-        <v>6559057</v>
+        <v>6559048</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26914,11 +26914,6 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26945,10 +26940,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119698814</v>
+        <v>119699664</v>
       </c>
       <c r="B210" t="n">
-        <v>5189</v>
+        <v>97907</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26957,46 +26952,41 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
-      <c r="M210" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577415</v>
+        <v>577505</v>
       </c>
       <c r="R210" t="n">
-        <v>6559187</v>
+        <v>6559057</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27026,6 +27016,11 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27052,10 +27047,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119699541</v>
+        <v>119698814</v>
       </c>
       <c r="B211" t="n">
-        <v>91832</v>
+        <v>5189</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27064,41 +27059,46 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4361</v>
+        <v>105930</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577460</v>
+        <v>577415</v>
       </c>
       <c r="R211" t="n">
-        <v>6559048</v>
+        <v>6559187</v>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27993,10 +27993,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119698812</v>
+        <v>119701851</v>
       </c>
       <c r="B220" t="n">
-        <v>5169</v>
+        <v>91861</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -28009,42 +28009,37 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577415</v>
+        <v>577273</v>
       </c>
       <c r="R220" t="n">
-        <v>6559187</v>
+        <v>6559028</v>
       </c>
       <c r="S220" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28100,10 +28095,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701851</v>
+        <v>119701751</v>
       </c>
       <c r="B221" t="n">
-        <v>91861</v>
+        <v>97907</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -28112,25 +28107,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -28140,10 +28135,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577273</v>
+        <v>577203</v>
       </c>
       <c r="R221" t="n">
-        <v>6559028</v>
+        <v>6558998</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28202,7 +28197,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119701751</v>
+        <v>119701628</v>
       </c>
       <c r="B222" t="n">
         <v>97907</v>
@@ -28242,10 +28237,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577203</v>
+        <v>577186</v>
       </c>
       <c r="R222" t="n">
-        <v>6558998</v>
+        <v>6558951</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28304,10 +28299,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119701628</v>
+        <v>119698812</v>
       </c>
       <c r="B223" t="n">
-        <v>97907</v>
+        <v>5169</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28316,41 +28311,46 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577186</v>
+        <v>577415</v>
       </c>
       <c r="R223" t="n">
-        <v>6558951</v>
+        <v>6559187</v>
       </c>
       <c r="S223" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -26838,10 +26838,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119699541</v>
+        <v>119699664</v>
       </c>
       <c r="B209" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -26850,25 +26850,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -26878,10 +26878,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>577460</v>
+        <v>577505</v>
       </c>
       <c r="R209" t="n">
-        <v>6559048</v>
+        <v>6559057</v>
       </c>
       <c r="S209" t="n">
         <v>15</v>
@@ -26914,6 +26914,11 @@
       <c r="AA209" t="inlineStr">
         <is>
           <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26940,10 +26945,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119699664</v>
+        <v>119698814</v>
       </c>
       <c r="B210" t="n">
-        <v>97907</v>
+        <v>5189</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -26952,41 +26957,46 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P210" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>577505</v>
+        <v>577415</v>
       </c>
       <c r="R210" t="n">
-        <v>6559057</v>
+        <v>6559187</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -27016,11 +27026,6 @@
       <c r="AA210" t="inlineStr">
         <is>
           <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Knärot i avverkningsamält och underröjt område</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -27047,10 +27052,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119698814</v>
+        <v>119699541</v>
       </c>
       <c r="B211" t="n">
-        <v>5189</v>
+        <v>91832</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -27059,46 +27064,41 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>105930</v>
+        <v>4361</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="M211" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P211" t="inlineStr">
         <is>
           <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>577415</v>
+        <v>577460</v>
       </c>
       <c r="R211" t="n">
-        <v>6559187</v>
+        <v>6559048</v>
       </c>
       <c r="S211" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -27993,10 +27993,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119701851</v>
+        <v>119698812</v>
       </c>
       <c r="B220" t="n">
-        <v>91861</v>
+        <v>5169</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -28009,37 +28009,42 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>577273</v>
+        <v>577415</v>
       </c>
       <c r="R220" t="n">
-        <v>6559028</v>
+        <v>6559187</v>
       </c>
       <c r="S220" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -28095,10 +28100,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119701751</v>
+        <v>119701851</v>
       </c>
       <c r="B221" t="n">
-        <v>97907</v>
+        <v>91861</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -28107,25 +28112,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -28135,10 +28140,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>577203</v>
+        <v>577273</v>
       </c>
       <c r="R221" t="n">
-        <v>6558998</v>
+        <v>6559028</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -28197,7 +28202,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119701628</v>
+        <v>119701751</v>
       </c>
       <c r="B222" t="n">
         <v>97907</v>
@@ -28237,10 +28242,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>577186</v>
+        <v>577203</v>
       </c>
       <c r="R222" t="n">
-        <v>6558951</v>
+        <v>6558998</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -28299,10 +28304,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119698812</v>
+        <v>119701628</v>
       </c>
       <c r="B223" t="n">
-        <v>5169</v>
+        <v>97907</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -28311,46 +28316,41 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>577415</v>
+        <v>577186</v>
       </c>
       <c r="R223" t="n">
-        <v>6559187</v>
+        <v>6558951</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -13632,7 +13632,7 @@
         <v>118747517</v>
       </c>
       <c r="B103" t="n">
-        <v>91842</v>
+        <v>91860</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -29021,7 +29021,7 @@
         <v>120223306</v>
       </c>
       <c r="B230" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY230"/>
+  <dimension ref="A1:AY240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29139,6 +29139,1110 @@
       </c>
       <c r="AY230" t="inlineStr"/>
     </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>120421211</v>
+      </c>
+      <c r="B231" t="n">
+        <v>91876</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr"/>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q231" t="n">
+        <v>577470</v>
+      </c>
+      <c r="R231" t="n">
+        <v>6559035</v>
+      </c>
+      <c r="S231" t="n">
+        <v>10</v>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG231" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT231" t="inlineStr"/>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>120421075</v>
+      </c>
+      <c r="B232" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>577478</v>
+      </c>
+      <c r="R232" t="n">
+        <v>6559050</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>120421609</v>
+      </c>
+      <c r="B233" t="n">
+        <v>91876</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>577383</v>
+      </c>
+      <c r="R233" t="n">
+        <v>6559108</v>
+      </c>
+      <c r="S233" t="n">
+        <v>7</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>120421513</v>
+      </c>
+      <c r="B234" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>577423</v>
+      </c>
+      <c r="R234" t="n">
+        <v>6559071</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>120420939</v>
+      </c>
+      <c r="B235" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>577457</v>
+      </c>
+      <c r="R235" t="n">
+        <v>6559199</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>120420928</v>
+      </c>
+      <c r="B236" t="n">
+        <v>91881</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>577455</v>
+      </c>
+      <c r="R236" t="n">
+        <v>6559209</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z236" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB236" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>120420968</v>
+      </c>
+      <c r="B237" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>577460</v>
+      </c>
+      <c r="R237" t="n">
+        <v>6559188</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>120421265</v>
+      </c>
+      <c r="B238" t="n">
+        <v>90351</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>577449</v>
+      </c>
+      <c r="R238" t="n">
+        <v>6559055</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Kaiko Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>120421230</v>
+      </c>
+      <c r="B239" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>577476</v>
+      </c>
+      <c r="R239" t="n">
+        <v>6559024</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB239" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>120421495</v>
+      </c>
+      <c r="B240" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Stenbrottet, Stenbrottet, Srm</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>577419</v>
+      </c>
+      <c r="R240" t="n">
+        <v>6559075</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Malin Max Nordgren</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29141,10 +29141,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>120421211</v>
+        <v>120421513</v>
       </c>
       <c r="B231" t="n">
-        <v>91876</v>
+        <v>97930</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -29153,25 +29153,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -29181,10 +29181,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>577470</v>
+        <v>577423</v>
       </c>
       <c r="R231" t="n">
-        <v>6559035</v>
+        <v>6559071</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -29216,7 +29216,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -29226,7 +29226,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29253,7 +29253,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120421075</v>
+        <v>120421265</v>
       </c>
       <c r="B232" t="n">
         <v>90351</v>
@@ -29293,10 +29293,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>577478</v>
+        <v>577449</v>
       </c>
       <c r="R232" t="n">
-        <v>6559050</v>
+        <v>6559055</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -29326,19 +29326,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z232" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB232" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -29353,22 +29343,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120421609</v>
+        <v>120421230</v>
       </c>
       <c r="B233" t="n">
-        <v>91876</v>
+        <v>57236</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29381,37 +29371,41 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4368</v>
+        <v>100067</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P233" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>577383</v>
+        <v>577476</v>
       </c>
       <c r="R233" t="n">
-        <v>6559108</v>
+        <v>6559024</v>
       </c>
       <c r="S233" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -29438,9 +29432,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB233" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -29455,22 +29459,22 @@
       <c r="AT233" t="inlineStr"/>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120421513</v>
+        <v>120421609</v>
       </c>
       <c r="B234" t="n">
-        <v>97930</v>
+        <v>91876</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29479,25 +29483,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -29507,13 +29511,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>577423</v>
+        <v>577383</v>
       </c>
       <c r="R234" t="n">
-        <v>6559071</v>
+        <v>6559108</v>
       </c>
       <c r="S234" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -29540,19 +29544,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z234" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB234" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -29567,22 +29561,22 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120420939</v>
+        <v>120421075</v>
       </c>
       <c r="B235" t="n">
-        <v>91881</v>
+        <v>90351</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -29591,25 +29585,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5966</v>
+        <v>3215</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -29619,10 +29613,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>577457</v>
+        <v>577478</v>
       </c>
       <c r="R235" t="n">
-        <v>6559199</v>
+        <v>6559050</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -29654,7 +29648,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -29664,7 +29658,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -29691,10 +29685,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120420928</v>
+        <v>120421495</v>
       </c>
       <c r="B236" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29703,25 +29697,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29731,10 +29725,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577455</v>
+        <v>577419</v>
       </c>
       <c r="R236" t="n">
-        <v>6559209</v>
+        <v>6559075</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29766,7 +29760,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29776,7 +29770,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29803,10 +29797,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120420968</v>
+        <v>120420939</v>
       </c>
       <c r="B237" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29815,25 +29809,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29843,10 +29837,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>577460</v>
+        <v>577457</v>
       </c>
       <c r="R237" t="n">
-        <v>6559188</v>
+        <v>6559199</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29878,7 +29872,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -29888,7 +29882,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29915,10 +29909,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120421265</v>
+        <v>120420968</v>
       </c>
       <c r="B238" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29927,25 +29921,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -29955,10 +29949,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>577449</v>
+        <v>577460</v>
       </c>
       <c r="R238" t="n">
-        <v>6559055</v>
+        <v>6559188</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -29988,9 +29982,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30005,22 +30009,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120421230</v>
+        <v>120421211</v>
       </c>
       <c r="B239" t="n">
-        <v>57236</v>
+        <v>91876</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30033,38 +30037,34 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100067</v>
+        <v>4368</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577476</v>
+        <v>577470</v>
       </c>
       <c r="R239" t="n">
-        <v>6559024</v>
+        <v>6559035</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30133,10 +30133,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120421495</v>
+        <v>120420928</v>
       </c>
       <c r="B240" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -30145,25 +30145,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -30173,10 +30173,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>577419</v>
+        <v>577455</v>
       </c>
       <c r="R240" t="n">
-        <v>6559075</v>
+        <v>6559209</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -30208,7 +30208,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD240" t="b">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29141,10 +29141,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>120421513</v>
+        <v>120421609</v>
       </c>
       <c r="B231" t="n">
-        <v>97930</v>
+        <v>91876</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -29153,25 +29153,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -29181,13 +29181,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>577423</v>
+        <v>577383</v>
       </c>
       <c r="R231" t="n">
-        <v>6559071</v>
+        <v>6559108</v>
       </c>
       <c r="S231" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -29214,19 +29214,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z231" t="inlineStr">
-        <is>
-          <t>15:16</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB231" t="inlineStr">
-        <is>
-          <t>15:16</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29241,22 +29231,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120421265</v>
+        <v>120420939</v>
       </c>
       <c r="B232" t="n">
-        <v>90351</v>
+        <v>91881</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29265,25 +29255,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29293,10 +29283,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>577449</v>
+        <v>577457</v>
       </c>
       <c r="R232" t="n">
-        <v>6559055</v>
+        <v>6559199</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -29326,9 +29316,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB232" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -29343,22 +29343,22 @@
       <c r="AT232" t="inlineStr"/>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120421230</v>
+        <v>120420968</v>
       </c>
       <c r="B233" t="n">
-        <v>57236</v>
+        <v>97930</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29367,42 +29367,38 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>100067</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
       <c r="P233" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>577476</v>
+        <v>577460</v>
       </c>
       <c r="R233" t="n">
-        <v>6559024</v>
+        <v>6559188</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -29434,7 +29430,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -29444,7 +29440,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -29471,10 +29467,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120421609</v>
+        <v>120421513</v>
       </c>
       <c r="B234" t="n">
-        <v>91876</v>
+        <v>97930</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29483,25 +29479,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -29511,13 +29507,13 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>577383</v>
+        <v>577423</v>
       </c>
       <c r="R234" t="n">
-        <v>6559108</v>
+        <v>6559071</v>
       </c>
       <c r="S234" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -29544,9 +29540,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB234" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -29561,19 +29567,19 @@
       <c r="AT234" t="inlineStr"/>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120421075</v>
+        <v>120421265</v>
       </c>
       <c r="B235" t="n">
         <v>90351</v>
@@ -29613,10 +29619,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>577478</v>
+        <v>577449</v>
       </c>
       <c r="R235" t="n">
-        <v>6559050</v>
+        <v>6559055</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -29646,19 +29652,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>14:48</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>14:48</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -29673,22 +29669,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120421495</v>
+        <v>120421075</v>
       </c>
       <c r="B236" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29697,25 +29693,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29725,10 +29721,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577419</v>
+        <v>577478</v>
       </c>
       <c r="R236" t="n">
-        <v>6559075</v>
+        <v>6559050</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29760,7 +29756,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29770,7 +29766,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29797,10 +29793,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120420939</v>
+        <v>120421495</v>
       </c>
       <c r="B237" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29809,25 +29805,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29837,10 +29833,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>577457</v>
+        <v>577419</v>
       </c>
       <c r="R237" t="n">
-        <v>6559199</v>
+        <v>6559075</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29872,7 +29868,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -29882,7 +29878,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29909,10 +29905,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120420968</v>
+        <v>120421230</v>
       </c>
       <c r="B238" t="n">
-        <v>97930</v>
+        <v>57236</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29921,38 +29917,42 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>577460</v>
+        <v>577476</v>
       </c>
       <c r="R238" t="n">
-        <v>6559188</v>
+        <v>6559024</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -29984,7 +29984,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30021,10 +30021,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120421211</v>
+        <v>120420928</v>
       </c>
       <c r="B239" t="n">
-        <v>91876</v>
+        <v>91881</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30037,21 +30037,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4368</v>
+        <v>5966</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -30061,10 +30061,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577470</v>
+        <v>577455</v>
       </c>
       <c r="R239" t="n">
-        <v>6559035</v>
+        <v>6559209</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30096,7 +30096,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30133,10 +30133,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120420928</v>
+        <v>120421211</v>
       </c>
       <c r="B240" t="n">
-        <v>91881</v>
+        <v>91876</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -30149,21 +30149,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -30173,10 +30173,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>577455</v>
+        <v>577470</v>
       </c>
       <c r="R240" t="n">
-        <v>6559209</v>
+        <v>6559035</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -30208,7 +30208,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD240" t="b">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29243,10 +29243,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120420939</v>
+        <v>120421513</v>
       </c>
       <c r="B232" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29255,25 +29255,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29283,10 +29283,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>577457</v>
+        <v>577423</v>
       </c>
       <c r="R232" t="n">
-        <v>6559199</v>
+        <v>6559071</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -29355,10 +29355,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120420968</v>
+        <v>120421075</v>
       </c>
       <c r="B233" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29367,25 +29367,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -29395,10 +29395,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>577460</v>
+        <v>577478</v>
       </c>
       <c r="R233" t="n">
-        <v>6559188</v>
+        <v>6559050</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -29430,7 +29430,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -29440,7 +29440,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -29467,10 +29467,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120421513</v>
+        <v>120421211</v>
       </c>
       <c r="B234" t="n">
-        <v>97930</v>
+        <v>91876</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29479,25 +29479,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>220787</v>
+        <v>4368</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -29507,10 +29507,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>577423</v>
+        <v>577470</v>
       </c>
       <c r="R234" t="n">
-        <v>6559071</v>
+        <v>6559035</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -29542,7 +29542,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -29579,10 +29579,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120421265</v>
+        <v>120420928</v>
       </c>
       <c r="B235" t="n">
-        <v>90351</v>
+        <v>91881</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -29591,25 +29591,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -29619,10 +29619,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>577449</v>
+        <v>577455</v>
       </c>
       <c r="R235" t="n">
-        <v>6559055</v>
+        <v>6559209</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -29652,9 +29652,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -29669,22 +29679,22 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120421075</v>
+        <v>120420939</v>
       </c>
       <c r="B236" t="n">
-        <v>90351</v>
+        <v>91881</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29693,25 +29703,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29721,10 +29731,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577478</v>
+        <v>577457</v>
       </c>
       <c r="R236" t="n">
-        <v>6559050</v>
+        <v>6559199</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29756,7 +29766,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29766,7 +29776,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29793,7 +29803,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120421495</v>
+        <v>120420968</v>
       </c>
       <c r="B237" t="n">
         <v>97930</v>
@@ -29833,10 +29843,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>577419</v>
+        <v>577460</v>
       </c>
       <c r="R237" t="n">
-        <v>6559075</v>
+        <v>6559188</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29868,7 +29878,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -29878,7 +29888,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29905,10 +29915,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120421230</v>
+        <v>120421495</v>
       </c>
       <c r="B238" t="n">
-        <v>57236</v>
+        <v>97930</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29917,42 +29927,38 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>100067</v>
+        <v>220787</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>577476</v>
+        <v>577419</v>
       </c>
       <c r="R238" t="n">
-        <v>6559024</v>
+        <v>6559075</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -29984,7 +29990,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -29994,7 +30000,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30021,10 +30027,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120420928</v>
+        <v>120421230</v>
       </c>
       <c r="B239" t="n">
-        <v>91881</v>
+        <v>57236</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30037,34 +30043,38 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5966</v>
+        <v>100067</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577455</v>
+        <v>577476</v>
       </c>
       <c r="R239" t="n">
-        <v>6559209</v>
+        <v>6559024</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30096,7 +30106,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30106,7 +30116,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30133,10 +30143,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120421211</v>
+        <v>120421265</v>
       </c>
       <c r="B240" t="n">
-        <v>91876</v>
+        <v>90351</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -30145,25 +30155,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4368</v>
+        <v>3215</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -30173,10 +30183,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>577470</v>
+        <v>577449</v>
       </c>
       <c r="R240" t="n">
-        <v>6559035</v>
+        <v>6559055</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -30206,19 +30216,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -30233,12 +30233,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29243,10 +29243,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120421513</v>
+        <v>120421075</v>
       </c>
       <c r="B232" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29255,25 +29255,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29283,10 +29283,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>577423</v>
+        <v>577478</v>
       </c>
       <c r="R232" t="n">
-        <v>6559071</v>
+        <v>6559050</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -29328,7 +29328,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -29355,10 +29355,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120421075</v>
+        <v>120420928</v>
       </c>
       <c r="B233" t="n">
-        <v>90351</v>
+        <v>91881</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29367,25 +29367,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -29395,10 +29395,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>577478</v>
+        <v>577455</v>
       </c>
       <c r="R233" t="n">
-        <v>6559050</v>
+        <v>6559209</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -29430,7 +29430,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -29440,7 +29440,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -29467,10 +29467,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120421211</v>
+        <v>120421230</v>
       </c>
       <c r="B234" t="n">
-        <v>91876</v>
+        <v>57236</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29483,34 +29483,38 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4368</v>
+        <v>100067</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P234" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>577470</v>
+        <v>577476</v>
       </c>
       <c r="R234" t="n">
-        <v>6559035</v>
+        <v>6559024</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -29542,7 +29546,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -29552,7 +29556,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -29579,10 +29583,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120420928</v>
+        <v>120421211</v>
       </c>
       <c r="B235" t="n">
-        <v>91881</v>
+        <v>91876</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -29595,21 +29599,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -29619,10 +29623,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>577455</v>
+        <v>577470</v>
       </c>
       <c r="R235" t="n">
-        <v>6559209</v>
+        <v>6559035</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -29654,7 +29658,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -29664,7 +29668,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -29691,10 +29695,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120420939</v>
+        <v>120421513</v>
       </c>
       <c r="B236" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29703,25 +29707,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29731,10 +29735,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577457</v>
+        <v>577423</v>
       </c>
       <c r="R236" t="n">
-        <v>6559199</v>
+        <v>6559071</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29766,7 +29770,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29776,7 +29780,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29803,10 +29807,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120420968</v>
+        <v>120420939</v>
       </c>
       <c r="B237" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29815,25 +29819,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29843,10 +29847,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>577460</v>
+        <v>577457</v>
       </c>
       <c r="R237" t="n">
-        <v>6559188</v>
+        <v>6559199</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29878,7 +29882,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -29888,7 +29892,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -30027,10 +30031,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120421230</v>
+        <v>120420968</v>
       </c>
       <c r="B239" t="n">
-        <v>57236</v>
+        <v>97930</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30039,42 +30043,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100067</v>
+        <v>220787</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577476</v>
+        <v>577460</v>
       </c>
       <c r="R239" t="n">
-        <v>6559024</v>
+        <v>6559188</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD239" t="b">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29141,10 +29141,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>120421609</v>
+        <v>120421513</v>
       </c>
       <c r="B231" t="n">
-        <v>91876</v>
+        <v>97930</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -29153,25 +29153,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4368</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -29181,13 +29181,13 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>577383</v>
+        <v>577423</v>
       </c>
       <c r="R231" t="n">
-        <v>6559108</v>
+        <v>6559071</v>
       </c>
       <c r="S231" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -29214,9 +29214,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -29231,22 +29241,22 @@
       <c r="AT231" t="inlineStr"/>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>120421075</v>
+        <v>120420928</v>
       </c>
       <c r="B232" t="n">
-        <v>90351</v>
+        <v>91881</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -29255,25 +29265,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3215</v>
+        <v>5966</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -29283,10 +29293,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>577478</v>
+        <v>577455</v>
       </c>
       <c r="R232" t="n">
-        <v>6559050</v>
+        <v>6559209</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -29318,7 +29328,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -29328,7 +29338,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -29355,10 +29365,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120420928</v>
+        <v>120421211</v>
       </c>
       <c r="B233" t="n">
-        <v>91881</v>
+        <v>91876</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -29371,21 +29381,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5966</v>
+        <v>4368</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -29395,10 +29405,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>577455</v>
+        <v>577470</v>
       </c>
       <c r="R233" t="n">
-        <v>6559209</v>
+        <v>6559035</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -29430,7 +29440,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -29440,7 +29450,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -29467,10 +29477,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120421230</v>
+        <v>120421075</v>
       </c>
       <c r="B234" t="n">
-        <v>57236</v>
+        <v>90351</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -29479,42 +29489,38 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>100067</v>
+        <v>3215</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>577476</v>
+        <v>577478</v>
       </c>
       <c r="R234" t="n">
-        <v>6559024</v>
+        <v>6559050</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -29546,7 +29552,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -29556,7 +29562,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -29583,7 +29589,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120421211</v>
+        <v>120421609</v>
       </c>
       <c r="B235" t="n">
         <v>91876</v>
@@ -29623,13 +29629,13 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>577470</v>
+        <v>577383</v>
       </c>
       <c r="R235" t="n">
-        <v>6559035</v>
+        <v>6559108</v>
       </c>
       <c r="S235" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -29656,19 +29662,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z235" t="inlineStr">
-        <is>
-          <t>14:55</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB235" t="inlineStr">
-        <is>
-          <t>14:55</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -29683,19 +29679,19 @@
       <c r="AT235" t="inlineStr"/>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120421513</v>
+        <v>120421495</v>
       </c>
       <c r="B236" t="n">
         <v>97930</v>
@@ -29735,10 +29731,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577423</v>
+        <v>577419</v>
       </c>
       <c r="R236" t="n">
-        <v>6559071</v>
+        <v>6559075</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29770,7 +29766,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29780,7 +29776,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29919,10 +29915,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120421495</v>
+        <v>120421265</v>
       </c>
       <c r="B238" t="n">
-        <v>97930</v>
+        <v>90351</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29931,25 +29927,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -29959,10 +29955,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>577419</v>
+        <v>577449</v>
       </c>
       <c r="R238" t="n">
-        <v>6559075</v>
+        <v>6559055</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -29992,19 +29988,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z238" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB238" t="inlineStr">
-        <is>
-          <t>15:15</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30019,22 +30005,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120420968</v>
+        <v>120421230</v>
       </c>
       <c r="B239" t="n">
-        <v>97930</v>
+        <v>57236</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30043,38 +30029,42 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>220787</v>
+        <v>100067</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P239" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577460</v>
+        <v>577476</v>
       </c>
       <c r="R239" t="n">
-        <v>6559188</v>
+        <v>6559024</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30106,7 +30096,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -30116,7 +30106,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30143,10 +30133,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120421265</v>
+        <v>120420968</v>
       </c>
       <c r="B240" t="n">
-        <v>90351</v>
+        <v>97930</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -30155,25 +30145,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -30183,10 +30173,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>577449</v>
+        <v>577460</v>
       </c>
       <c r="R240" t="n">
-        <v>6559055</v>
+        <v>6559188</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -30216,9 +30206,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB240" t="inlineStr">
+        <is>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -30233,12 +30233,12 @@
       <c r="AT240" t="inlineStr"/>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -29691,10 +29691,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120421495</v>
+        <v>120420939</v>
       </c>
       <c r="B236" t="n">
-        <v>97930</v>
+        <v>91881</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -29703,25 +29703,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -29731,10 +29731,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>577419</v>
+        <v>577457</v>
       </c>
       <c r="R236" t="n">
-        <v>6559075</v>
+        <v>6559199</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -29803,10 +29803,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120420939</v>
+        <v>120421495</v>
       </c>
       <c r="B237" t="n">
-        <v>91881</v>
+        <v>97930</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -29815,25 +29815,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -29843,10 +29843,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>577457</v>
+        <v>577419</v>
       </c>
       <c r="R237" t="n">
-        <v>6559199</v>
+        <v>6559075</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -29878,7 +29878,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -29888,7 +29888,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -29915,10 +29915,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120421265</v>
+        <v>120421230</v>
       </c>
       <c r="B238" t="n">
-        <v>90351</v>
+        <v>57236</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -29927,38 +29927,42 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3215</v>
+        <v>100067</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P238" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>577449</v>
+        <v>577476</v>
       </c>
       <c r="R238" t="n">
-        <v>6559055</v>
+        <v>6559024</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -29988,9 +29992,19 @@
           <t>2024-10-15</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AB238" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -30005,22 +30019,22 @@
       <c r="AT238" t="inlineStr"/>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>Kaiko Gustafsson</t>
+          <t>Malin Max Nordgren</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120421230</v>
+        <v>120421265</v>
       </c>
       <c r="B239" t="n">
-        <v>57236</v>
+        <v>90351</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -30029,42 +30043,38 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>100067</v>
+        <v>3215</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Stenbrottet, Stenbrottet, Srm</t>
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>577476</v>
+        <v>577449</v>
       </c>
       <c r="R239" t="n">
-        <v>6559024</v>
+        <v>6559055</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -30094,19 +30104,9 @@
           <t>2024-10-15</t>
         </is>
       </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -30121,12 +30121,12 @@
       <c r="AT239" t="inlineStr"/>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>Malin Max Nordgren</t>
+          <t>Kaiko Gustafsson</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -8803,7 +8803,7 @@
         <v>118607355</v>
       </c>
       <c r="B65" t="n">
-        <v>90181</v>
+        <v>90191</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -30245,10 +30245,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120841364</v>
+        <v>120841150</v>
       </c>
       <c r="B241" t="n">
-        <v>97028</v>
+        <v>92008</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -30257,25 +30257,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>221946</v>
+        <v>5966</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -30283,23 +30283,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J241" t="inlineStr"/>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Strandmossen, Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>577546</v>
+        <v>577624</v>
       </c>
       <c r="R241" t="n">
-        <v>6559150</v>
+        <v>6559164</v>
       </c>
       <c r="S241" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -30328,7 +30329,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -30338,7 +30339,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -30349,26 +30350,31 @@
       </c>
       <c r="AG241" t="b">
         <v>0</v>
+      </c>
+      <c r="AH241" t="inlineStr">
+        <is>
+          <t>Hällmarkstallskog</t>
+        </is>
       </c>
       <c r="AT241" t="inlineStr"/>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Staffan Petré</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120841150</v>
+        <v>120841364</v>
       </c>
       <c r="B242" t="n">
-        <v>91998</v>
+        <v>97038</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -30377,25 +30383,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5966</v>
+        <v>221946</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -30403,24 +30409,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Strandmossen, Strandmossen, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>577624</v>
+        <v>577546</v>
       </c>
       <c r="R242" t="n">
-        <v>6559164</v>
+        <v>6559150</v>
       </c>
       <c r="S242" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -30449,7 +30454,7 @@
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -30459,7 +30464,7 @@
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -30470,21 +30475,16 @@
       </c>
       <c r="AG242" t="b">
         <v>0</v>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>Hällmarkstallskog</t>
-        </is>
       </c>
       <c r="AT242" t="inlineStr"/>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>Staffan Petré</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
@@ -30494,7 +30494,7 @@
         <v>120420904</v>
       </c>
       <c r="B243" t="n">
-        <v>91991</v>
+        <v>92001</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -8803,7 +8803,7 @@
         <v>118607355</v>
       </c>
       <c r="B65" t="n">
-        <v>90191</v>
+        <v>90203</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -30494,7 +30494,7 @@
         <v>120420904</v>
       </c>
       <c r="B243" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30494,7 +30494,7 @@
         <v>120420904</v>
       </c>
       <c r="B243" t="n">
-        <v>92013</v>
+        <v>92014</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30494,7 +30494,7 @@
         <v>120420904</v>
       </c>
       <c r="B243" t="n">
-        <v>92014</v>
+        <v>92017</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -19445,11 +19445,11 @@
         <v>118902324</v>
       </c>
       <c r="B148" t="n">
-        <v>91811</v>
+        <v>92006</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -19445,7 +19445,7 @@
         <v>118902324</v>
       </c>
       <c r="B148" t="n">
-        <v>92006</v>
+        <v>92020</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -19445,7 +19445,7 @@
         <v>118902324</v>
       </c>
       <c r="B148" t="n">
-        <v>92020</v>
+        <v>92022</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -19445,7 +19445,7 @@
         <v>118902324</v>
       </c>
       <c r="B148" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -19445,7 +19445,7 @@
         <v>118902324</v>
       </c>
       <c r="B148" t="n">
-        <v>92023</v>
+        <v>92032</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -5712,7 +5712,7 @@
         <v>118607818</v>
       </c>
       <c r="B41" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>118606437</v>
       </c>
       <c r="B42" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>118608908</v>
       </c>
       <c r="B52" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -5727,11 +5727,6 @@
       <c r="E41" t="n">
         <v>100138</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -5856,11 +5851,6 @@
       <c r="E42" t="n">
         <v>100138</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>
@@ -7126,11 +7116,6 @@
       </c>
       <c r="E52" t="n">
         <v>100138</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -5712,7 +5712,7 @@
         <v>118607818</v>
       </c>
       <c r="B41" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5726,6 +5726,11 @@
       </c>
       <c r="E41" t="n">
         <v>100138</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -5836,7 +5841,7 @@
         <v>118606437</v>
       </c>
       <c r="B42" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5850,6 +5855,11 @@
       </c>
       <c r="E42" t="n">
         <v>100138</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -7102,7 +7112,7 @@
         <v>118608908</v>
       </c>
       <c r="B52" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7116,6 +7126,11 @@
       </c>
       <c r="E52" t="n">
         <v>100138</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -20229,11 +20229,11 @@
         <v>119013293</v>
       </c>
       <c r="B155" t="n">
-        <v>57324</v>
+        <v>57494</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,11 +27157,11 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>91858</v>
+        <v>92251</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -28409,11 +28409,11 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>91858</v>
+        <v>92251</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -20229,7 +20229,7 @@
         <v>119013293</v>
       </c>
       <c r="B155" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -27157,7 +27157,7 @@
         <v>119699345</v>
       </c>
       <c r="B212" t="n">
-        <v>92287</v>
+        <v>92289</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>119699197</v>
       </c>
       <c r="B224" t="n">
-        <v>92287</v>
+        <v>92289</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY243"/>
+  <dimension ref="A1:AY244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30591,6 +30591,126 @@
       </c>
       <c r="AY243" t="inlineStr"/>
     </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>118531013</v>
+      </c>
+      <c r="B244" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>577088</v>
+      </c>
+      <c r="R244" t="n">
+        <v>6558794</v>
+      </c>
+      <c r="S244" t="n">
+        <v>2</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF244" t="inlineStr"/>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY244"/>
+  <dimension ref="A1:AY262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30711,6 +30711,2150 @@
       </c>
       <c r="AY244" t="inlineStr"/>
     </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>128078400</v>
+      </c>
+      <c r="B245" t="n">
+        <v>91314</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>577571</v>
+      </c>
+      <c r="R245" t="n">
+        <v>6558993</v>
+      </c>
+      <c r="S245" t="n">
+        <v>7</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>128077874</v>
+      </c>
+      <c r="B246" t="n">
+        <v>92641</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>788</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>577474</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6559047</v>
+      </c>
+      <c r="S246" t="n">
+        <v>8</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Hanna Nordin, Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>128079171</v>
+      </c>
+      <c r="B247" t="n">
+        <v>92651</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>577559</v>
+      </c>
+      <c r="R247" t="n">
+        <v>6558900</v>
+      </c>
+      <c r="S247" t="n">
+        <v>5</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>Hundratals fruktkroppar, färska och fjolårets. På en yta av ca 30 kvm</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>128078876</v>
+      </c>
+      <c r="B248" t="n">
+        <v>92657</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>577552</v>
+      </c>
+      <c r="R248" t="n">
+        <v>6558912</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>128080803</v>
+      </c>
+      <c r="B249" t="n">
+        <v>92667</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>577304</v>
+      </c>
+      <c r="R249" t="n">
+        <v>6559008</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>128080627</v>
+      </c>
+      <c r="B250" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>577344</v>
+      </c>
+      <c r="R250" t="n">
+        <v>6559035</v>
+      </c>
+      <c r="S250" t="n">
+        <v>5</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>128078577</v>
+      </c>
+      <c r="B251" t="n">
+        <v>101553</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Djupadroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>577638</v>
+      </c>
+      <c r="R251" t="n">
+        <v>6558943</v>
+      </c>
+      <c r="S251" t="n">
+        <v>2</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>128078005</v>
+      </c>
+      <c r="B252" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>577493</v>
+      </c>
+      <c r="R252" t="n">
+        <v>6559036</v>
+      </c>
+      <c r="S252" t="n">
+        <v>5</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>Hundratal plantor samt överblimmade exemplar.</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>128080535</v>
+      </c>
+      <c r="B253" t="n">
+        <v>92667</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>577318</v>
+      </c>
+      <c r="R253" t="n">
+        <v>6559001</v>
+      </c>
+      <c r="S253" t="n">
+        <v>4</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>128079953</v>
+      </c>
+      <c r="B254" t="n">
+        <v>92633</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>577370</v>
+      </c>
+      <c r="R254" t="n">
+        <v>6559005</v>
+      </c>
+      <c r="S254" t="n">
+        <v>4</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Hanna Nordin, Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>128081735</v>
+      </c>
+      <c r="B255" t="n">
+        <v>92667</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>577353</v>
+      </c>
+      <c r="R255" t="n">
+        <v>6559120</v>
+      </c>
+      <c r="S255" t="n">
+        <v>4</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>128079597</v>
+      </c>
+      <c r="B256" t="n">
+        <v>92651</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>577522</v>
+      </c>
+      <c r="R256" t="n">
+        <v>6558938</v>
+      </c>
+      <c r="S256" t="n">
+        <v>4</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Hanna Nordin, Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>128078152</v>
+      </c>
+      <c r="B257" t="n">
+        <v>92667</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>577538</v>
+      </c>
+      <c r="R257" t="n">
+        <v>6559023</v>
+      </c>
+      <c r="S257" t="n">
+        <v>4</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>128079606</v>
+      </c>
+      <c r="B258" t="n">
+        <v>96069</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>577523</v>
+      </c>
+      <c r="R258" t="n">
+        <v>6558924</v>
+      </c>
+      <c r="S258" t="n">
+        <v>7</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>Kudde om ca 90 cm hög. Flera höga kuddar på hällmarken.</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>128080139</v>
+      </c>
+      <c r="B259" t="n">
+        <v>92631</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>577344</v>
+      </c>
+      <c r="R259" t="n">
+        <v>6559035</v>
+      </c>
+      <c r="S259" t="n">
+        <v>5</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>128078836</v>
+      </c>
+      <c r="B260" t="n">
+        <v>92667</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>577565</v>
+      </c>
+      <c r="R260" t="n">
+        <v>6558921</v>
+      </c>
+      <c r="S260" t="n">
+        <v>4</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Hanna Nordin, Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>128078589</v>
+      </c>
+      <c r="B261" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>577614</v>
+      </c>
+      <c r="R261" t="n">
+        <v>6558989</v>
+      </c>
+      <c r="S261" t="n">
+        <v>5</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>128078494</v>
+      </c>
+      <c r="B262" t="n">
+        <v>98467</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Djupadroget, Srm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>577630</v>
+      </c>
+      <c r="R262" t="n">
+        <v>6558954</v>
+      </c>
+      <c r="S262" t="n">
+        <v>13</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Hanna Nordin</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -32383,10 +32383,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128080139</v>
+        <v>128078836</v>
       </c>
       <c r="B259" t="n">
-        <v>92631</v>
+        <v>92667</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32394,44 +32394,52 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>577344</v>
+        <v>577565</v>
       </c>
       <c r="R259" t="n">
-        <v>6559035</v>
+        <v>6558921</v>
       </c>
       <c r="S259" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -32460,7 +32468,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -32470,7 +32478,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -32485,22 +32493,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128078836</v>
+        <v>128080139</v>
       </c>
       <c r="B260" t="n">
-        <v>92667</v>
+        <v>92631</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32508,52 +32516,44 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>577565</v>
+        <v>577344</v>
       </c>
       <c r="R260" t="n">
-        <v>6558921</v>
+        <v>6559035</v>
       </c>
       <c r="S260" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -32607,19 +32607,19 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>128078589</v>
+        <v>128078494</v>
       </c>
       <c r="B261" t="n">
         <v>98467</v>
@@ -32649,7 +32649,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -32662,17 +32662,17 @@
       <c r="N261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Djupadroget, Srm</t>
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>577614</v>
+        <v>577630</v>
       </c>
       <c r="R261" t="n">
-        <v>6558989</v>
+        <v>6558954</v>
       </c>
       <c r="S261" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -32701,7 +32701,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -32711,7 +32711,7 @@
       </c>
       <c r="AB261" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD261" t="b">
@@ -32726,19 +32726,19 @@
       <c r="AT261" t="inlineStr"/>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>128078494</v>
+        <v>128078589</v>
       </c>
       <c r="B262" t="n">
         <v>98467</v>
@@ -32768,7 +32768,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -32781,17 +32781,17 @@
       <c r="N262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
         <is>
-          <t>Djupadroget, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>577630</v>
+        <v>577614</v>
       </c>
       <c r="R262" t="n">
-        <v>6558954</v>
+        <v>6558989</v>
       </c>
       <c r="S262" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -32820,7 +32820,7 @@
       </c>
       <c r="Z262" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -32830,7 +32830,7 @@
       </c>
       <c r="AB262" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD262" t="b">
@@ -32845,12 +32845,12 @@
       <c r="AT262" t="inlineStr"/>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30713,35 +30713,39 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128078400</v>
+        <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>91314</v>
+        <v>92642</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5447</v>
+        <v>788</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30755,13 +30759,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>577571</v>
+        <v>577474</v>
       </c>
       <c r="R245" t="n">
-        <v>6558993</v>
+        <v>6559047</v>
       </c>
       <c r="S245" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30790,7 +30794,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -30800,7 +30804,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -30815,51 +30819,47 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128077874</v>
+        <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>92641</v>
+        <v>91315</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>788</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30873,13 +30873,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>577474</v>
+        <v>577571</v>
       </c>
       <c r="R246" t="n">
-        <v>6559047</v>
+        <v>6558993</v>
       </c>
       <c r="S246" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -30933,12 +30933,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92657</v>
+        <v>92658</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101553</v>
+        <v>101554</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander, Hanna Nordin</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92651</v>
+        <v>92652</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander, Hanna Nordin</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96069</v>
+        <v>96070</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128078836</v>
       </c>
       <c r="B259" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>128080139</v>
       </c>
       <c r="B260" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -31898,7 +31898,7 @@
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>Michael Lander, Hanna Nordin</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
@@ -32383,10 +32383,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128078836</v>
+        <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92668</v>
+        <v>92632</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32394,52 +32394,44 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K259" t="inlineStr"/>
       <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>577565</v>
+        <v>577344</v>
       </c>
       <c r="R259" t="n">
-        <v>6558921</v>
+        <v>6559035</v>
       </c>
       <c r="S259" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -32468,7 +32460,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -32478,7 +32470,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -32493,22 +32485,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128080139</v>
+        <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92632</v>
+        <v>92668</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32516,44 +32508,52 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J260" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>577344</v>
+        <v>577565</v>
       </c>
       <c r="R260" t="n">
-        <v>6559035</v>
+        <v>6558921</v>
       </c>
       <c r="S260" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -32607,12 +32607,12 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>92642</v>
+        <v>92643</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101554</v>
+        <v>101555</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Michael Lander, Hanna Nordin</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96070</v>
+        <v>96071</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>92643</v>
+        <v>92644</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96071</v>
+        <v>96072</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>92644</v>
+        <v>92652</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101556</v>
+        <v>101564</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96072</v>
+        <v>96080</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92670</v>
+        <v>92678</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101564</v>
+        <v>101657</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96080</v>
+        <v>96173</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92678</v>
+        <v>92770</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander, Hanna Nordin</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30713,39 +30713,35 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128077874</v>
+        <v>128078400</v>
       </c>
       <c r="B245" t="n">
-        <v>92744</v>
+        <v>91417</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>788</v>
+        <v>5447</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30759,13 +30755,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>577474</v>
+        <v>577571</v>
       </c>
       <c r="R245" t="n">
-        <v>6559047</v>
+        <v>6558993</v>
       </c>
       <c r="S245" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30794,7 +30790,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -30804,7 +30800,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -30819,47 +30815,51 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128078400</v>
+        <v>128077874</v>
       </c>
       <c r="B246" t="n">
-        <v>91417</v>
+        <v>92744</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5447</v>
+        <v>788</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30873,13 +30873,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>577571</v>
+        <v>577474</v>
       </c>
       <c r="R246" t="n">
-        <v>6558993</v>
+        <v>6559047</v>
       </c>
       <c r="S246" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -30933,12 +30933,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -32612,7 +32612,7 @@
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Michael Lander, Hanna Nordin</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander, Hanna Nordin</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128078400</v>
       </c>
       <c r="B245" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>128077874</v>
       </c>
       <c r="B246" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92760</v>
+        <v>92772</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101657</v>
+        <v>101673</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>Michael Lander, Hanna Nordin</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96173</v>
+        <v>96185</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>128080139</v>
       </c>
       <c r="B259" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>128078836</v>
       </c>
       <c r="B260" t="n">
-        <v>92770</v>
+        <v>92782</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30713,35 +30713,39 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128078400</v>
+        <v>128077874</v>
       </c>
       <c r="B245" t="n">
-        <v>91429</v>
+        <v>92756</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>5447</v>
+        <v>788</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30755,13 +30759,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>577571</v>
+        <v>577474</v>
       </c>
       <c r="R245" t="n">
-        <v>6558993</v>
+        <v>6559047</v>
       </c>
       <c r="S245" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30790,7 +30794,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -30800,7 +30804,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -30815,51 +30819,47 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128077874</v>
+        <v>128078400</v>
       </c>
       <c r="B246" t="n">
-        <v>92756</v>
+        <v>91429</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>788</v>
+        <v>5447</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30873,13 +30873,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>577474</v>
+        <v>577571</v>
       </c>
       <c r="R246" t="n">
-        <v>6559047</v>
+        <v>6558993</v>
       </c>
       <c r="S246" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -30933,12 +30933,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101673</v>
+        <v>101676</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30713,39 +30713,35 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128077874</v>
+        <v>128078400</v>
       </c>
       <c r="B245" t="n">
-        <v>92756</v>
+        <v>91429</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>788</v>
+        <v>5447</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30759,13 +30755,13 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>577474</v>
+        <v>577571</v>
       </c>
       <c r="R245" t="n">
-        <v>6559047</v>
+        <v>6558993</v>
       </c>
       <c r="S245" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -30794,7 +30790,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -30804,7 +30800,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -30819,47 +30815,51 @@
       <c r="AT245" t="inlineStr"/>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128078400</v>
+        <v>128077874</v>
       </c>
       <c r="B246" t="n">
-        <v>91429</v>
+        <v>92756</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5447</v>
+        <v>788</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J246" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -30873,13 +30873,13 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>577571</v>
+        <v>577474</v>
       </c>
       <c r="R246" t="n">
-        <v>6558993</v>
+        <v>6559047</v>
       </c>
       <c r="S246" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -30918,7 +30918,7 @@
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -30933,12 +30933,12 @@
       <c r="AT246" t="inlineStr"/>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -30716,7 +30716,7 @@
         <v>128078400</v>
       </c>
       <c r="B245" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>128077874</v>
       </c>
       <c r="B246" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>128079171</v>
       </c>
       <c r="B247" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>128078876</v>
       </c>
       <c r="B248" t="n">
-        <v>92772</v>
+        <v>92774</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -31185,7 +31185,7 @@
         <v>128080803</v>
       </c>
       <c r="B249" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -31299,7 +31299,7 @@
         <v>128080627</v>
       </c>
       <c r="B250" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>128078577</v>
       </c>
       <c r="B251" t="n">
-        <v>101676</v>
+        <v>101684</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>128078005</v>
       </c>
       <c r="B252" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>128080535</v>
       </c>
       <c r="B253" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>128079953</v>
       </c>
       <c r="B254" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>128081735</v>
       </c>
       <c r="B255" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -32026,7 +32026,7 @@
         <v>128079597</v>
       </c>
       <c r="B256" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>128078152</v>
       </c>
       <c r="B257" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>128079606</v>
       </c>
       <c r="B258" t="n">
-        <v>96185</v>
+        <v>96187</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -32383,10 +32383,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>128080139</v>
+        <v>128078836</v>
       </c>
       <c r="B259" t="n">
-        <v>92746</v>
+        <v>92784</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -32394,44 +32394,52 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
         <is>
-          <t>Strandmossen, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>577344</v>
+        <v>577565</v>
       </c>
       <c r="R259" t="n">
-        <v>6559035</v>
+        <v>6558921</v>
       </c>
       <c r="S259" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -32460,7 +32468,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -32470,7 +32478,7 @@
       </c>
       <c r="AB259" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD259" t="b">
@@ -32485,22 +32493,22 @@
       <c r="AT259" t="inlineStr"/>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Hanna Nordin, Michael Lander</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>128078836</v>
+        <v>128080139</v>
       </c>
       <c r="B260" t="n">
-        <v>92782</v>
+        <v>92748</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -32508,52 +32516,44 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="N260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Strandmossen, Srm</t>
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>577565</v>
+        <v>577344</v>
       </c>
       <c r="R260" t="n">
-        <v>6558921</v>
+        <v>6559035</v>
       </c>
       <c r="S260" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="Z260" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -32592,7 +32592,7 @@
       </c>
       <c r="AB260" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD260" t="b">
@@ -32607,12 +32607,12 @@
       <c r="AT260" t="inlineStr"/>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Hanna Nordin</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>Hanna Nordin, Michael Lander</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
@@ -32622,7 +32622,7 @@
         <v>128078494</v>
       </c>
       <c r="B261" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>128078589</v>
       </c>
       <c r="B262" t="n">
-        <v>98585</v>
+        <v>98591</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY262"/>
+  <dimension ref="A1:AY263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32855,6 +32855,144 @@
       </c>
       <c r="AY262" t="inlineStr"/>
     </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>129966723</v>
+      </c>
+      <c r="B263" t="n">
+        <v>56918</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Söder om Strandmossen, Strandmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>577519</v>
+      </c>
+      <c r="R263" t="n">
+        <v>6559015</v>
+      </c>
+      <c r="S263" t="n">
+        <v>25</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>Järpe,hona. Spelade skadad för att skydda ungar.</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>Fuktig barrskog med inslag av löv.</t>
+        </is>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -32860,7 +32860,7 @@
         <v>129966723</v>
       </c>
       <c r="B263" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY263"/>
+  <dimension ref="A1:AY266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32993,6 +32993,336 @@
       </c>
       <c r="AY263" t="inlineStr"/>
     </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>130052884</v>
+      </c>
+      <c r="B264" t="n">
+        <v>91627</v>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>577043</v>
+      </c>
+      <c r="R264" t="n">
+        <v>6558734</v>
+      </c>
+      <c r="S264" t="n">
+        <v>2</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>130052890</v>
+      </c>
+      <c r="B265" t="n">
+        <v>92426</v>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Koralltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Hericium coralloides</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Scop.) Pers.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>577033</v>
+      </c>
+      <c r="R265" t="n">
+        <v>6558745</v>
+      </c>
+      <c r="S265" t="n">
+        <v>4</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>130052888</v>
+      </c>
+      <c r="B266" t="n">
+        <v>92038</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>577043</v>
+      </c>
+      <c r="R266" t="n">
+        <v>6558735</v>
+      </c>
+      <c r="S266" t="n">
+        <v>3</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Göran Ekström, Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY266"/>
+  <dimension ref="A1:AY267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33323,6 +33323,112 @@
       </c>
       <c r="AY266" t="inlineStr"/>
     </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>130079626</v>
+      </c>
+      <c r="B267" t="n">
+        <v>92263</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Hökhult NV om , Srm</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>576957</v>
+      </c>
+      <c r="R267" t="n">
+        <v>6558807</v>
+      </c>
+      <c r="S267" t="n">
+        <v>25</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF267" t="inlineStr"/>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -32998,7 +32998,7 @@
         <v>130052884</v>
       </c>
       <c r="B264" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>130052890</v>
       </c>
       <c r="B265" t="n">
-        <v>92426</v>
+        <v>92443</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>130052888</v>
       </c>
       <c r="B266" t="n">
-        <v>92038</v>
+        <v>92055</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>130079626</v>
       </c>
       <c r="B267" t="n">
-        <v>92263</v>
+        <v>92276</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY272"/>
+  <dimension ref="A1:AY275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32998,7 +32998,7 @@
         <v>130052884</v>
       </c>
       <c r="B264" t="n">
-        <v>91660</v>
+        <v>91662</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>130052890</v>
       </c>
       <c r="B265" t="n">
-        <v>92459</v>
+        <v>92461</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>130052888</v>
       </c>
       <c r="B266" t="n">
-        <v>92071</v>
+        <v>92073</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>130079626</v>
       </c>
       <c r="B267" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -34046,6 +34046,405 @@
       </c>
       <c r="AY272" t="inlineStr"/>
     </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>130244515</v>
+      </c>
+      <c r="B273" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>577399</v>
+      </c>
+      <c r="R273" t="n">
+        <v>6558902</v>
+      </c>
+      <c r="S273" t="n">
+        <v>4</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>130251368</v>
+      </c>
+      <c r="B274" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>577354</v>
+      </c>
+      <c r="R274" t="n">
+        <v>6558830</v>
+      </c>
+      <c r="S274" t="n">
+        <v>5</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>Observerade spillkråkan som födosökte på gran och tall.</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>130251199</v>
+      </c>
+      <c r="B275" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>577410</v>
+      </c>
+      <c r="R275" t="n">
+        <v>6558799</v>
+      </c>
+      <c r="S275" t="n">
+        <v>25</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>Ett par spillkråkor födosökte i skogspartiet. Både på gran och tall.</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY275"/>
+  <dimension ref="A1:AY276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32860,7 +32860,7 @@
         <v>129966723</v>
       </c>
       <c r="B263" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -32998,7 +32998,7 @@
         <v>130052884</v>
       </c>
       <c r="B264" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>130052890</v>
       </c>
       <c r="B265" t="n">
-        <v>92461</v>
+        <v>92548</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>130052888</v>
       </c>
       <c r="B266" t="n">
-        <v>92073</v>
+        <v>92160</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>130079626</v>
       </c>
       <c r="B267" t="n">
-        <v>92294</v>
+        <v>92381</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>130184327</v>
       </c>
       <c r="B271" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>130189802</v>
       </c>
       <c r="B272" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -34048,44 +34048,40 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>130244515</v>
+        <v>130251827</v>
       </c>
       <c r="B273" t="n">
-        <v>57738</v>
+        <v>57016</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -34095,17 +34091,17 @@
       </c>
       <c r="P273" t="inlineStr">
         <is>
-          <t>Hökhult, Srm</t>
+          <t>Hökhult, Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>577399</v>
+        <v>577397</v>
       </c>
       <c r="R273" t="n">
-        <v>6558902</v>
+        <v>6558891</v>
       </c>
       <c r="S273" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -34134,7 +34130,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -34144,7 +34140,12 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>Färsk spillning och blindtarmstömning under äldre tall. Skogen är hotad av avverkning.</t>
         </is>
       </c>
       <c r="AD273" t="b">
@@ -34155,6 +34156,16 @@
       </c>
       <c r="AG273" t="b">
         <v>0</v>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
       </c>
       <c r="AT273" t="inlineStr"/>
       <c r="AW273" t="inlineStr">
@@ -34171,10 +34182,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>130251368</v>
+        <v>130244515</v>
       </c>
       <c r="B274" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -34204,31 +34215,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Hökhult, Hökhult, Srm</t>
+          <t>Hökhult, Srm</t>
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>577354</v>
+        <v>577399</v>
       </c>
       <c r="R274" t="n">
-        <v>6558830</v>
+        <v>6558902</v>
       </c>
       <c r="S274" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -34257,7 +34268,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -34267,12 +34278,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>Observerade spillkråkan som födosökte på gran och tall.</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD274" t="b">
@@ -34283,16 +34289,6 @@
       </c>
       <c r="AG274" t="b">
         <v>0</v>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
       </c>
       <c r="AT274" t="inlineStr"/>
       <c r="AW274" t="inlineStr">
@@ -34309,10 +34305,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>130251199</v>
+        <v>130251368</v>
       </c>
       <c r="B275" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -34339,7 +34335,7 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -34360,13 +34356,13 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>577410</v>
+        <v>577354</v>
       </c>
       <c r="R275" t="n">
-        <v>6558799</v>
+        <v>6558830</v>
       </c>
       <c r="S275" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -34410,7 +34406,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>Ett par spillkråkor födosökte i skogspartiet. Både på gran och tall.</t>
+          <t>Observerade spillkråkan som födosökte på gran och tall.</t>
         </is>
       </c>
       <c r="AD275" t="b">
@@ -34429,7 +34425,7 @@
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Äldre barrblandskog</t>
         </is>
       </c>
       <c r="AT275" t="inlineStr"/>
@@ -34444,6 +34440,144 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>130251199</v>
+      </c>
+      <c r="B276" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>577410</v>
+      </c>
+      <c r="R276" t="n">
+        <v>6558799</v>
+      </c>
+      <c r="S276" t="n">
+        <v>25</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2025-12-21</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>Ett par spillkråkor födosökte i skogspartiet. Både på gran och tall.</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -16990,7 +16990,7 @@
         <v>0</v>
       </c>
       <c r="AE127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
@@ -30471,7 +30471,7 @@
         <v>0</v>
       </c>
       <c r="AE242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG242" t="b">
         <v>0</v>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33431,7 +33431,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130184617</v>
+        <v>130185125</v>
       </c>
       <c r="B268" t="n">
         <v>5177</v>
@@ -33483,10 +33483,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>577136</v>
+        <v>577124</v>
       </c>
       <c r="R268" t="n">
-        <v>6558787</v>
+        <v>6558759</v>
       </c>
       <c r="S268" t="n">
         <v>4</v>
@@ -33518,7 +33518,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -33555,7 +33555,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>130185125</v>
+        <v>130184617</v>
       </c>
       <c r="B269" t="n">
         <v>5177</v>
@@ -33607,10 +33607,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>577124</v>
+        <v>577136</v>
       </c>
       <c r="R269" t="n">
-        <v>6558759</v>
+        <v>6558787</v>
       </c>
       <c r="S269" t="n">
         <v>4</v>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33431,7 +33431,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>130185125</v>
+        <v>130184617</v>
       </c>
       <c r="B268" t="n">
         <v>5177</v>
@@ -33483,10 +33483,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>577124</v>
+        <v>577136</v>
       </c>
       <c r="R268" t="n">
-        <v>6558759</v>
+        <v>6558787</v>
       </c>
       <c r="S268" t="n">
         <v>4</v>
@@ -33518,7 +33518,7 @@
       </c>
       <c r="Z268" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
@@ -33528,7 +33528,7 @@
       </c>
       <c r="AB268" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD268" t="b">
@@ -33555,7 +33555,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>130184617</v>
+        <v>130185125</v>
       </c>
       <c r="B269" t="n">
         <v>5177</v>
@@ -33607,10 +33607,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>577136</v>
+        <v>577124</v>
       </c>
       <c r="R269" t="n">
-        <v>6558787</v>
+        <v>6558759</v>
       </c>
       <c r="S269" t="n">
         <v>4</v>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="Z269" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="AB269" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD269" t="b">
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>130184327</v>
       </c>
       <c r="B271" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>130189802</v>
       </c>
       <c r="B272" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>130251827</v>
       </c>
       <c r="B273" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>130244515</v>
       </c>
       <c r="B274" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>130251368</v>
       </c>
       <c r="B275" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>130251199</v>
       </c>
       <c r="B276" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33682,7 +33682,7 @@
         <v>130184605</v>
       </c>
       <c r="B270" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>130184327</v>
       </c>
       <c r="B271" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>130189802</v>
       </c>
       <c r="B272" t="n">
-        <v>57033</v>
+        <v>57035</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>130251827</v>
       </c>
       <c r="B273" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
         <v>130244515</v>
       </c>
       <c r="B274" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>130251368</v>
       </c>
       <c r="B275" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -34446,7 +34446,7 @@
         <v>130251199</v>
       </c>
       <c r="B276" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -33919,7 +33919,7 @@
         <v>130189802</v>
       </c>
       <c r="B272" t="n">
-        <v>57035</v>
+        <v>57044</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -34051,7 +34051,7 @@
         <v>130251827</v>
       </c>
       <c r="B273" t="n">
-        <v>57044</v>
+        <v>57053</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY276"/>
+  <dimension ref="A1:AY277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34579,6 +34579,122 @@
       </c>
       <c r="AY276" t="inlineStr"/>
     </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>131430243</v>
+      </c>
+      <c r="B277" t="n">
+        <v>96612</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Hökhult, Hökhult, Srm</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>577332</v>
+      </c>
+      <c r="R277" t="n">
+        <v>6558844</v>
+      </c>
+      <c r="S277" t="n">
+        <v>4</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Floda</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>Flertal större kuddar</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96612</v>
+        <v>96613</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96613</v>
+        <v>96616</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96617</v>
+        <v>96623</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96623</v>
+        <v>96624</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96634</v>
+        <v>96637</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -34584,7 +34584,7 @@
         <v>131430243</v>
       </c>
       <c r="B277" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY285"/>
+  <dimension ref="A1:AZ285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128081265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747517</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118899119</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118902324</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699553</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128077874</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1462,6 +1497,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601087</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120223306</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1694,6 +1739,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184605</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1815,6 +1865,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120841678</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1949,6 +2004,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762406</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052890</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2174,6 +2239,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607245</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2289,6 +2359,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607355</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746783</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2537,6 +2617,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762857</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2656,6 +2741,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118900182</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2767,6 +2857,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118901119</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,6 +2980,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601840</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3001,6 +3101,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608044</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3128,6 +3233,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762985</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3244,6 +3354,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118984152</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3351,6 +3466,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118984277</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3462,6 +3582,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599967</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3581,6 +3706,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119600732</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3696,6 +3826,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601987</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3811,6 +3946,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602000</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3926,6 +4066,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602448</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4037,6 +4182,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602593</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4148,6 +4298,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602836</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4259,6 +4414,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603451</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4375,6 +4535,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079606</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4491,6 +4656,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131430243</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4609,6 +4779,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601728</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4716,6 +4891,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421075</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4813,6 +4993,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421265</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4920,6 +5105,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118901779</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5027,6 +5217,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118905501</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5141,6 +5336,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602671</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5255,6 +5455,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603136</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5352,6 +5557,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699541</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5449,6 +5659,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119700995</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5563,6 +5778,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128080139</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5685,6 +5905,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079953</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5799,6 +6024,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118606898</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5913,6 +6143,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745381</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6020,6 +6255,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118905087</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6138,6 +6378,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602238</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6235,6 +6480,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699969</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6332,6 +6582,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701705</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6450,6 +6705,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128080627</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6564,6 +6824,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960801</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6687,6 +6952,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079171</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6809,6 +7079,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128079597</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6920,6 +7195,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118984851</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7017,6 +7297,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699197</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7118,6 +7403,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699263</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7215,6 +7505,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699345</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7322,6 +7617,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421211</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7419,6 +7719,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421609</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7533,6 +7838,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078876</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7652,6 +7962,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118609397</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7759,6 +8074,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119014363</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7856,6 +8176,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119702774</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7963,6 +8288,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420997</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8073,6 +8403,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052888</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8197,6 +8532,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656843</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8326,6 +8666,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763011</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8433,6 +8778,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118904861</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8540,6 +8890,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983498</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8658,6 +9013,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599395</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8774,6 +9134,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599599</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8892,6 +9257,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599816</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9002,6 +9372,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052884</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9116,6 +9491,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078400</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9234,6 +9614,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601454</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9345,6 +9730,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119016084</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9442,6 +9832,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701851</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9539,6 +9934,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703722</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9636,6 +10036,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420691</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9743,6 +10148,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420733</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9850,6 +10260,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420928</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9957,6 +10372,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420939</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10078,6 +10498,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120841150</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10175,6 +10600,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701745</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10281,6 +10711,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130079626</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10392,6 +10827,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119703369</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10489,6 +10929,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699114</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10630,6 +11075,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117895998</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10744,6 +11194,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118742934</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10863,6 +11318,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118742959</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10970,6 +11430,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119014968</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11084,6 +11549,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603449</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11204,6 +11674,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117895991</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11334,6 +11809,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117896031</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11453,6 +11933,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607100</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11574,6 +12059,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659226</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11686,6 +12176,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013293</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11809,6 +12304,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601316</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11925,6 +12425,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699339</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12048,6 +12553,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130244515</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12186,6 +12696,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251199</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12324,6 +12839,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251368</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12435,6 +12955,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421230</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12551,6 +13076,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013201</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12679,6 +13209,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118606437</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12803,6 +13338,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607818</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12927,6 +13467,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608908</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13059,6 +13604,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118741753</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13193,6 +13743,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130251827</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13313,6 +13868,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118529201</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13433,6 +13993,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118741866</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13553,6 +14118,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118741902</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13673,6 +14243,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745607</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13793,6 +14368,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599958</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13909,6 +14489,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119600012</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14011,6 +14596,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119698812</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14135,6 +14725,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184617</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14259,6 +14854,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130185125</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14371,6 +14971,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603453</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14509,6 +15114,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129966723</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14641,6 +15251,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130189802</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14764,6 +15379,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118742686</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14883,6 +15503,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746645</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15006,6 +15631,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607040</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15130,6 +15760,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659071</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15246,6 +15881,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699976</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15369,6 +16009,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130184327</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15489,6 +16134,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118530482</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15616,6 +16266,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762639</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15736,6 +16391,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599959</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15838,6 +16498,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119698814</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15958,6 +16623,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608516</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16085,6 +16755,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763040</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16210,6 +16885,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118530351</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16326,6 +17006,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531029</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16446,6 +17131,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743490</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16570,6 +17260,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745501</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16698,6 +17393,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746047</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16826,6 +17526,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746174</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16954,6 +17659,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746895</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -17074,6 +17784,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747177</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17202,6 +17917,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747303</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17338,6 +18058,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762728</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17445,6 +18170,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118982113</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17561,6 +18291,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983369</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17681,6 +18416,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603442</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17801,6 +18541,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119600824</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17908,6 +18653,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119015409</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -18038,6 +18788,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656618</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -18145,6 +18900,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118904803</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -18252,6 +19012,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118983332</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18376,6 +19141,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117886809</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18500,6 +19270,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118529355</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18625,6 +19400,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118530311</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18745,6 +19525,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531013</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18873,6 +19658,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531233</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -19001,6 +19791,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531272</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -19129,6 +19924,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531470</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -19257,6 +20057,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531539</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -19381,6 +20186,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531593</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -19505,6 +20315,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531648</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19625,6 +20440,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531769</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19745,6 +20565,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531795</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19865,6 +20690,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531894</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19989,6 +20819,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118531964</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -20117,6 +20952,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532104</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -20245,6 +21085,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532152</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -20368,6 +21213,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532207</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -20491,6 +21341,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532244</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -20614,6 +21469,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532340</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20738,6 +21598,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118532518</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20866,6 +21731,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604154</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20990,6 +21860,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604257</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -21118,6 +21993,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604444</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -21242,6 +22122,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604601</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -21370,6 +22255,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604642</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -21489,6 +22379,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118604936</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -21617,6 +22512,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118605674</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -21737,6 +22637,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118605786</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21865,6 +22770,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607500</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21993,6 +22903,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118607610</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -22116,6 +23031,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608463</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -22237,6 +23157,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118608594</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -22368,6 +23293,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656671</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -22493,6 +23423,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118656811</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -22623,6 +23558,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657203</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -22753,6 +23693,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657356</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -22883,6 +23828,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657434</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -23013,6 +23963,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118657784</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -23143,6 +24098,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118658222</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -23266,6 +24226,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118741394</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -23389,6 +24354,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118742646</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -23512,6 +24482,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743184</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -23635,6 +24610,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743461</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -23759,6 +24739,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743767</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -23887,6 +24872,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118744246</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -24010,6 +25000,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745017</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -24138,6 +25133,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745041</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -24257,6 +25257,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745126</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -24376,6 +25381,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745157</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -24504,6 +25514,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745173</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -24627,6 +25642,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745233</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -24746,6 +25766,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745374</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -24869,6 +25894,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745546</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -24992,6 +26022,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746192</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -25111,6 +26146,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746546</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -25234,6 +26274,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746563</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -25362,6 +26407,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746924</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -25485,6 +26535,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746972</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -25613,6 +26668,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747088</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -25736,6 +26796,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747585</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -25864,6 +26929,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118747671</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -25999,6 +27069,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118761703</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -26134,6 +27209,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762009</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -26269,6 +27349,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762028</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -26404,6 +27489,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762063</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -26534,6 +27624,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762118</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -26669,6 +27764,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762211</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -26808,6 +27908,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762253</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -26943,6 +28048,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762329</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -27073,6 +28183,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762491</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -27208,6 +28323,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762524</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -27343,6 +28463,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762567</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -27473,6 +28598,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762766</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -27604,6 +28734,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762787</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -27739,6 +28874,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762826</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -27869,6 +29009,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762923</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -28004,6 +29149,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118762969</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -28139,6 +29289,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763082</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -28270,6 +29425,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763103</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -28377,6 +29537,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118898276</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -28478,6 +29643,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118898293</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -28601,6 +29771,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118898334</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -28716,6 +29891,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599396</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -28831,6 +30011,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119599963</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -28950,6 +30135,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119600170</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -29069,6 +30259,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601023</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -29190,6 +30385,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601286</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -29309,6 +30509,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601607</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -29428,6 +30633,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119601750</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -29544,6 +30754,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602280</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -29663,6 +30878,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602380</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -29782,6 +31002,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602564</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -29903,6 +31128,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119603201</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -30040,6 +31270,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612701</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -30177,6 +31412,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612765</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -30314,6 +31554,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612860</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -30451,6 +31696,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119612900</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -30548,6 +31798,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699201</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -30650,6 +31905,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119699664</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -30747,6 +32007,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701512</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -30844,6 +32109,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701601</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -30941,6 +32211,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701628</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -31038,6 +32313,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119701751</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -31135,6 +32415,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119702381</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -31232,6 +32517,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119702969</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -31339,6 +32629,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120420968</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -31446,6 +32741,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421495</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -31553,6 +32853,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421513</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -31660,6 +32965,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421553</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -31788,6 +33098,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078005</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -31907,6 +33222,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078494</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -32026,6 +33346,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078589</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -32154,6 +33479,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118529884</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -32278,6 +33608,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118530252</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -32402,6 +33737,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118605873</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -32521,6 +33861,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743618</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -32640,6 +33985,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745272</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -32759,6 +34109,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118745456</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -32878,6 +34233,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118746507</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -32985,6 +34345,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118905789</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -33100,6 +34465,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602497</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -33219,6 +34589,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119602562</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -33326,6 +34701,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54038836</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -33445,6 +34825,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128078577</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -33557,6 +34942,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118659430</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -33679,6 +35069,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118763090</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -33786,6 +35181,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118984865</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -33893,6 +35293,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119013375</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -34008,6 +35413,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120841364</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -34120,6 +35530,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54038835</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -34222,6 +35637,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54038823</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -34341,8 +35761,299 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118743417</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56838</v>
+        <v>56840</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56840</v>
+        <v>56841</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56841</v>
+        <v>56845</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56845</v>
+        <v>56846</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56846</v>
+        <v>56851</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91558</v>
+        <v>91559</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91559</v>
+        <v>91572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>136001867</v>
       </c>
       <c r="B136" t="n">
-        <v>56851</v>
+        <v>56864</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 28806-2024 artfynd.xlsx
+++ b/artfynd/A 28806-2024 artfynd.xlsx
@@ -2130,7 +2130,7 @@
         <v>118607245</v>
       </c>
       <c r="B14" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>118762857</v>
       </c>
       <c r="B17" t="n">
-        <v>91572</v>
+        <v>91573</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
